--- a/MATERIAL 1.xlsx
+++ b/MATERIAL 1.xlsx
@@ -7,11 +7,15 @@
     <workbookView windowWidth="24000" windowHeight="9600"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="REKAP_INPUT" sheetId="2" r:id="rId2"/>
+    <sheet name="HEADER APLIKASI" sheetId="1" r:id="rId1"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId2"/>
+  </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$6:$H$62</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'HEADER APLIKASI'!$A$6:$J$62</definedName>
+    <definedName name="_\aaaaaaaaaaaaa">#REF!</definedName>
+    <definedName name="_\B">#N/A</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -31,15 +35,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1370" uniqueCount="180">
   <si>
     <t>NAMA PEKERJAAN :</t>
   </si>
   <si>
-    <t>TYPE PEKERJAAN : SAR/PFK/PREVENTIF/KEYPOINT (bisa di dropdown)</t>
-  </si>
-  <si>
-    <t>JENIS KONSTRUKSI : SKTR/SKSR/SUTR/SUTM (bisa di dropdown)</t>
+    <t>ALAMAT PEKERJAAN :</t>
+  </si>
+  <si>
+    <t>JENIS PEKERJAAN : SAR/PFK/PREVENTIF/KEYPOINT (bisa di dropdown)</t>
   </si>
   <si>
     <t xml:space="preserve">TANGGAL : </t>
@@ -48,9 +52,15 @@
     <t>NO</t>
   </si>
   <si>
+    <t>JENIS KONSTRUKSI</t>
+  </si>
+  <si>
     <t>NAMA MATERIAL</t>
   </si>
   <si>
+    <t>TYPE KONSTRUKSI</t>
+  </si>
+  <si>
     <t>Volume Matrial</t>
   </si>
   <si>
@@ -60,184 +70,511 @@
     <t>Volume Bongkar</t>
   </si>
   <si>
-    <t>Bata Merah (Hanya Untuk Sekat Antar Kabel)</t>
-  </si>
-  <si>
-    <t>Bc 50 Mm (Bare Conductor)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bolt M.12 X 30 + Washer Cu </t>
-  </si>
-  <si>
-    <t>Borring Untuk Kabel Tanah</t>
-  </si>
-  <si>
-    <t>Concrete Slove</t>
-  </si>
-  <si>
-    <t>Cross Arm Unp 100 - 500 Mm - (L=50 Mm, T=5 Mm, Tgg=100 Mm)</t>
-  </si>
-  <si>
-    <t>Cross Arm Unp 100 - 900 Mm - (L=50Mm, T=5Mm, Tgg=100Mm)</t>
-  </si>
-  <si>
-    <t>Dinabolt 10Mmx100Mm</t>
-  </si>
-  <si>
-    <t>Earthing Rod 16 Mm - 1,5 M+Clamp - Tr- Besi As, Electroplatting Tembaga 35 Micron</t>
-  </si>
-  <si>
-    <t>Fuse  Holder 400A 600 V</t>
-  </si>
-  <si>
-    <t>Galian &amp; Pengurugan Kembali Beton Bertulang</t>
-  </si>
-  <si>
-    <t>Galian Aspal &amp; Pengurugan Kembali Aspal (Tebal Aspal 30 Cm + Dipadatkan)</t>
-  </si>
-  <si>
-    <t>Galian Floor Beton &amp; Pengurugan Kembali Floor Beton</t>
-  </si>
-  <si>
-    <t>Galian Tanah &amp; Pengurugan Kembali Di Bawah Pv Blok/Tembok/Plesteran</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Galian Tanah &amp; Pengurugan Kembali Kabel Sktm   Uk. (0,7 X 0,4 X 1) </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Galian Tanah &amp; Pengurugan Kembali Kabel Sktr    Uk. (0,6 X 0,4 X 1) </t>
-  </si>
-  <si>
-    <t>Isolator (Footstuken)+ Bolt &amp; Nuts Bahan Ebonit</t>
-  </si>
-  <si>
-    <t>Kabel  Nyfgby 4 X  10 Mm2</t>
-  </si>
-  <si>
-    <t>Kabel  Nyfgby 4 X  50 Mm2</t>
-  </si>
-  <si>
-    <t>Kabel  Nyfgby 4 X  70 Mm2</t>
-  </si>
-  <si>
-    <t>Kabel  Nyfgby 4 X  95 Mm2</t>
-  </si>
-  <si>
-    <t>Kabel Nya 10 Mm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kanal Np 10 2200 </t>
-  </si>
-  <si>
-    <t>Lampu Indikator  R, S, T  Dan Kelengkapan</t>
-  </si>
-  <si>
-    <t>Mcb 3Phs 50 A</t>
-  </si>
-  <si>
-    <t>Nh Fuse Jurusan 125 A</t>
-  </si>
-  <si>
-    <t>Nh Fuse Jurusan 250 A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P X L X T = 70 X 40 X 107 Cm </t>
-  </si>
-  <si>
-    <t>Panel Sdp Pelanggan Ip45 Tebal 3 Mm Lengkap Aksesoris</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Panel Sdp Pembagi Ip45 Tebal 3 Mm </t>
-  </si>
-  <si>
-    <t>Pasir Urug ( 0,2 X 0,4 X 1 )</t>
-  </si>
-  <si>
-    <t>Patok Pelindung Sdp Pipa 3"-1Mtr Dalam Pipa Diisi Cor Semen</t>
-  </si>
-  <si>
-    <t>Patok Tanda Kabel (Rute Kabel)</t>
-  </si>
-  <si>
-    <t>Pipa Galvanized 3" - 6 M (Tebal= 2,5 Mm)</t>
-  </si>
-  <si>
-    <t>Pipa Galvanized 3/4" - 1 M (Tebal= 1,6 Mm)</t>
-  </si>
-  <si>
-    <t>Pipa Galvanized 4" - 6 M (Tebal= 3,2 Mm)</t>
-  </si>
-  <si>
-    <t>Plate Cooper U/ Netral+Ground Uk. 20X3 Mm</t>
-  </si>
-  <si>
-    <t>Plate Cooper Uk. 5X30 Mm Dan Heatshrink Tanda Phasa</t>
-  </si>
-  <si>
-    <t>Pondasi Gardu Menara</t>
-  </si>
-  <si>
-    <t>Pondasi Sdp Sesuai Spesifikasi</t>
-  </si>
-  <si>
-    <t>Saklar Utama Mccb 125 A  50 Hz</t>
-  </si>
-  <si>
-    <t>Saklar Utama Mccb 300 A  50 Hz</t>
-  </si>
-  <si>
-    <t>Sock Draad Pipa Galvanized 3"</t>
-  </si>
-  <si>
-    <t>Sock Draad Pipa Galvanized 4"</t>
-  </si>
-  <si>
-    <t>Terminal Lug 10 Mm - Cu 1 Hole</t>
-  </si>
-  <si>
-    <t>Terminal Lug 50 Mm - Cu 1 Hole</t>
-  </si>
-  <si>
-    <t>Terminal Lug 70 Mm - Cu 1 Hole</t>
-  </si>
-  <si>
-    <t>Terminal Lug 95 Mm - Cu 1 Hole</t>
-  </si>
-  <si>
-    <t>Nama Pekerjaan</t>
-  </si>
-  <si>
-    <t>Type Pekerjaan</t>
-  </si>
-  <si>
-    <t>Jenis Konstruksi</t>
-  </si>
-  <si>
-    <t>Tanggal</t>
-  </si>
-  <si>
-    <t>Material</t>
-  </si>
-  <si>
-    <t>Jumlah Pasang</t>
-  </si>
-  <si>
-    <t>Jumlah Bongkar</t>
-  </si>
-  <si>
-    <t>Jumlah Material</t>
-  </si>
-  <si>
-    <t>paul panggi</t>
-  </si>
-  <si>
-    <t>SAR</t>
-  </si>
-  <si>
     <t>SUTM</t>
   </si>
   <si>
-    <t>2026-08-13</t>
+    <t>CABLE PWR ACC;CABLE SHOE AL-CU 1H 150MM2/TERMINAL LUG 150 MM - AL/CU 1 HOLE</t>
+  </si>
+  <si>
+    <t>ACCESSORIES JAMPER</t>
+  </si>
+  <si>
+    <t>CABLE PWR ACC;CABLE SHOE AL-CU 2H 150MM2</t>
+  </si>
+  <si>
+    <t>COND ACC;TAP CONN 150-150MM2;TYPE G;HS</t>
+  </si>
+  <si>
+    <t>CONDUCTOR;AAAC-S;150MM2;</t>
+  </si>
+  <si>
+    <t>CABLE PWR ACC;CABLE SHOE CU ID 1H 150MM2/TERMINAL LUG 150 MM - CU 1 HOLE</t>
+  </si>
+  <si>
+    <t>BOLT &amp; NUT M.14X 25 - HDG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BOLT M.12 X 30 + WASHER CU </t>
+  </si>
+  <si>
+    <t>PENGHALANG PANJAT 10" HDG (L=35 MM, T=3,2 MM, BESI 10 MM) LENGKAP BOLT&amp;NUT-HDG</t>
+  </si>
+  <si>
+    <t>ANTI CLIMBING + DANGER PLATE</t>
+  </si>
+  <si>
+    <t>TANDA BAHAYA KECIL</t>
+  </si>
+  <si>
+    <t>BOLT &amp; NUT M.16 X 75 - HDG</t>
+  </si>
+  <si>
+    <t>KONDUKTOR</t>
+  </si>
+  <si>
+    <t>CONDUCTOR;AAAC;150MM2;</t>
+  </si>
+  <si>
+    <t>COND ACC;JOINT SLEEVE AL 150MM2</t>
+  </si>
+  <si>
+    <t>COND ACC;NON TENSION JOINT AL 150MM2</t>
+  </si>
+  <si>
+    <t>CONN;20KV;LLC;AL;70-150;BOLT</t>
+  </si>
+  <si>
+    <t>LINE TAP CONNECTOR 240/240 MM TYPE G</t>
+  </si>
+  <si>
+    <t>CONN;1KV;CCO;AL;120-150/50-70MM2;PRS</t>
+  </si>
+  <si>
+    <t>BOLT &amp; NUT M.16 X 50 - HDG</t>
+  </si>
+  <si>
+    <t>TANDA BAHAYA BESAR - (L=400 MM, TGG=450 MM)</t>
+  </si>
+  <si>
+    <t>DANGER PLATE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STAINLESS STEEL STRIP NON MAGNETIC </t>
+  </si>
+  <si>
+    <t>STOPING BUCKLE NON MAGNETIC</t>
+  </si>
+  <si>
+    <t>GALVANIZED STEEL WIRE 35 MM - HDG</t>
+  </si>
+  <si>
+    <t>GROUND WIRE  STEEL  35 MM</t>
+  </si>
+  <si>
+    <t>GROUND WIRE CLAMP TYPE A - TM - (L=50 MM, T=6 MM, P=300 MM)</t>
+  </si>
+  <si>
+    <t>GROUND WIRE CLAMP TYPE B - TM - (L=50 MM, T=6 MM, P=300 MM)</t>
+  </si>
+  <si>
+    <t>SINGLE GUY WIRE BAND 7" - (T = 6 MM X 42 MM) HDG TM LENGKAP NUT-HDG</t>
+  </si>
+  <si>
+    <t>COUSEN/THIMBLE - (T = 2,5 MM)</t>
+  </si>
+  <si>
+    <t>PREFORMED TERMINATION 35 MM (542/U/2009)</t>
+  </si>
+  <si>
+    <t>EARTHING ROD 16 MM - 2,5 M+CLAMP - TM - BESI AS, ELECTROPLATTING TEMBAGA 35 MICRON</t>
+  </si>
+  <si>
+    <t>GROUNDING ARESTER + SKTM + SKUTM</t>
+  </si>
+  <si>
+    <t>AAAC - 70 SQ MM</t>
+  </si>
+  <si>
+    <t>CABLE PWR ACC;CABLE SHOE AL-CU 1H 70MM2/TERMINAL LUG 70 MM - AL/CU 1 HOLE</t>
+  </si>
+  <si>
+    <t>CABLE PWR ACC;CABLE SHOE CU ID 1H 50MM2/TERMINAL LUG CU 50MM 1H</t>
+  </si>
+  <si>
+    <t>NYA 50 SQ MM (SPLN)</t>
+  </si>
+  <si>
+    <t>CABLE PWR ACC;CABLE SHOE CU ID 1H 35MM2/TERMINAL LUG CU 35MM 1H</t>
+  </si>
+  <si>
+    <t>NYAF 35 SQ MM U/BAWAH ARRESTER (SPLN)</t>
+  </si>
+  <si>
+    <t>LINK - HDG</t>
+  </si>
+  <si>
+    <t>PIPA GALVANIZED 3/4" - 4 M (TEBAL= 1,6 MM)</t>
+  </si>
+  <si>
+    <t>CONN;1KV;CCO;AL;50-70/50-70;INSUL;PITA</t>
+  </si>
+  <si>
+    <t>GROUNDING LUAR</t>
+  </si>
+  <si>
+    <t>EARTHING ROD 16 MM - 1,5 M+CLAMP - TR- BESI AS, ELECTROPLATTING TEMBAGA 35 MICRON</t>
+  </si>
+  <si>
+    <t>BOLT &amp; NUT M.16 X 120 - HDG</t>
+  </si>
+  <si>
+    <t>POLE ACC;CR ARM UNP100X50X5X2000MM GALV</t>
+  </si>
+  <si>
+    <t>KONSTRUKSI ARRESTER / LA</t>
+  </si>
+  <si>
+    <t>SINGLE ARM BAND 8" (T = 6 MM X 42 MM) HDG TM LENGKAP NUT-HDG</t>
+  </si>
+  <si>
+    <t>SINGLE ARM BAND 9" (T = 6 MM X 42 MM) HDG TM LENGKAP NUT-HDG</t>
+  </si>
+  <si>
+    <t>ARM TIE TYPE 750 - 3/4" - (T=2,3 MM)</t>
+  </si>
+  <si>
+    <t>ARM TIE BAND 8"(TM) (T = 6 MM X 42 MM) HDG TM LENGKAP BOLT&amp;NUT-HDG</t>
+  </si>
+  <si>
+    <t>ARM TIE BAND 9"(TM) (T = 6 MM X 42 MM) HDG TM LENGKAP BOLT&amp;NUT-HDG</t>
+  </si>
+  <si>
+    <t>SQUARE WASHER - (L=50 MM, P=50 MM, T=2,5 MM)</t>
+  </si>
+  <si>
+    <t>LA;20-24KV;K;10KA;POLYMER;;</t>
+  </si>
+  <si>
+    <t>UNIV ACC;COVER ARRESTER</t>
+  </si>
+  <si>
+    <t>NYA 35 SQ MM (SPLN)</t>
+  </si>
+  <si>
+    <t>DS;K;20KV;1P;630A; ; ;OD</t>
+  </si>
+  <si>
+    <t>KONSTRUKSI DS</t>
+  </si>
+  <si>
+    <t>KONTRUKSI TM - 1</t>
+  </si>
+  <si>
+    <t>ARM TIE BAND 4"(TM) (T = 6 MM X 42 MM) HDG TM LENGKAP BOLT&amp;NUT-HDG</t>
+  </si>
+  <si>
+    <t>BOLT &amp; NUT M.16 X 400 (BESI AS) DOUBLE ARM - HDG</t>
+  </si>
+  <si>
+    <t>SINGLE ARM BAND 6" (T = 6 MM X 42 MM) HDG TM LENGKAP NUT-HDG</t>
+  </si>
+  <si>
+    <t>SINGLE ARM BAND 4" (T = 6 MM X 42 MM) HDG TM LENGKAP NUT-HDG</t>
+  </si>
+  <si>
+    <t>ISOLATOR;PINPOS;PORC;24KV;12,5KN/PIN ISOLATOR 24 KV</t>
+  </si>
+  <si>
+    <t>COND ACC;TOP TIES 150MM2/PREFORMED TOP TIES 150 MM</t>
+  </si>
+  <si>
+    <t>PEKERJAAN UTAMA :</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KONTRUKSI TM - 10 </t>
+  </si>
+  <si>
+    <t>DOUBLE ARM BAND 8 " (T = 6 MM X 42 MM) HDG TM LENGKAP BOLT&amp;NUT-HDG</t>
+  </si>
+  <si>
+    <t>DOUBLE ARM BAND 9 " (T = 6 MM X 42 MM) HDG TM LENGKAP BOLT&amp;NUT-HDG</t>
+  </si>
+  <si>
+    <t>ISOLATOR ;SUSP;POLYMER;24KV;70KN/STRAIN INSULATOR 20 KV PORCELAIN (TARIK)</t>
+  </si>
+  <si>
+    <t>STRAIN CLAMP 150 - 240 MM - 3 NUT</t>
+  </si>
+  <si>
+    <t>CROSS ARM CLEVIS - TM - (L=42 MM, T=6 MM, P=35 MM) - HDG</t>
+  </si>
+  <si>
+    <t>ALLUMINIUM INSULATED BINDING WIRE</t>
+  </si>
+  <si>
+    <t>KONTRUKSI TM - 11 DS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KONTRUKSI TM - 12 </t>
+  </si>
+  <si>
+    <t>POLE ACC;CR ARM UNP100X50X5X2500MM GALV</t>
+  </si>
+  <si>
+    <t>KONTRUKSI TM - 13  GTT 2T  PORTAL SEJAJAR</t>
+  </si>
+  <si>
+    <t>U - STRAP - TM - (L=42 MM, T=6 MM)</t>
+  </si>
+  <si>
+    <t>KONTRUKSI TM - 2</t>
+  </si>
+  <si>
+    <t>PREFORMED SIDE TIE DOUBLE 150 MM (SEMI COND/NON METALIC/COMPOSITE)</t>
+  </si>
+  <si>
+    <t>KONTRUKSI TM - 4 ( TM.4 - TM.4X - TM.4XC )</t>
+  </si>
+  <si>
+    <t>CUT OUT;20KV;5-100A;10KA;125KV</t>
+  </si>
+  <si>
+    <t>KONTRUKSI TM - 5</t>
+  </si>
+  <si>
+    <t>KONTRUKSI TM - 8</t>
+  </si>
+  <si>
+    <t>ARM TIE BAND 6"(TM) (T = 6 MM X 42 MM) HDG TM LENGKAP BOLT&amp;NUT-HDG</t>
+  </si>
+  <si>
+    <t>DOUBLE ARM BAND 6" (T = 6 MM X 42 MM) HDG TM LENGKAP BOLT&amp;NUT-HDG</t>
+  </si>
+  <si>
+    <t>DOUBLE ARM BAND 11" (T = 6 MM X 42 MM) HDG TM LENGKAP BOLT&amp;NUT-HDG</t>
+  </si>
+  <si>
+    <t>POLE BLOCK</t>
+  </si>
+  <si>
+    <t>POLE BLOCK BAND 12" - TM (557/U/2009)</t>
+  </si>
+  <si>
+    <t>CROSS ARM UNP 100 - 1200 MM - (L=50 MM, T=5 MM, TGG=100 MM)</t>
+  </si>
+  <si>
+    <t>POLE ACC;CR ARM UNP100X50X5X1500MM GALV</t>
+  </si>
+  <si>
+    <t>BETON BLOCK 400 X 400 X 100 - KOTAK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">POLE SUPORTER </t>
+  </si>
+  <si>
+    <t>GALVANIZED STEEL WIRE 70 MM - HDG</t>
+  </si>
+  <si>
+    <t>GUY INSULATOR MV (TM) - BELIMBING</t>
+  </si>
+  <si>
+    <t>GUY WIRE ROD 5/8" (15 MM) - 2.500 MM - TM</t>
+  </si>
+  <si>
+    <t>PIPA GALVANIZED 3/4" - 2 M (TEBAL= 1,6 MM) U/PIPA PELINDUNG</t>
+  </si>
+  <si>
+    <t>PREFORMED TERMINATION 70 MM (542/U/2009)</t>
+  </si>
+  <si>
+    <t>SINGLE GUY WIRE BAND 8" - (T = 6 MM X 42 MM) HDG TM LENGKAP NUT-HDG</t>
+  </si>
+  <si>
+    <t>STRUT ARM TM - (L=50 MM, T=5 MM, TGG=100 MM) NP 10 - 30 CM</t>
+  </si>
+  <si>
+    <t>STRUT TIE 2000 - PIPE 2" - 2,0 M, TEBAL 2,0 MM - TM</t>
+  </si>
+  <si>
+    <t>TURN BUCKLE TM 3/4" (7000 KG) - TM - (L=42 MM, T=6 MM)</t>
+  </si>
+  <si>
+    <t>U - BOLT + STEEL PLATE TM/TR BOLT M.18 + 2 NUT</t>
+  </si>
+  <si>
+    <t>WIRE CLIP M12 (70 MM)</t>
+  </si>
+  <si>
+    <t>PONDASI TYPE A (1 TIANG) (91/U/2009)</t>
+  </si>
+  <si>
+    <t>PONDASI TYPE A - TIANG JTM)</t>
+  </si>
+  <si>
+    <t>PONDASI TYPE B</t>
+  </si>
+  <si>
+    <t>TIANG BESI 11 METER</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TIANG TM </t>
+  </si>
+  <si>
+    <t>TIANG BESI 13 METER</t>
+  </si>
+  <si>
+    <t>TIANG BESI 14 METER</t>
+  </si>
+  <si>
+    <t>TIANG BETON 14 METER - 350 DAN</t>
+  </si>
+  <si>
+    <t>TIANG BETON 13 METER - 350 DAN</t>
+  </si>
+  <si>
+    <t>TIANG BETON 11 METER - 200 DAN</t>
+  </si>
+  <si>
+    <t>PIPA GALVANIZED 4" - 4 M (MEDIUM 3,2 MM) + PLAT GW CLAMP TYPE A</t>
+  </si>
+  <si>
+    <t>VERLENK STUCK JARINGAN  SUTM / SKUTM</t>
+  </si>
+  <si>
+    <t>PIPA GALVANIZED 4" - 3 M (MEDIUM 3,2 MM) + PLAT GW CLAMP TYPE B</t>
+  </si>
+  <si>
+    <t>PIPA GALVANIZED 4" - 3 M (MEDIUM 3,2 MM) + PLAT GW CLAMP TYPE C</t>
+  </si>
+  <si>
+    <t>ORNAMENT CABEL BAND 4" - 3 U/FERLENGK - (L=42 MM, T=6 MM) LENGKAP BOLT&amp;NUT-HDG</t>
+  </si>
+  <si>
+    <t>ORNAMENT CABEL BAND 4" X 7" - TM LENGKAP BOLT&amp;NUT-HDG</t>
+  </si>
+  <si>
+    <t>VERLENK STUCK STEEL WIRE</t>
+  </si>
+  <si>
+    <t>ORNAMENT CABEL BAND 3" X 8" - TM LENGKAP BOLT&amp;NUT-HDG</t>
+  </si>
+  <si>
+    <t>SINGLE GUY WIRE BAND 3" - (T = 6 MM X 42 MM) HDG TM LENGKAP NUT-HDG</t>
+  </si>
+  <si>
+    <t>SKUTM</t>
+  </si>
+  <si>
+    <t>BOLT &amp; NUT M.14 X 30 - HDG</t>
+  </si>
+  <si>
+    <t>ARRESTER &amp; ACCESORIES KABEL</t>
+  </si>
+  <si>
+    <t>CABLE PWR;NFA2XSY-T;3X150+1X95;20KV;OH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CONDUCTOR ACCESSORIES </t>
+  </si>
+  <si>
+    <t>CABLE PWR;NFA2XSY-T;3X240+1X95;20KV;OH</t>
+  </si>
+  <si>
+    <t>BESI SIKU L 50X50X3,5 MM X 900 MM - DUDUKAN JOINTING</t>
+  </si>
+  <si>
+    <t>DUDUKAN JOINTING</t>
+  </si>
+  <si>
+    <t>CROSS ARM UNP 100 - 750 MM - (L=50 MM, T=5 MM, TGG=100 MM)</t>
+  </si>
+  <si>
+    <t>GROUNDING KABEL + LA</t>
+  </si>
+  <si>
+    <t>BC 50 MM (BARE CONDUCTOR)</t>
+  </si>
+  <si>
+    <t>ACCESORIES :</t>
+  </si>
+  <si>
+    <t>GROUNDING TERMINATION</t>
+  </si>
+  <si>
+    <t>PIPA GALVANIZED 3/4" - 3 M (TEBAL= 1,6 MM)</t>
+  </si>
+  <si>
+    <t>KONTRUKSI MVTIC - 1  (LURUS)</t>
+  </si>
+  <si>
+    <t>COND ACC; EXT GROUND WIRE TYPE A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PLASTIC STRAP </t>
+  </si>
+  <si>
+    <t>SEPARATOR CLAMP FOR NETRAL - (ACC.MVTIC)</t>
+  </si>
+  <si>
+    <t>SINGLE GUY WIRE BAND 9" - (T = 6 MM X 42 MM) HDG TM LENGKAP NUT-HDG</t>
+  </si>
+  <si>
+    <t>KONTRUKSI MVTIC - 10</t>
+  </si>
+  <si>
+    <t>COND ACC; EXT GROUND WIRE TYPE B</t>
+  </si>
+  <si>
+    <t>STRINGSET ACC;STRAIN CLAMP 150-240MM2</t>
+  </si>
+  <si>
+    <t>KONTRUKSI MVTIC - 2 (SUDUT &gt;150)</t>
+  </si>
+  <si>
+    <t>KONTRUKSI MVTIC - 3 (POSISI GTT 2 T HARUS ADA SPELING LEBIH )</t>
+  </si>
+  <si>
+    <t>KONTRUKSI MVTIC - 4  (AKHIR)</t>
+  </si>
+  <si>
+    <t>BEGEL 2" U - (T = 6 MM X 42 MM) HDG TM LENGKAP BOLT&amp;NUT-HDG</t>
+  </si>
+  <si>
+    <t>WASHER 45 X 45 X 3,5 - HDG</t>
+  </si>
+  <si>
+    <t>KONTRUKSI MVTIC - 5  (JUMPER ATAS)</t>
+  </si>
+  <si>
+    <t>KONTRUKSI MVTIC - 5A (JOINTING)</t>
+  </si>
+  <si>
+    <t>CONNECTION CLAMP FOR NETRAL + BOLT M12 X 25 - (ACC. MVTIC)</t>
+  </si>
+  <si>
+    <t>PERLENGKAPAN PENGGANTUNG</t>
+  </si>
+  <si>
+    <t>POLE ACC;CONNECTION CLAMP NETRAL 35MM2</t>
+  </si>
+  <si>
+    <t>POLE SUPORTER</t>
+  </si>
+  <si>
+    <t>AAAC - S 70 SQ MM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TERMINATION </t>
+  </si>
+  <si>
+    <t>LLC 150-240</t>
+  </si>
+  <si>
+    <t>TERMINATION OUTDOOR 24 KV - UK. 150  MM - 1 CORE/MVTIC</t>
+  </si>
+  <si>
+    <t>ACCESORIES SPELLING + JUMPER :</t>
+  </si>
+  <si>
+    <t>CROSS ARM UNP 80 - 2000 (L=42 MM,T=3,5 MM,TGG=80 MM)</t>
+  </si>
+  <si>
+    <t>ORNAMENT CABEL BAND 4" X 10" - TM LENGKAP BOLT&amp;NUT-HDG</t>
+  </si>
+  <si>
+    <t>COMPRESION JOINT SLEEVE NON TENSION 95 MM - AL</t>
+  </si>
+  <si>
+    <t>TERMINATION JOINTING</t>
+  </si>
+  <si>
+    <t>JOINTING TERMINATION 24 KV - UK. 150 MM - 1 CORE/MVTIC</t>
+  </si>
+  <si>
+    <t>TIANG BETON</t>
+  </si>
+  <si>
+    <t>TIANG BETON 9 METER - 200 DAN</t>
   </si>
 </sst>
 </file>
@@ -260,8 +597,7 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="16"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
@@ -885,7 +1221,7 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -893,12 +1229,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="distributed"/>
     </xf>
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="52">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -954,7 +1292,17 @@
     <cellStyle name="Normal 23" xfId="50"/>
     <cellStyle name="Normal_rab-sdp-kabel1" xfId="51"/>
   </cellStyles>
-  <dxfs count="17">
+  <dxfs count="18">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -1148,25 +1496,25 @@
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
     <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
-      <tableStyleElement type="wholeTable" dxfId="6"/>
-      <tableStyleElement type="headerRow" dxfId="5"/>
-      <tableStyleElement type="totalRow" dxfId="4"/>
-      <tableStyleElement type="firstColumn" dxfId="3"/>
-      <tableStyleElement type="lastColumn" dxfId="2"/>
-      <tableStyleElement type="firstRowStripe" dxfId="1"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
+      <tableStyleElement type="wholeTable" dxfId="7"/>
+      <tableStyleElement type="headerRow" dxfId="6"/>
+      <tableStyleElement type="totalRow" dxfId="5"/>
+      <tableStyleElement type="firstColumn" dxfId="4"/>
+      <tableStyleElement type="lastColumn" dxfId="3"/>
+      <tableStyleElement type="firstRowStripe" dxfId="2"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="1"/>
     </tableStyle>
     <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
-      <tableStyleElement type="headerRow" dxfId="16"/>
-      <tableStyleElement type="totalRow" dxfId="15"/>
-      <tableStyleElement type="firstRowStripe" dxfId="14"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
-      <tableStyleElement type="pageFieldValues" dxfId="7"/>
+      <tableStyleElement type="headerRow" dxfId="17"/>
+      <tableStyleElement type="totalRow" dxfId="16"/>
+      <tableStyleElement type="firstRowStripe" dxfId="15"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="14"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="13"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="12"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="11"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="10"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="9"/>
+      <tableStyleElement type="pageFieldValues" dxfId="8"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -1175,6 +1523,51 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="SUTM"/>
+      <sheetName val="SKUTM"/>
+      <sheetName val="SKTM"/>
+      <sheetName val="GTT 1 TIANG"/>
+      <sheetName val="GTT 2 TIANG"/>
+      <sheetName val="FOOTKLEM"/>
+      <sheetName val="APP TR (53-197 kVA)"/>
+      <sheetName val="APP TR ( 23-41,5kVA)"/>
+      <sheetName val="APP TR (6,6-16,2 kVA)"/>
+      <sheetName val="SUTR"/>
+      <sheetName val="KUBIKEL"/>
+      <sheetName val="GARDU KONVEN"/>
+      <sheetName val="SKTR &amp; SKSR"/>
+      <sheetName val="COMMISIONING"/>
+      <sheetName val="SAFETY COST"/>
+      <sheetName val="MATERIAL TAMBAHAN"/>
+      <sheetName val="RESUM  KR 037"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+      <sheetData sheetId="8"/>
+      <sheetData sheetId="9"/>
+      <sheetData sheetId="10"/>
+      <sheetData sheetId="11"/>
+      <sheetData sheetId="12"/>
+      <sheetData sheetId="13"/>
+      <sheetData sheetId="14"/>
+      <sheetData sheetId="15"/>
+      <sheetData sheetId="16"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1427,852 +1820,8229 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H62"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="20" customHeight="1" outlineLevelCol="7"/>
+  <dimension ref="A1:J459"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="20" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="4.42857142857143" style="1" customWidth="1"/>
-    <col min="2" max="2" width="82" style="1" customWidth="1"/>
-    <col min="3" max="3" width="19" style="1" customWidth="1"/>
-    <col min="4" max="4" width="17.4285714285714" style="1" customWidth="1"/>
+    <col min="2" max="2" width="21.7142857142857" style="1" customWidth="1"/>
+    <col min="3" max="3" width="52.8571428571429" style="1" customWidth="1"/>
+    <col min="4" max="4" width="36.247619047619" style="1" customWidth="1"/>
     <col min="5" max="5" width="19" style="1" customWidth="1"/>
-    <col min="8" max="8" width="16.8571428571429" style="1" customWidth="1"/>
+    <col min="6" max="6" width="17.4285714285714" style="1" customWidth="1"/>
+    <col min="7" max="7" width="19" style="1" customWidth="1"/>
+    <col min="10" max="10" width="16.8571428571429" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customHeight="1" spans="1:5">
+    <row r="1" customHeight="1" spans="1:7">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" customHeight="1" spans="1:5">
+    <row r="2" customHeight="1" spans="1:7">
       <c r="A2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" customHeight="1" spans="1:5">
+    <row r="3" customHeight="1" spans="1:7">
       <c r="A3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" customHeight="1" spans="1:5">
+    <row r="4" customHeight="1" spans="1:7">
       <c r="A4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" customHeight="1" spans="1:5">
+    <row r="6" customHeight="1" spans="1:7">
       <c r="A6" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="3" t="s">
         <v>7</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="7" customHeight="1" spans="1:5">
+      <c r="F6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" customHeight="1" spans="1:7">
       <c r="A7" s="2">
         <v>1</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
+      <c r="B7" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>13</v>
+      </c>
       <c r="E7" s="2"/>
-    </row>
-    <row r="8" customHeight="1" spans="1:5">
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
+    </row>
+    <row r="8" customHeight="1" spans="1:7">
       <c r="A8" s="2">
         <f t="shared" ref="A8:A62" si="0">A7+1</f>
         <v>2</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
+      <c r="B8" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>13</v>
+      </c>
       <c r="E8" s="2"/>
-    </row>
-    <row r="9" customHeight="1" spans="1:5">
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+    </row>
+    <row r="9" customHeight="1" spans="1:7">
       <c r="A9" s="2">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
+      <c r="B9" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>13</v>
+      </c>
       <c r="E9" s="2"/>
-    </row>
-    <row r="10" customHeight="1" spans="1:5">
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
+    </row>
+    <row r="10" customHeight="1" spans="1:7">
       <c r="A10" s="2">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
+      <c r="B10" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>13</v>
+      </c>
       <c r="E10" s="2"/>
-    </row>
-    <row r="11" customHeight="1" spans="1:5">
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
+    </row>
+    <row r="11" customHeight="1" spans="1:7">
       <c r="A11" s="2">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D11" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
       <c r="E11" s="2"/>
-    </row>
-    <row r="12" customHeight="1" spans="1:5">
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+    </row>
+    <row r="12" customHeight="1" spans="1:7">
       <c r="A12" s="2">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
+      <c r="B12" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>13</v>
+      </c>
       <c r="E12" s="2"/>
-    </row>
-    <row r="13" customHeight="1" spans="1:5">
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+    </row>
+    <row r="13" customHeight="1" spans="1:7">
       <c r="A13" s="2">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
+      <c r="B13" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>13</v>
+      </c>
       <c r="E13" s="2"/>
-    </row>
-    <row r="14" customHeight="1" spans="1:5">
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
+    </row>
+    <row r="14" customHeight="1" spans="1:7">
       <c r="A14" s="2">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="B14" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
+      <c r="B14" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>21</v>
+      </c>
       <c r="E14" s="2"/>
-    </row>
-    <row r="15" customHeight="1" spans="1:5">
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
+    </row>
+    <row r="15" customHeight="1" spans="1:7">
       <c r="A15" s="2">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
+      <c r="B15" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>21</v>
+      </c>
       <c r="E15" s="2"/>
-    </row>
-    <row r="16" customHeight="1" spans="1:5">
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
+    </row>
+    <row r="16" customHeight="1" spans="1:7">
       <c r="A16" s="2">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="B16" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2"/>
+      <c r="B16" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>21</v>
+      </c>
       <c r="E16" s="2"/>
-    </row>
-    <row r="17" customHeight="1" spans="1:5">
+      <c r="F16" s="2"/>
+      <c r="G16" s="2"/>
+    </row>
+    <row r="17" customHeight="1" spans="1:7">
       <c r="A17" s="2">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="B17" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2"/>
+      <c r="B17" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>21</v>
+      </c>
       <c r="E17" s="2"/>
-    </row>
-    <row r="18" customHeight="1" spans="1:5">
+      <c r="F17" s="2"/>
+      <c r="G17" s="2"/>
+    </row>
+    <row r="18" customHeight="1" spans="1:7">
       <c r="A18" s="2">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="B18" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2"/>
+      <c r="B18" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>21</v>
+      </c>
       <c r="E18" s="2"/>
-    </row>
-    <row r="19" customHeight="1" spans="1:5">
+      <c r="F18" s="2"/>
+      <c r="G18" s="2"/>
+    </row>
+    <row r="19" customHeight="1" spans="1:7">
       <c r="A19" s="2">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="B19" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C19" s="2"/>
-      <c r="D19" s="2"/>
+      <c r="B19" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>21</v>
+      </c>
       <c r="E19" s="2"/>
-    </row>
-    <row r="20" customHeight="1" spans="1:5">
+      <c r="F19" s="2"/>
+      <c r="G19" s="2"/>
+    </row>
+    <row r="20" customHeight="1" spans="1:7">
       <c r="A20" s="2">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="B20" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D20" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="C20" s="2"/>
-      <c r="D20" s="2"/>
       <c r="E20" s="2"/>
-    </row>
-    <row r="21" customHeight="1" spans="1:5">
+      <c r="F20" s="2"/>
+      <c r="G20" s="2"/>
+    </row>
+    <row r="21" customHeight="1" spans="1:7">
       <c r="A21" s="2">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="B21" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C21" s="2"/>
-      <c r="D21" s="2"/>
+      <c r="B21" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>21</v>
+      </c>
       <c r="E21" s="2"/>
-    </row>
-    <row r="22" customHeight="1" spans="1:5">
+      <c r="F21" s="2"/>
+      <c r="G21" s="2"/>
+    </row>
+    <row r="22" customHeight="1" spans="1:7">
       <c r="A22" s="2">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="B22" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C22" s="2"/>
-      <c r="D22" s="2"/>
+      <c r="B22" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>21</v>
+      </c>
       <c r="E22" s="2"/>
-    </row>
-    <row r="23" customHeight="1" spans="1:5">
+      <c r="F22" s="2"/>
+      <c r="G22" s="2"/>
+    </row>
+    <row r="23" customHeight="1" spans="1:7">
       <c r="A23" s="2">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="B23" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C23" s="2"/>
-      <c r="D23" s="2"/>
+      <c r="B23" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>21</v>
+      </c>
       <c r="E23" s="2"/>
-    </row>
-    <row r="24" customHeight="1" spans="1:5">
+      <c r="F23" s="2"/>
+      <c r="G23" s="2"/>
+    </row>
+    <row r="24" customHeight="1" spans="1:7">
       <c r="A24" s="2">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="B24" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C24" s="2"/>
-      <c r="D24" s="2"/>
+      <c r="B24" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>21</v>
+      </c>
       <c r="E24" s="2"/>
-    </row>
-    <row r="25" customHeight="1" spans="1:5">
+      <c r="F24" s="2"/>
+      <c r="G24" s="2"/>
+    </row>
+    <row r="25" customHeight="1" spans="1:7">
       <c r="A25" s="2">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="B25" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C25" s="2"/>
-      <c r="D25" s="2"/>
+      <c r="B25" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>21</v>
+      </c>
       <c r="E25" s="2"/>
-    </row>
-    <row r="26" customHeight="1" spans="1:5">
+      <c r="F25" s="2"/>
+      <c r="G25" s="2"/>
+    </row>
+    <row r="26" customHeight="1" spans="1:7">
       <c r="A26" s="2">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="B26" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C26" s="2"/>
-      <c r="D26" s="2"/>
+      <c r="B26" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>21</v>
+      </c>
       <c r="E26" s="2"/>
-    </row>
-    <row r="27" customHeight="1" spans="1:5">
+      <c r="F26" s="2"/>
+      <c r="G26" s="2"/>
+    </row>
+    <row r="27" customHeight="1" spans="1:7">
       <c r="A27" s="2">
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="B27" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C27" s="2"/>
-      <c r="D27" s="2"/>
+      <c r="B27" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>21</v>
+      </c>
       <c r="E27" s="2"/>
-    </row>
-    <row r="28" customHeight="1" spans="1:5">
+      <c r="F27" s="2"/>
+      <c r="G27" s="2"/>
+    </row>
+    <row r="28" customHeight="1" spans="1:7">
       <c r="A28" s="2">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="B28" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C28" s="2"/>
-      <c r="D28" s="2"/>
+      <c r="B28" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>21</v>
+      </c>
       <c r="E28" s="2"/>
-    </row>
-    <row r="29" customHeight="1" spans="1:5">
+      <c r="F28" s="2"/>
+      <c r="G28" s="2"/>
+    </row>
+    <row r="29" customHeight="1" spans="1:7">
       <c r="A29" s="2">
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
-      <c r="B29" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C29" s="2"/>
-      <c r="D29" s="2"/>
+      <c r="B29" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="E29" s="2"/>
-    </row>
-    <row r="30" customHeight="1" spans="1:5">
+      <c r="F29" s="2"/>
+      <c r="G29" s="2"/>
+    </row>
+    <row r="30" customHeight="1" spans="1:7">
       <c r="A30" s="2">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="B30" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="C30" s="2"/>
-      <c r="D30" s="2"/>
+      <c r="B30" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="E30" s="2"/>
-    </row>
-    <row r="31" customHeight="1" spans="1:5">
+      <c r="F30" s="2"/>
+      <c r="G30" s="2"/>
+    </row>
+    <row r="31" customHeight="1" spans="1:7">
       <c r="A31" s="2">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="B31" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="C31" s="2"/>
-      <c r="D31" s="2"/>
+      <c r="B31" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="E31" s="2"/>
-    </row>
-    <row r="32" customHeight="1" spans="1:5">
+      <c r="F31" s="2"/>
+      <c r="G31" s="2"/>
+    </row>
+    <row r="32" customHeight="1" spans="1:7">
       <c r="A32" s="2">
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="B32" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="C32" s="2"/>
-      <c r="D32" s="2"/>
+      <c r="B32" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="E32" s="2"/>
-    </row>
-    <row r="33" customHeight="1" spans="1:5">
+      <c r="F32" s="2"/>
+      <c r="G32" s="2"/>
+    </row>
+    <row r="33" customHeight="1" spans="1:7">
       <c r="A33" s="2">
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
-      <c r="B33" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C33" s="2"/>
-      <c r="D33" s="2"/>
+      <c r="B33" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="E33" s="2"/>
-    </row>
-    <row r="34" customHeight="1" spans="1:5">
+      <c r="F33" s="2"/>
+      <c r="G33" s="2"/>
+    </row>
+    <row r="34" customHeight="1" spans="1:7">
       <c r="A34" s="2">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
-      <c r="B34" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C34" s="2"/>
-      <c r="D34" s="2"/>
+      <c r="B34" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="E34" s="2"/>
-    </row>
-    <row r="35" customHeight="1" spans="1:5">
+      <c r="F34" s="2"/>
+      <c r="G34" s="2"/>
+    </row>
+    <row r="35" customHeight="1" spans="1:7">
       <c r="A35" s="2">
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
-      <c r="B35" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C35" s="2"/>
-      <c r="D35" s="2"/>
+      <c r="B35" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>37</v>
+      </c>
       <c r="E35" s="2"/>
-    </row>
-    <row r="36" customHeight="1" spans="1:5">
+      <c r="F35" s="2"/>
+      <c r="G35" s="2"/>
+    </row>
+    <row r="36" customHeight="1" spans="1:7">
       <c r="A36" s="2">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
-      <c r="B36" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C36" s="2"/>
-      <c r="D36" s="2"/>
+      <c r="B36" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="D36" s="4" t="s">
+        <v>37</v>
+      </c>
       <c r="E36" s="2"/>
-    </row>
-    <row r="37" customHeight="1" spans="1:5">
+      <c r="F36" s="2"/>
+      <c r="G36" s="2"/>
+    </row>
+    <row r="37" customHeight="1" spans="1:7">
       <c r="A37" s="2">
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
-      <c r="B37" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C37" s="2"/>
-      <c r="D37" s="2"/>
+      <c r="B37" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="D37" s="4" t="s">
+        <v>37</v>
+      </c>
       <c r="E37" s="2"/>
-    </row>
-    <row r="38" customHeight="1" spans="1:5">
+      <c r="F37" s="2"/>
+      <c r="G37" s="2"/>
+    </row>
+    <row r="38" customHeight="1" spans="1:7">
       <c r="A38" s="2">
         <f t="shared" si="0"/>
         <v>32</v>
       </c>
-      <c r="B38" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C38" s="2"/>
-      <c r="D38" s="2"/>
+      <c r="B38" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="D38" s="4" t="s">
+        <v>37</v>
+      </c>
       <c r="E38" s="2"/>
-    </row>
-    <row r="39" customHeight="1" spans="1:5">
+      <c r="F38" s="2"/>
+      <c r="G38" s="2"/>
+    </row>
+    <row r="39" customHeight="1" spans="1:7">
       <c r="A39" s="2">
         <f t="shared" si="0"/>
         <v>33</v>
       </c>
-      <c r="B39" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C39" s="2"/>
-      <c r="D39" s="2"/>
+      <c r="B39" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="D39" s="4" t="s">
+        <v>37</v>
+      </c>
       <c r="E39" s="2"/>
-    </row>
-    <row r="40" customHeight="1" spans="1:5">
+      <c r="F39" s="2"/>
+      <c r="G39" s="2"/>
+    </row>
+    <row r="40" customHeight="1" spans="1:7">
       <c r="A40" s="2">
         <f t="shared" si="0"/>
         <v>34</v>
       </c>
-      <c r="B40" s="2" t="s">
+      <c r="B40" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D40" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="C40" s="2"/>
-      <c r="D40" s="2"/>
       <c r="E40" s="2"/>
-    </row>
-    <row r="41" customHeight="1" spans="1:5">
+      <c r="F40" s="2"/>
+      <c r="G40" s="2"/>
+    </row>
+    <row r="41" customHeight="1" spans="1:7">
       <c r="A41" s="2">
         <f t="shared" si="0"/>
         <v>35</v>
       </c>
-      <c r="B41" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C41" s="2"/>
-      <c r="D41" s="2"/>
+      <c r="B41" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D41" s="4" t="s">
+        <v>37</v>
+      </c>
       <c r="E41" s="2"/>
-    </row>
-    <row r="42" customHeight="1" spans="1:5">
+      <c r="F41" s="2"/>
+      <c r="G41" s="2"/>
+    </row>
+    <row r="42" customHeight="1" spans="1:7">
       <c r="A42" s="2">
         <f t="shared" si="0"/>
         <v>36</v>
       </c>
-      <c r="B42" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C42" s="2"/>
-      <c r="D42" s="2"/>
+      <c r="B42" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="D42" s="4" t="s">
+        <v>44</v>
+      </c>
       <c r="E42" s="2"/>
-    </row>
-    <row r="43" customHeight="1" spans="1:5">
+      <c r="F42" s="2"/>
+      <c r="G42" s="2"/>
+    </row>
+    <row r="43" customHeight="1" spans="1:7">
       <c r="A43" s="2">
         <f t="shared" si="0"/>
         <v>37</v>
       </c>
-      <c r="B43" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C43" s="2"/>
-      <c r="D43" s="2"/>
+      <c r="B43" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D43" s="4" t="s">
+        <v>44</v>
+      </c>
       <c r="E43" s="2"/>
-    </row>
-    <row r="44" customHeight="1" spans="1:5">
+      <c r="F43" s="2"/>
+      <c r="G43" s="2"/>
+    </row>
+    <row r="44" customHeight="1" spans="1:7">
       <c r="A44" s="2">
         <f t="shared" si="0"/>
         <v>38</v>
       </c>
-      <c r="B44" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="C44" s="2"/>
-      <c r="D44" s="2"/>
+      <c r="B44" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="D44" s="4" t="s">
+        <v>44</v>
+      </c>
       <c r="E44" s="2"/>
-    </row>
-    <row r="45" customHeight="1" spans="1:5">
+      <c r="F44" s="2"/>
+      <c r="G44" s="2"/>
+    </row>
+    <row r="45" customHeight="1" spans="1:7">
       <c r="A45" s="2">
         <f t="shared" si="0"/>
         <v>39</v>
       </c>
-      <c r="B45" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C45" s="2"/>
-      <c r="D45" s="2"/>
+      <c r="B45" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="D45" s="4" t="s">
+        <v>44</v>
+      </c>
       <c r="E45" s="2"/>
-    </row>
-    <row r="46" customHeight="1" spans="1:5">
+      <c r="F45" s="2"/>
+      <c r="G45" s="2"/>
+    </row>
+    <row r="46" customHeight="1" spans="1:7">
       <c r="A46" s="2">
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
-      <c r="B46" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C46" s="2"/>
-      <c r="D46" s="2"/>
+      <c r="B46" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D46" s="4" t="s">
+        <v>44</v>
+      </c>
       <c r="E46" s="2"/>
-    </row>
-    <row r="47" customHeight="1" spans="1:5">
+      <c r="F46" s="2"/>
+      <c r="G46" s="2"/>
+    </row>
+    <row r="47" customHeight="1" spans="1:7">
       <c r="A47" s="2">
         <f t="shared" si="0"/>
         <v>41</v>
       </c>
-      <c r="B47" s="2" t="s">
+      <c r="B47" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="D47" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="C47" s="2"/>
-      <c r="D47" s="2"/>
       <c r="E47" s="2"/>
-    </row>
-    <row r="48" customHeight="1" spans="1:5">
+      <c r="F47" s="2"/>
+      <c r="G47" s="2"/>
+    </row>
+    <row r="48" customHeight="1" spans="1:7">
       <c r="A48" s="2">
         <f t="shared" si="0"/>
         <v>42</v>
       </c>
-      <c r="B48" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="C48" s="2"/>
-      <c r="D48" s="2"/>
+      <c r="B48" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="D48" s="4" t="s">
+        <v>44</v>
+      </c>
       <c r="E48" s="2"/>
-    </row>
-    <row r="49" customHeight="1" spans="1:8">
+      <c r="F48" s="2"/>
+      <c r="G48" s="2"/>
+    </row>
+    <row r="49" customHeight="1" spans="1:10">
       <c r="A49" s="2">
         <f t="shared" si="0"/>
         <v>43</v>
       </c>
-      <c r="B49" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="C49" s="2"/>
-      <c r="D49" s="2"/>
+      <c r="B49" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D49" s="4" t="s">
+        <v>44</v>
+      </c>
       <c r="E49" s="2"/>
-      <c r="H49" s="4">
+      <c r="F49" s="2"/>
+      <c r="G49" s="2"/>
+      <c r="J49" s="5">
         <f>150*17700</f>
         <v>2655000</v>
       </c>
     </row>
-    <row r="50" customHeight="1" spans="1:8">
+    <row r="50" customHeight="1" spans="1:10">
       <c r="A50" s="2">
         <f t="shared" si="0"/>
         <v>44</v>
       </c>
-      <c r="B50" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C50" s="2"/>
-      <c r="D50" s="2"/>
+      <c r="B50" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D50" s="4" t="s">
+        <v>44</v>
+      </c>
       <c r="E50" s="2"/>
-    </row>
-    <row r="51" customHeight="1" spans="1:8">
+      <c r="F50" s="2"/>
+      <c r="G50" s="2"/>
+    </row>
+    <row r="51" customHeight="1" spans="1:10">
       <c r="A51" s="2">
         <f t="shared" si="0"/>
         <v>45</v>
       </c>
-      <c r="B51" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C51" s="2"/>
-      <c r="D51" s="2"/>
+      <c r="B51" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C51" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D51" s="4" t="s">
+        <v>44</v>
+      </c>
       <c r="E51" s="2"/>
-    </row>
-    <row r="52" customHeight="1" spans="1:8">
+      <c r="F51" s="2"/>
+      <c r="G51" s="2"/>
+    </row>
+    <row r="52" customHeight="1" spans="1:10">
       <c r="A52" s="2">
         <f t="shared" si="0"/>
         <v>46</v>
       </c>
-      <c r="B52" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="C52" s="2"/>
-      <c r="D52" s="2"/>
+      <c r="B52" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C52" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="D52" s="4" t="s">
+        <v>44</v>
+      </c>
       <c r="E52" s="2"/>
-    </row>
-    <row r="53" customHeight="1" spans="1:8">
+      <c r="F52" s="2"/>
+      <c r="G52" s="2"/>
+    </row>
+    <row r="53" customHeight="1" spans="1:10">
       <c r="A53" s="2">
         <f t="shared" si="0"/>
         <v>47</v>
       </c>
-      <c r="B53" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="C53" s="2"/>
-      <c r="D53" s="2"/>
+      <c r="B53" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C53" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="D53" s="4" t="s">
+        <v>44</v>
+      </c>
       <c r="E53" s="2"/>
-    </row>
-    <row r="54" customHeight="1" spans="1:8">
+      <c r="F53" s="2"/>
+      <c r="G53" s="2"/>
+    </row>
+    <row r="54" customHeight="1" spans="1:10">
       <c r="A54" s="2">
         <f t="shared" si="0"/>
         <v>48</v>
       </c>
-      <c r="B54" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="C54" s="2"/>
-      <c r="D54" s="2"/>
+      <c r="B54" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C54" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="D54" s="4" t="s">
+        <v>54</v>
+      </c>
       <c r="E54" s="2"/>
-    </row>
-    <row r="55" customHeight="1" spans="1:8">
+      <c r="F54" s="2"/>
+      <c r="G54" s="2"/>
+    </row>
+    <row r="55" customHeight="1" spans="1:10">
       <c r="A55" s="2">
         <f t="shared" si="0"/>
         <v>49</v>
       </c>
-      <c r="B55" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="C55" s="2"/>
-      <c r="D55" s="2"/>
+      <c r="B55" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C55" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D55" s="4" t="s">
+        <v>54</v>
+      </c>
       <c r="E55" s="2"/>
-    </row>
-    <row r="56" customHeight="1" spans="1:8">
+      <c r="F55" s="2"/>
+      <c r="G55" s="2"/>
+    </row>
+    <row r="56" customHeight="1" spans="1:10">
       <c r="A56" s="2">
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
-      <c r="B56" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="C56" s="2"/>
-      <c r="D56" s="2"/>
+      <c r="B56" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C56" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D56" s="4" t="s">
+        <v>54</v>
+      </c>
       <c r="E56" s="2"/>
-    </row>
-    <row r="57" customHeight="1" spans="1:8">
+      <c r="F56" s="2"/>
+      <c r="G56" s="2"/>
+    </row>
+    <row r="57" customHeight="1" spans="1:10">
       <c r="A57" s="2">
         <f t="shared" si="0"/>
         <v>51</v>
       </c>
-      <c r="B57" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="C57" s="2"/>
-      <c r="D57" s="2"/>
+      <c r="B57" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C57" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="D57" s="4" t="s">
+        <v>54</v>
+      </c>
       <c r="E57" s="2"/>
-    </row>
-    <row r="58" customHeight="1" spans="1:8">
+      <c r="F57" s="2"/>
+      <c r="G57" s="2"/>
+    </row>
+    <row r="58" customHeight="1" spans="1:10">
       <c r="A58" s="2">
         <f t="shared" si="0"/>
         <v>52</v>
       </c>
-      <c r="B58" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C58" s="2"/>
-      <c r="D58" s="2"/>
+      <c r="B58" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C58" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D58" s="4" t="s">
+        <v>54</v>
+      </c>
       <c r="E58" s="2"/>
-    </row>
-    <row r="59" customHeight="1" spans="1:8">
+      <c r="F58" s="2"/>
+      <c r="G58" s="2"/>
+    </row>
+    <row r="59" customHeight="1" spans="1:10">
       <c r="A59" s="2">
         <f t="shared" si="0"/>
         <v>53</v>
       </c>
-      <c r="B59" s="2" t="s">
+      <c r="B59" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C59" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D59" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="C59" s="2"/>
-      <c r="D59" s="2"/>
       <c r="E59" s="2"/>
-    </row>
-    <row r="60" customHeight="1" spans="1:8">
+      <c r="F59" s="2"/>
+      <c r="G59" s="2"/>
+    </row>
+    <row r="60" customHeight="1" spans="1:10">
       <c r="A60" s="2">
         <f t="shared" si="0"/>
         <v>54</v>
       </c>
-      <c r="B60" s="2" t="s">
+      <c r="B60" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C60" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D60" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="C60" s="2"/>
-      <c r="D60" s="2"/>
       <c r="E60" s="2"/>
-    </row>
-    <row r="61" customHeight="1" spans="1:8">
+      <c r="F60" s="2"/>
+      <c r="G60" s="2"/>
+    </row>
+    <row r="61" customHeight="1" spans="1:10">
       <c r="A61" s="2">
         <f t="shared" si="0"/>
         <v>55</v>
       </c>
-      <c r="B61" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="C61" s="2"/>
-      <c r="D61" s="2"/>
+      <c r="B61" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C61" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="D61" s="4" t="s">
+        <v>54</v>
+      </c>
       <c r="E61" s="2"/>
-    </row>
-    <row r="62" customHeight="1" spans="1:8">
+      <c r="F61" s="2"/>
+      <c r="G61" s="2"/>
+    </row>
+    <row r="62" customHeight="1" spans="1:10">
       <c r="A62" s="2">
         <f t="shared" si="0"/>
         <v>56</v>
       </c>
-      <c r="B62" s="2" t="s">
+      <c r="B62" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C62" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="D62" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="E62" s="2"/>
+      <c r="F62" s="2"/>
+      <c r="G62" s="2"/>
+    </row>
+    <row r="63" customHeight="1" spans="1:10">
+      <c r="A63" s="2">
+        <f t="shared" ref="A63:A126" si="1">A62+1</f>
+        <v>57</v>
+      </c>
+      <c r="B63" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C63" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D63" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="E63" s="6"/>
+      <c r="F63" s="6"/>
+      <c r="G63" s="6"/>
+    </row>
+    <row r="64" customHeight="1" spans="1:10">
+      <c r="A64" s="2">
+        <f t="shared" si="1"/>
+        <v>58</v>
+      </c>
+      <c r="B64" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C64" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D64" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="E64" s="6"/>
+      <c r="F64" s="6"/>
+      <c r="G64" s="6"/>
+    </row>
+    <row r="65" customHeight="1" spans="1:7">
+      <c r="A65" s="2">
+        <f t="shared" si="1"/>
+        <v>59</v>
+      </c>
+      <c r="B65" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C65" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="D65" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="E65" s="6"/>
+      <c r="F65" s="6"/>
+      <c r="G65" s="6"/>
+    </row>
+    <row r="66" customHeight="1" spans="1:7">
+      <c r="A66" s="2">
+        <f t="shared" si="1"/>
+        <v>60</v>
+      </c>
+      <c r="B66" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C66" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="D66" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="E66" s="6"/>
+      <c r="F66" s="6"/>
+      <c r="G66" s="6"/>
+    </row>
+    <row r="67" customHeight="1" spans="1:7">
+      <c r="A67" s="2">
+        <f t="shared" si="1"/>
+        <v>61</v>
+      </c>
+      <c r="B67" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C67" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="D67" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="E67" s="6"/>
+      <c r="F67" s="6"/>
+      <c r="G67" s="6"/>
+    </row>
+    <row r="68" customHeight="1" spans="1:7">
+      <c r="A68" s="2">
+        <f t="shared" si="1"/>
+        <v>62</v>
+      </c>
+      <c r="B68" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C68" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="D68" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="E68" s="6"/>
+      <c r="F68" s="6"/>
+      <c r="G68" s="6"/>
+    </row>
+    <row r="69" customHeight="1" spans="1:7">
+      <c r="A69" s="2">
+        <f t="shared" si="1"/>
+        <v>63</v>
+      </c>
+      <c r="B69" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C69" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D69" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="E69" s="6"/>
+      <c r="F69" s="6"/>
+      <c r="G69" s="6"/>
+    </row>
+    <row r="70" customHeight="1" spans="1:7">
+      <c r="A70" s="2">
+        <f t="shared" si="1"/>
+        <v>64</v>
+      </c>
+      <c r="B70" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C70" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D70" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="E70" s="6"/>
+      <c r="F70" s="6"/>
+      <c r="G70" s="6"/>
+    </row>
+    <row r="71" customHeight="1" spans="1:7">
+      <c r="A71" s="2">
+        <f t="shared" si="1"/>
+        <v>65</v>
+      </c>
+      <c r="B71" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C71" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="D71" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="E71" s="6"/>
+      <c r="F71" s="6"/>
+      <c r="G71" s="6"/>
+    </row>
+    <row r="72" customHeight="1" spans="1:7">
+      <c r="A72" s="2">
+        <f t="shared" si="1"/>
+        <v>66</v>
+      </c>
+      <c r="B72" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C72" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="D72" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="E72" s="6"/>
+      <c r="F72" s="6"/>
+      <c r="G72" s="6"/>
+    </row>
+    <row r="73" customHeight="1" spans="1:7">
+      <c r="A73" s="2">
+        <f t="shared" si="1"/>
+        <v>67</v>
+      </c>
+      <c r="B73" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C73" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="D73" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="E73" s="6"/>
+      <c r="F73" s="6"/>
+      <c r="G73" s="6"/>
+    </row>
+    <row r="74" customHeight="1" spans="1:7">
+      <c r="A74" s="2">
+        <f t="shared" si="1"/>
+        <v>68</v>
+      </c>
+      <c r="B74" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C74" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D74" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="E74" s="6"/>
+      <c r="F74" s="6"/>
+      <c r="G74" s="6"/>
+    </row>
+    <row r="75" customHeight="1" spans="1:7">
+      <c r="A75" s="2">
+        <f t="shared" si="1"/>
+        <v>69</v>
+      </c>
+      <c r="B75" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C75" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="D75" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="E75" s="6"/>
+      <c r="F75" s="6"/>
+      <c r="G75" s="6"/>
+    </row>
+    <row r="76" customHeight="1" spans="1:7">
+      <c r="A76" s="2">
+        <f t="shared" si="1"/>
+        <v>70</v>
+      </c>
+      <c r="B76" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C76" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="D76" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="E76" s="6"/>
+      <c r="F76" s="6"/>
+      <c r="G76" s="6"/>
+    </row>
+    <row r="77" customHeight="1" spans="1:7">
+      <c r="A77" s="2">
+        <f t="shared" si="1"/>
+        <v>71</v>
+      </c>
+      <c r="B77" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C77" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="D77" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="E77" s="6"/>
+      <c r="F77" s="6"/>
+      <c r="G77" s="6"/>
+    </row>
+    <row r="78" customHeight="1" spans="1:7">
+      <c r="A78" s="2">
+        <f t="shared" si="1"/>
+        <v>72</v>
+      </c>
+      <c r="B78" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C78" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="D78" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="E78" s="6"/>
+      <c r="F78" s="6"/>
+      <c r="G78" s="6"/>
+    </row>
+    <row r="79" customHeight="1" spans="1:7">
+      <c r="A79" s="2">
+        <f t="shared" si="1"/>
+        <v>73</v>
+      </c>
+      <c r="B79" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C79" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="D79" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="E79" s="6"/>
+      <c r="F79" s="6"/>
+      <c r="G79" s="6"/>
+    </row>
+    <row r="80" customHeight="1" spans="1:7">
+      <c r="A80" s="2">
+        <f t="shared" si="1"/>
+        <v>74</v>
+      </c>
+      <c r="B80" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C80" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D80" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="E80" s="6"/>
+      <c r="F80" s="6"/>
+      <c r="G80" s="6"/>
+    </row>
+    <row r="81" customHeight="1" spans="1:7">
+      <c r="A81" s="2">
+        <f t="shared" si="1"/>
+        <v>75</v>
+      </c>
+      <c r="B81" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C81" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D81" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="E81" s="6"/>
+      <c r="F81" s="6"/>
+      <c r="G81" s="6"/>
+    </row>
+    <row r="82" customHeight="1" spans="1:7">
+      <c r="A82" s="2">
+        <f t="shared" si="1"/>
+        <v>76</v>
+      </c>
+      <c r="B82" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C82" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="D82" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="E82" s="6"/>
+      <c r="F82" s="6"/>
+      <c r="G82" s="6"/>
+    </row>
+    <row r="83" customHeight="1" spans="1:7">
+      <c r="A83" s="2">
+        <f t="shared" si="1"/>
+        <v>77</v>
+      </c>
+      <c r="B83" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C83" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="D83" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="E83" s="6"/>
+      <c r="F83" s="6"/>
+      <c r="G83" s="6"/>
+    </row>
+    <row r="84" customHeight="1" spans="1:7">
+      <c r="A84" s="2">
+        <f t="shared" si="1"/>
+        <v>78</v>
+      </c>
+      <c r="B84" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C84" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="D84" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="E84" s="6"/>
+      <c r="F84" s="6"/>
+      <c r="G84" s="6"/>
+    </row>
+    <row r="85" customHeight="1" spans="1:7">
+      <c r="A85" s="2">
+        <f t="shared" si="1"/>
+        <v>79</v>
+      </c>
+      <c r="B85" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C85" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="D85" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="E85" s="6"/>
+      <c r="F85" s="6"/>
+      <c r="G85" s="6"/>
+    </row>
+    <row r="86" customHeight="1" spans="1:7">
+      <c r="A86" s="2">
+        <f t="shared" si="1"/>
+        <v>80</v>
+      </c>
+      <c r="B86" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C86" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D86" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="E86" s="6"/>
+      <c r="F86" s="6"/>
+      <c r="G86" s="6"/>
+    </row>
+    <row r="87" customHeight="1" spans="1:7">
+      <c r="A87" s="2">
+        <f t="shared" si="1"/>
+        <v>81</v>
+      </c>
+      <c r="B87" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C87" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D87" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="E87" s="6"/>
+      <c r="F87" s="6"/>
+      <c r="G87" s="6"/>
+    </row>
+    <row r="88" customHeight="1" spans="1:7">
+      <c r="A88" s="2">
+        <f t="shared" si="1"/>
+        <v>82</v>
+      </c>
+      <c r="B88" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C88" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="D88" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="E88" s="6"/>
+      <c r="F88" s="6"/>
+      <c r="G88" s="6"/>
+    </row>
+    <row r="89" customHeight="1" spans="1:7">
+      <c r="A89" s="2">
+        <f t="shared" si="1"/>
+        <v>83</v>
+      </c>
+      <c r="B89" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C89" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D89" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="E89" s="6"/>
+      <c r="F89" s="6"/>
+      <c r="G89" s="6"/>
+    </row>
+    <row r="90" customHeight="1" spans="1:7">
+      <c r="A90" s="2">
+        <f t="shared" si="1"/>
+        <v>84</v>
+      </c>
+      <c r="B90" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C90" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="D90" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="E90" s="6"/>
+      <c r="F90" s="6"/>
+      <c r="G90" s="6"/>
+    </row>
+    <row r="91" customHeight="1" spans="1:7">
+      <c r="A91" s="2">
+        <f t="shared" si="1"/>
+        <v>85</v>
+      </c>
+      <c r="B91" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C91" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="D91" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="E91" s="6"/>
+      <c r="F91" s="6"/>
+      <c r="G91" s="6"/>
+    </row>
+    <row r="92" customHeight="1" spans="1:7">
+      <c r="A92" s="2">
+        <f t="shared" si="1"/>
+        <v>86</v>
+      </c>
+      <c r="B92" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C92" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="D92" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="E92" s="6"/>
+      <c r="F92" s="6"/>
+      <c r="G92" s="6"/>
+    </row>
+    <row r="93" customHeight="1" spans="1:7">
+      <c r="A93" s="2">
+        <f t="shared" si="1"/>
+        <v>87</v>
+      </c>
+      <c r="B93" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C93" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D93" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="E93" s="6"/>
+      <c r="F93" s="6"/>
+      <c r="G93" s="6"/>
+    </row>
+    <row r="94" customHeight="1" spans="1:7">
+      <c r="A94" s="2">
+        <f t="shared" si="1"/>
+        <v>88</v>
+      </c>
+      <c r="B94" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C94" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D94" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="E94" s="6"/>
+      <c r="F94" s="6"/>
+      <c r="G94" s="6"/>
+    </row>
+    <row r="95" customHeight="1" spans="1:7">
+      <c r="A95" s="2">
+        <f t="shared" si="1"/>
+        <v>89</v>
+      </c>
+      <c r="B95" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C95" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="D95" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="E95" s="6"/>
+      <c r="F95" s="6"/>
+      <c r="G95" s="6"/>
+    </row>
+    <row r="96" customHeight="1" spans="1:7">
+      <c r="A96" s="2">
+        <f t="shared" si="1"/>
+        <v>90</v>
+      </c>
+      <c r="B96" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C96" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="D96" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="E96" s="6"/>
+      <c r="F96" s="6"/>
+      <c r="G96" s="6"/>
+    </row>
+    <row r="97" customHeight="1" spans="1:7">
+      <c r="A97" s="2">
+        <f t="shared" si="1"/>
+        <v>91</v>
+      </c>
+      <c r="B97" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C97" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="D97" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="E97" s="6"/>
+      <c r="F97" s="6"/>
+      <c r="G97" s="6"/>
+    </row>
+    <row r="98" customHeight="1" spans="1:7">
+      <c r="A98" s="2">
+        <f t="shared" si="1"/>
+        <v>92</v>
+      </c>
+      <c r="B98" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C98" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D98" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="E98" s="6"/>
+      <c r="F98" s="6"/>
+      <c r="G98" s="6"/>
+    </row>
+    <row r="99" customHeight="1" spans="1:7">
+      <c r="A99" s="2">
+        <f t="shared" si="1"/>
+        <v>93</v>
+      </c>
+      <c r="B99" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C99" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="D99" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="E99" s="6"/>
+      <c r="F99" s="6"/>
+      <c r="G99" s="6"/>
+    </row>
+    <row r="100" customHeight="1" spans="1:7">
+      <c r="A100" s="2">
+        <f t="shared" si="1"/>
+        <v>94</v>
+      </c>
+      <c r="B100" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C100" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="D100" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="E100" s="6"/>
+      <c r="F100" s="6"/>
+      <c r="G100" s="6"/>
+    </row>
+    <row r="101" customHeight="1" spans="1:7">
+      <c r="A101" s="2">
+        <f t="shared" si="1"/>
+        <v>95</v>
+      </c>
+      <c r="B101" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C101" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="D101" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="E101" s="6"/>
+      <c r="F101" s="6"/>
+      <c r="G101" s="6"/>
+    </row>
+    <row r="102" customHeight="1" spans="1:7">
+      <c r="A102" s="2">
+        <f t="shared" si="1"/>
+        <v>96</v>
+      </c>
+      <c r="B102" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C102" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="D102" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="E102" s="6"/>
+      <c r="F102" s="6"/>
+      <c r="G102" s="6"/>
+    </row>
+    <row r="103" customHeight="1" spans="1:7">
+      <c r="A103" s="2">
+        <f t="shared" si="1"/>
+        <v>97</v>
+      </c>
+      <c r="B103" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C103" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="D103" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="E103" s="6"/>
+      <c r="F103" s="6"/>
+      <c r="G103" s="6"/>
+    </row>
+    <row r="104" customHeight="1" spans="1:7">
+      <c r="A104" s="2">
+        <f t="shared" si="1"/>
+        <v>98</v>
+      </c>
+      <c r="B104" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C104" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D104" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="E104" s="6"/>
+      <c r="F104" s="6"/>
+      <c r="G104" s="6"/>
+    </row>
+    <row r="105" customHeight="1" spans="1:7">
+      <c r="A105" s="2">
+        <f t="shared" si="1"/>
+        <v>99</v>
+      </c>
+      <c r="B105" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C105" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="D105" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="E105" s="6"/>
+      <c r="F105" s="6"/>
+      <c r="G105" s="6"/>
+    </row>
+    <row r="106" customHeight="1" spans="1:7">
+      <c r="A106" s="2">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+      <c r="B106" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C106" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="D106" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="E106" s="6"/>
+      <c r="F106" s="6"/>
+      <c r="G106" s="6"/>
+    </row>
+    <row r="107" customHeight="1" spans="1:7">
+      <c r="A107" s="2">
+        <f t="shared" si="1"/>
+        <v>101</v>
+      </c>
+      <c r="B107" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C107" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="D107" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="E107" s="6"/>
+      <c r="F107" s="6"/>
+      <c r="G107" s="6"/>
+    </row>
+    <row r="108" customHeight="1" spans="1:7">
+      <c r="A108" s="2">
+        <f t="shared" si="1"/>
+        <v>102</v>
+      </c>
+      <c r="B108" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C108" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D108" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="E108" s="6"/>
+      <c r="F108" s="6"/>
+      <c r="G108" s="6"/>
+    </row>
+    <row r="109" customHeight="1" spans="1:7">
+      <c r="A109" s="2">
+        <f t="shared" si="1"/>
+        <v>103</v>
+      </c>
+      <c r="B109" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C109" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D109" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="E109" s="6"/>
+      <c r="F109" s="6"/>
+      <c r="G109" s="6"/>
+    </row>
+    <row r="110" customHeight="1" spans="1:7">
+      <c r="A110" s="2">
+        <f t="shared" si="1"/>
+        <v>104</v>
+      </c>
+      <c r="B110" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C110" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="D110" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="E110" s="6"/>
+      <c r="F110" s="6"/>
+      <c r="G110" s="6"/>
+    </row>
+    <row r="111" customHeight="1" spans="1:7">
+      <c r="A111" s="2">
+        <f t="shared" si="1"/>
+        <v>105</v>
+      </c>
+      <c r="B111" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C111" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="D111" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="E111" s="6"/>
+      <c r="F111" s="6"/>
+      <c r="G111" s="6"/>
+    </row>
+    <row r="112" customHeight="1" spans="1:7">
+      <c r="A112" s="2">
+        <f t="shared" si="1"/>
+        <v>106</v>
+      </c>
+      <c r="B112" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C112" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="D112" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="E112" s="6"/>
+      <c r="F112" s="6"/>
+      <c r="G112" s="6"/>
+    </row>
+    <row r="113" customHeight="1" spans="1:7">
+      <c r="A113" s="2">
+        <f t="shared" si="1"/>
+        <v>107</v>
+      </c>
+      <c r="B113" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C113" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="D113" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="E113" s="6"/>
+      <c r="F113" s="6"/>
+      <c r="G113" s="6"/>
+    </row>
+    <row r="114" customHeight="1" spans="1:7">
+      <c r="A114" s="2">
+        <f t="shared" si="1"/>
+        <v>108</v>
+      </c>
+      <c r="B114" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C114" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="D114" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="E114" s="6"/>
+      <c r="F114" s="6"/>
+      <c r="G114" s="6"/>
+    </row>
+    <row r="115" customHeight="1" spans="1:7">
+      <c r="A115" s="2">
+        <f t="shared" si="1"/>
+        <v>109</v>
+      </c>
+      <c r="B115" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C115" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D115" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="E115" s="6"/>
+      <c r="F115" s="6"/>
+      <c r="G115" s="6"/>
+    </row>
+    <row r="116" customHeight="1" spans="1:7">
+      <c r="A116" s="2">
+        <f t="shared" si="1"/>
+        <v>110</v>
+      </c>
+      <c r="B116" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C116" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="D116" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="E116" s="6"/>
+      <c r="F116" s="6"/>
+      <c r="G116" s="6"/>
+    </row>
+    <row r="117" customHeight="1" spans="1:7">
+      <c r="A117" s="2">
+        <f t="shared" si="1"/>
+        <v>111</v>
+      </c>
+      <c r="B117" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C117" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="D117" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="E117" s="6"/>
+      <c r="F117" s="6"/>
+      <c r="G117" s="6"/>
+    </row>
+    <row r="118" customHeight="1" spans="1:7">
+      <c r="A118" s="2">
+        <f t="shared" si="1"/>
+        <v>112</v>
+      </c>
+      <c r="B118" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C118" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="C62" s="2"/>
-      <c r="D62" s="2"/>
-      <c r="E62" s="2"/>
+      <c r="D118" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="E118" s="6"/>
+      <c r="F118" s="6"/>
+      <c r="G118" s="6"/>
+    </row>
+    <row r="119" customHeight="1" spans="1:7">
+      <c r="A119" s="2">
+        <f t="shared" si="1"/>
+        <v>113</v>
+      </c>
+      <c r="B119" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C119" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="D119" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="E119" s="6"/>
+      <c r="F119" s="6"/>
+      <c r="G119" s="6"/>
+    </row>
+    <row r="120" customHeight="1" spans="1:7">
+      <c r="A120" s="2">
+        <f t="shared" si="1"/>
+        <v>114</v>
+      </c>
+      <c r="B120" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C120" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="D120" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="E120" s="6"/>
+      <c r="F120" s="6"/>
+      <c r="G120" s="6"/>
+    </row>
+    <row r="121" customHeight="1" spans="1:7">
+      <c r="A121" s="2">
+        <f t="shared" si="1"/>
+        <v>115</v>
+      </c>
+      <c r="B121" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C121" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D121" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="E121" s="6"/>
+      <c r="F121" s="6"/>
+      <c r="G121" s="6"/>
+    </row>
+    <row r="122" customHeight="1" spans="1:7">
+      <c r="A122" s="2">
+        <f t="shared" si="1"/>
+        <v>116</v>
+      </c>
+      <c r="B122" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C122" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D122" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="E122" s="6"/>
+      <c r="F122" s="6"/>
+      <c r="G122" s="6"/>
+    </row>
+    <row r="123" customHeight="1" spans="1:7">
+      <c r="A123" s="2">
+        <f t="shared" si="1"/>
+        <v>117</v>
+      </c>
+      <c r="B123" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C123" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D123" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="E123" s="6"/>
+      <c r="F123" s="6"/>
+      <c r="G123" s="6"/>
+    </row>
+    <row r="124" customHeight="1" spans="1:7">
+      <c r="A124" s="2">
+        <f t="shared" si="1"/>
+        <v>118</v>
+      </c>
+      <c r="B124" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C124" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="D124" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="E124" s="6"/>
+      <c r="F124" s="6"/>
+      <c r="G124" s="6"/>
+    </row>
+    <row r="125" customHeight="1" spans="1:7">
+      <c r="A125" s="2">
+        <f t="shared" si="1"/>
+        <v>119</v>
+      </c>
+      <c r="B125" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C125" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="D125" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="E125" s="6"/>
+      <c r="F125" s="6"/>
+      <c r="G125" s="6"/>
+    </row>
+    <row r="126" customHeight="1" spans="1:7">
+      <c r="A126" s="2">
+        <f t="shared" si="1"/>
+        <v>120</v>
+      </c>
+      <c r="B126" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C126" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="D126" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="E126" s="6"/>
+      <c r="F126" s="6"/>
+      <c r="G126" s="6"/>
+    </row>
+    <row r="127" customHeight="1" spans="1:7">
+      <c r="A127" s="2">
+        <f t="shared" ref="A127:A190" si="2">A126+1</f>
+        <v>121</v>
+      </c>
+      <c r="B127" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C127" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="D127" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="E127" s="6"/>
+      <c r="F127" s="6"/>
+      <c r="G127" s="6"/>
+    </row>
+    <row r="128" customHeight="1" spans="1:7">
+      <c r="A128" s="2">
+        <f t="shared" si="2"/>
+        <v>122</v>
+      </c>
+      <c r="B128" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C128" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="D128" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="E128" s="6"/>
+      <c r="F128" s="6"/>
+      <c r="G128" s="6"/>
+    </row>
+    <row r="129" customHeight="1" spans="1:7">
+      <c r="A129" s="2">
+        <f t="shared" si="2"/>
+        <v>123</v>
+      </c>
+      <c r="B129" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C129" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="D129" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="E129" s="6"/>
+      <c r="F129" s="6"/>
+      <c r="G129" s="6"/>
+    </row>
+    <row r="130" customHeight="1" spans="1:7">
+      <c r="A130" s="2">
+        <f t="shared" si="2"/>
+        <v>124</v>
+      </c>
+      <c r="B130" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C130" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D130" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="E130" s="6"/>
+      <c r="F130" s="6"/>
+      <c r="G130" s="6"/>
+    </row>
+    <row r="131" customHeight="1" spans="1:7">
+      <c r="A131" s="2">
+        <f t="shared" si="2"/>
+        <v>125</v>
+      </c>
+      <c r="B131" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C131" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D131" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="E131" s="6"/>
+      <c r="F131" s="6"/>
+      <c r="G131" s="6"/>
+    </row>
+    <row r="132" customHeight="1" spans="1:7">
+      <c r="A132" s="2">
+        <f t="shared" si="2"/>
+        <v>126</v>
+      </c>
+      <c r="B132" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C132" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="D132" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="E132" s="6"/>
+      <c r="F132" s="6"/>
+      <c r="G132" s="6"/>
+    </row>
+    <row r="133" customHeight="1" spans="1:7">
+      <c r="A133" s="2">
+        <f t="shared" si="2"/>
+        <v>127</v>
+      </c>
+      <c r="B133" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C133" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="D133" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="E133" s="6"/>
+      <c r="F133" s="6"/>
+      <c r="G133" s="6"/>
+    </row>
+    <row r="134" customHeight="1" spans="1:7">
+      <c r="A134" s="2">
+        <f t="shared" si="2"/>
+        <v>128</v>
+      </c>
+      <c r="B134" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C134" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D134" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="E134" s="6"/>
+      <c r="F134" s="6"/>
+      <c r="G134" s="6"/>
+    </row>
+    <row r="135" customHeight="1" spans="1:7">
+      <c r="A135" s="2">
+        <f t="shared" si="2"/>
+        <v>129</v>
+      </c>
+      <c r="B135" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C135" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D135" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="E135" s="6"/>
+      <c r="F135" s="6"/>
+      <c r="G135" s="6"/>
+    </row>
+    <row r="136" customHeight="1" spans="1:7">
+      <c r="A136" s="2">
+        <f t="shared" si="2"/>
+        <v>130</v>
+      </c>
+      <c r="B136" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C136" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="D136" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="E136" s="6"/>
+      <c r="F136" s="6"/>
+      <c r="G136" s="6"/>
+    </row>
+    <row r="137" customHeight="1" spans="1:7">
+      <c r="A137" s="2">
+        <f t="shared" si="2"/>
+        <v>131</v>
+      </c>
+      <c r="B137" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C137" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D137" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="E137" s="6"/>
+      <c r="F137" s="6"/>
+      <c r="G137" s="6"/>
+    </row>
+    <row r="138" customHeight="1" spans="1:7">
+      <c r="A138" s="2">
+        <f t="shared" si="2"/>
+        <v>132</v>
+      </c>
+      <c r="B138" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C138" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="D138" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="E138" s="6"/>
+      <c r="F138" s="6"/>
+      <c r="G138" s="6"/>
+    </row>
+    <row r="139" customHeight="1" spans="1:7">
+      <c r="A139" s="2">
+        <f t="shared" si="2"/>
+        <v>133</v>
+      </c>
+      <c r="B139" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C139" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="D139" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="E139" s="6"/>
+      <c r="F139" s="6"/>
+      <c r="G139" s="6"/>
+    </row>
+    <row r="140" customHeight="1" spans="1:7">
+      <c r="A140" s="2">
+        <f t="shared" si="2"/>
+        <v>134</v>
+      </c>
+      <c r="B140" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C140" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="D140" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="E140" s="6"/>
+      <c r="F140" s="6"/>
+      <c r="G140" s="6"/>
+    </row>
+    <row r="141" customHeight="1" spans="1:7">
+      <c r="A141" s="2">
+        <f t="shared" si="2"/>
+        <v>135</v>
+      </c>
+      <c r="B141" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C141" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="D141" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="E141" s="6"/>
+      <c r="F141" s="6"/>
+      <c r="G141" s="6"/>
+    </row>
+    <row r="142" customHeight="1" spans="1:7">
+      <c r="A142" s="2">
+        <f t="shared" si="2"/>
+        <v>136</v>
+      </c>
+      <c r="B142" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C142" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D142" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="E142" s="6"/>
+      <c r="F142" s="6"/>
+      <c r="G142" s="6"/>
+    </row>
+    <row r="143" customHeight="1" spans="1:7">
+      <c r="A143" s="2">
+        <f t="shared" si="2"/>
+        <v>137</v>
+      </c>
+      <c r="B143" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C143" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="D143" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="E143" s="6"/>
+      <c r="F143" s="6"/>
+      <c r="G143" s="6"/>
+    </row>
+    <row r="144" customHeight="1" spans="1:7">
+      <c r="A144" s="2">
+        <f t="shared" si="2"/>
+        <v>138</v>
+      </c>
+      <c r="B144" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C144" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="D144" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="E144" s="6"/>
+      <c r="F144" s="6"/>
+      <c r="G144" s="6"/>
+    </row>
+    <row r="145" customHeight="1" spans="1:7">
+      <c r="A145" s="2">
+        <f t="shared" si="2"/>
+        <v>139</v>
+      </c>
+      <c r="B145" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C145" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="D145" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="E145" s="6"/>
+      <c r="F145" s="6"/>
+      <c r="G145" s="6"/>
+    </row>
+    <row r="146" customHeight="1" spans="1:7">
+      <c r="A146" s="2">
+        <f t="shared" si="2"/>
+        <v>140</v>
+      </c>
+      <c r="B146" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C146" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="D146" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="E146" s="6"/>
+      <c r="F146" s="6"/>
+      <c r="G146" s="6"/>
+    </row>
+    <row r="147" customHeight="1" spans="1:7">
+      <c r="A147" s="2">
+        <f t="shared" si="2"/>
+        <v>141</v>
+      </c>
+      <c r="B147" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C147" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D147" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="E147" s="6"/>
+      <c r="F147" s="6"/>
+      <c r="G147" s="6"/>
+    </row>
+    <row r="148" customHeight="1" spans="1:7">
+      <c r="A148" s="2">
+        <f t="shared" si="2"/>
+        <v>142</v>
+      </c>
+      <c r="B148" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C148" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D148" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="E148" s="6"/>
+      <c r="F148" s="6"/>
+      <c r="G148" s="6"/>
+    </row>
+    <row r="149" customHeight="1" spans="1:7">
+      <c r="A149" s="2">
+        <f t="shared" si="2"/>
+        <v>143</v>
+      </c>
+      <c r="B149" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C149" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D149" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="E149" s="6"/>
+      <c r="F149" s="6"/>
+      <c r="G149" s="6"/>
+    </row>
+    <row r="150" customHeight="1" spans="1:7">
+      <c r="A150" s="2">
+        <f t="shared" si="2"/>
+        <v>144</v>
+      </c>
+      <c r="B150" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C150" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D150" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="E150" s="6"/>
+      <c r="F150" s="6"/>
+      <c r="G150" s="6"/>
+    </row>
+    <row r="151" customHeight="1" spans="1:7">
+      <c r="A151" s="2">
+        <f t="shared" si="2"/>
+        <v>145</v>
+      </c>
+      <c r="B151" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C151" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="D151" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="E151" s="6"/>
+      <c r="F151" s="6"/>
+      <c r="G151" s="6"/>
+    </row>
+    <row r="152" customHeight="1" spans="1:7">
+      <c r="A152" s="2">
+        <f t="shared" si="2"/>
+        <v>146</v>
+      </c>
+      <c r="B152" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C152" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="D152" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="E152" s="6"/>
+      <c r="F152" s="6"/>
+      <c r="G152" s="6"/>
+    </row>
+    <row r="153" customHeight="1" spans="1:7">
+      <c r="A153" s="2">
+        <f t="shared" si="2"/>
+        <v>147</v>
+      </c>
+      <c r="B153" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C153" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="D153" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="E153" s="6"/>
+      <c r="F153" s="6"/>
+      <c r="G153" s="6"/>
+    </row>
+    <row r="154" customHeight="1" spans="1:7">
+      <c r="A154" s="2">
+        <f t="shared" si="2"/>
+        <v>148</v>
+      </c>
+      <c r="B154" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C154" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="D154" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="E154" s="6"/>
+      <c r="F154" s="6"/>
+      <c r="G154" s="6"/>
+    </row>
+    <row r="155" customHeight="1" spans="1:7">
+      <c r="A155" s="2">
+        <f t="shared" si="2"/>
+        <v>149</v>
+      </c>
+      <c r="B155" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C155" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="D155" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="E155" s="6"/>
+      <c r="F155" s="6"/>
+      <c r="G155" s="6"/>
+    </row>
+    <row r="156" customHeight="1" spans="1:7">
+      <c r="A156" s="2">
+        <f t="shared" si="2"/>
+        <v>150</v>
+      </c>
+      <c r="B156" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C156" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D156" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="E156" s="6"/>
+      <c r="F156" s="6"/>
+      <c r="G156" s="6"/>
+    </row>
+    <row r="157" customHeight="1" spans="1:7">
+      <c r="A157" s="2">
+        <f t="shared" si="2"/>
+        <v>151</v>
+      </c>
+      <c r="B157" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C157" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="D157" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="E157" s="6"/>
+      <c r="F157" s="6"/>
+      <c r="G157" s="6"/>
+    </row>
+    <row r="158" customHeight="1" spans="1:7">
+      <c r="A158" s="2">
+        <f t="shared" si="2"/>
+        <v>152</v>
+      </c>
+      <c r="B158" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C158" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D158" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="E158" s="6"/>
+      <c r="F158" s="6"/>
+      <c r="G158" s="6"/>
+    </row>
+    <row r="159" customHeight="1" spans="1:7">
+      <c r="A159" s="2">
+        <f t="shared" si="2"/>
+        <v>153</v>
+      </c>
+      <c r="B159" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C159" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D159" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="E159" s="6"/>
+      <c r="F159" s="6"/>
+      <c r="G159" s="6"/>
+    </row>
+    <row r="160" customHeight="1" spans="1:7">
+      <c r="A160" s="2">
+        <f t="shared" si="2"/>
+        <v>154</v>
+      </c>
+      <c r="B160" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C160" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="D160" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="E160" s="6"/>
+      <c r="F160" s="6"/>
+      <c r="G160" s="6"/>
+    </row>
+    <row r="161" customHeight="1" spans="1:7">
+      <c r="A161" s="2">
+        <f t="shared" si="2"/>
+        <v>155</v>
+      </c>
+      <c r="B161" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C161" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="D161" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="E161" s="6"/>
+      <c r="F161" s="6"/>
+      <c r="G161" s="6"/>
+    </row>
+    <row r="162" customHeight="1" spans="1:7">
+      <c r="A162" s="2">
+        <f t="shared" si="2"/>
+        <v>156</v>
+      </c>
+      <c r="B162" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C162" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="D162" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="E162" s="6"/>
+      <c r="F162" s="6"/>
+      <c r="G162" s="6"/>
+    </row>
+    <row r="163" customHeight="1" spans="1:7">
+      <c r="A163" s="2">
+        <f t="shared" si="2"/>
+        <v>157</v>
+      </c>
+      <c r="B163" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C163" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D163" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="E163" s="6"/>
+      <c r="F163" s="6"/>
+      <c r="G163" s="6"/>
+    </row>
+    <row r="164" customHeight="1" spans="1:7">
+      <c r="A164" s="2">
+        <f t="shared" si="2"/>
+        <v>158</v>
+      </c>
+      <c r="B164" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C164" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D164" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="E164" s="6"/>
+      <c r="F164" s="6"/>
+      <c r="G164" s="6"/>
+    </row>
+    <row r="165" customHeight="1" spans="1:7">
+      <c r="A165" s="2">
+        <f t="shared" si="2"/>
+        <v>159</v>
+      </c>
+      <c r="B165" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C165" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="D165" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="E165" s="6"/>
+      <c r="F165" s="6"/>
+      <c r="G165" s="6"/>
+    </row>
+    <row r="166" customHeight="1" spans="1:7">
+      <c r="A166" s="2">
+        <f t="shared" si="2"/>
+        <v>160</v>
+      </c>
+      <c r="B166" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C166" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="D166" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="E166" s="6"/>
+      <c r="F166" s="6"/>
+      <c r="G166" s="6"/>
+    </row>
+    <row r="167" customHeight="1" spans="1:7">
+      <c r="A167" s="2">
+        <f t="shared" si="2"/>
+        <v>161</v>
+      </c>
+      <c r="B167" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C167" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="D167" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="E167" s="6"/>
+      <c r="F167" s="6"/>
+      <c r="G167" s="6"/>
+    </row>
+    <row r="168" customHeight="1" spans="1:7">
+      <c r="A168" s="2">
+        <f t="shared" si="2"/>
+        <v>162</v>
+      </c>
+      <c r="B168" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C168" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="D168" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="E168" s="6"/>
+      <c r="F168" s="6"/>
+      <c r="G168" s="6"/>
+    </row>
+    <row r="169" customHeight="1" spans="1:7">
+      <c r="A169" s="2">
+        <f t="shared" si="2"/>
+        <v>163</v>
+      </c>
+      <c r="B169" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C169" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="D169" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="E169" s="6"/>
+      <c r="F169" s="6"/>
+      <c r="G169" s="6"/>
+    </row>
+    <row r="170" customHeight="1" spans="1:7">
+      <c r="A170" s="2">
+        <f t="shared" si="2"/>
+        <v>164</v>
+      </c>
+      <c r="B170" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C170" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="D170" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="E170" s="6"/>
+      <c r="F170" s="6"/>
+      <c r="G170" s="6"/>
+    </row>
+    <row r="171" customHeight="1" spans="1:7">
+      <c r="A171" s="2">
+        <f t="shared" si="2"/>
+        <v>165</v>
+      </c>
+      <c r="B171" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C171" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D171" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="E171" s="6"/>
+      <c r="F171" s="6"/>
+      <c r="G171" s="6"/>
+    </row>
+    <row r="172" customHeight="1" spans="1:7">
+      <c r="A172" s="2">
+        <f t="shared" si="2"/>
+        <v>166</v>
+      </c>
+      <c r="B172" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C172" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D172" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="E172" s="6"/>
+      <c r="F172" s="6"/>
+      <c r="G172" s="6"/>
+    </row>
+    <row r="173" customHeight="1" spans="1:7">
+      <c r="A173" s="2">
+        <f t="shared" si="2"/>
+        <v>167</v>
+      </c>
+      <c r="B173" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C173" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="D173" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="E173" s="6"/>
+      <c r="F173" s="6"/>
+      <c r="G173" s="6"/>
+    </row>
+    <row r="174" customHeight="1" spans="1:7">
+      <c r="A174" s="2">
+        <f t="shared" si="2"/>
+        <v>168</v>
+      </c>
+      <c r="B174" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C174" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="D174" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="E174" s="6"/>
+      <c r="F174" s="6"/>
+      <c r="G174" s="6"/>
+    </row>
+    <row r="175" customHeight="1" spans="1:7">
+      <c r="A175" s="2">
+        <f t="shared" si="2"/>
+        <v>169</v>
+      </c>
+      <c r="B175" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C175" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="D175" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="E175" s="6"/>
+      <c r="F175" s="6"/>
+      <c r="G175" s="6"/>
+    </row>
+    <row r="176" customHeight="1" spans="1:7">
+      <c r="A176" s="2">
+        <f t="shared" si="2"/>
+        <v>170</v>
+      </c>
+      <c r="B176" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C176" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="D176" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="E176" s="6"/>
+      <c r="F176" s="6"/>
+      <c r="G176" s="6"/>
+    </row>
+    <row r="177" customHeight="1" spans="1:7">
+      <c r="A177" s="2">
+        <f t="shared" si="2"/>
+        <v>171</v>
+      </c>
+      <c r="B177" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C177" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="D177" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="E177" s="6"/>
+      <c r="F177" s="6"/>
+      <c r="G177" s="6"/>
+    </row>
+    <row r="178" customHeight="1" spans="1:7">
+      <c r="A178" s="2">
+        <f t="shared" si="2"/>
+        <v>172</v>
+      </c>
+      <c r="B178" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C178" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D178" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="E178" s="6"/>
+      <c r="F178" s="6"/>
+      <c r="G178" s="6"/>
+    </row>
+    <row r="179" customHeight="1" spans="1:7">
+      <c r="A179" s="2">
+        <f t="shared" si="2"/>
+        <v>173</v>
+      </c>
+      <c r="B179" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C179" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D179" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="E179" s="6"/>
+      <c r="F179" s="6"/>
+      <c r="G179" s="6"/>
+    </row>
+    <row r="180" customHeight="1" spans="1:7">
+      <c r="A180" s="2">
+        <f t="shared" si="2"/>
+        <v>174</v>
+      </c>
+      <c r="B180" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C180" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="D180" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="E180" s="6"/>
+      <c r="F180" s="6"/>
+      <c r="G180" s="6"/>
+    </row>
+    <row r="181" customHeight="1" spans="1:7">
+      <c r="A181" s="2">
+        <f t="shared" si="2"/>
+        <v>175</v>
+      </c>
+      <c r="B181" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C181" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="D181" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="E181" s="6"/>
+      <c r="F181" s="6"/>
+      <c r="G181" s="6"/>
+    </row>
+    <row r="182" customHeight="1" spans="1:7">
+      <c r="A182" s="2">
+        <f t="shared" si="2"/>
+        <v>176</v>
+      </c>
+      <c r="B182" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C182" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D182" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="E182" s="6"/>
+      <c r="F182" s="6"/>
+      <c r="G182" s="6"/>
+    </row>
+    <row r="183" customHeight="1" spans="1:7">
+      <c r="A183" s="2">
+        <f t="shared" si="2"/>
+        <v>177</v>
+      </c>
+      <c r="B183" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C183" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="D183" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="E183" s="6"/>
+      <c r="F183" s="6"/>
+      <c r="G183" s="6"/>
+    </row>
+    <row r="184" customHeight="1" spans="1:7">
+      <c r="A184" s="2">
+        <f t="shared" si="2"/>
+        <v>178</v>
+      </c>
+      <c r="B184" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C184" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="D184" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="E184" s="6"/>
+      <c r="F184" s="6"/>
+      <c r="G184" s="6"/>
+    </row>
+    <row r="185" customHeight="1" spans="1:7">
+      <c r="A185" s="2">
+        <f t="shared" si="2"/>
+        <v>179</v>
+      </c>
+      <c r="B185" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C185" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="D185" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="E185" s="6"/>
+      <c r="F185" s="6"/>
+      <c r="G185" s="6"/>
+    </row>
+    <row r="186" customHeight="1" spans="1:7">
+      <c r="A186" s="2">
+        <f t="shared" si="2"/>
+        <v>180</v>
+      </c>
+      <c r="B186" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C186" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D186" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="E186" s="6"/>
+      <c r="F186" s="6"/>
+      <c r="G186" s="6"/>
+    </row>
+    <row r="187" customHeight="1" spans="1:7">
+      <c r="A187" s="2">
+        <f t="shared" si="2"/>
+        <v>181</v>
+      </c>
+      <c r="B187" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C187" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D187" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="E187" s="6"/>
+      <c r="F187" s="6"/>
+      <c r="G187" s="6"/>
+    </row>
+    <row r="188" customHeight="1" spans="1:7">
+      <c r="A188" s="2">
+        <f t="shared" si="2"/>
+        <v>182</v>
+      </c>
+      <c r="B188" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C188" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D188" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="E188" s="6"/>
+      <c r="F188" s="6"/>
+      <c r="G188" s="6"/>
+    </row>
+    <row r="189" customHeight="1" spans="1:7">
+      <c r="A189" s="2">
+        <f t="shared" si="2"/>
+        <v>183</v>
+      </c>
+      <c r="B189" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C189" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D189" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="E189" s="6"/>
+      <c r="F189" s="6"/>
+      <c r="G189" s="6"/>
+    </row>
+    <row r="190" customHeight="1" spans="1:7">
+      <c r="A190" s="2">
+        <f t="shared" si="2"/>
+        <v>184</v>
+      </c>
+      <c r="B190" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C190" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D190" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="E190" s="6"/>
+      <c r="F190" s="6"/>
+      <c r="G190" s="6"/>
+    </row>
+    <row r="191" customHeight="1" spans="1:7">
+      <c r="A191" s="2">
+        <f t="shared" ref="A191:A254" si="3">A190+1</f>
+        <v>185</v>
+      </c>
+      <c r="B191" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C191" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="D191" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="E191" s="6"/>
+      <c r="F191" s="6"/>
+      <c r="G191" s="6"/>
+    </row>
+    <row r="192" customHeight="1" spans="1:7">
+      <c r="A192" s="2">
+        <f t="shared" si="3"/>
+        <v>186</v>
+      </c>
+      <c r="B192" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C192" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="D192" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="E192" s="6"/>
+      <c r="F192" s="6"/>
+      <c r="G192" s="6"/>
+    </row>
+    <row r="193" customHeight="1" spans="1:7">
+      <c r="A193" s="2">
+        <f t="shared" si="3"/>
+        <v>187</v>
+      </c>
+      <c r="B193" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C193" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="D193" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="E193" s="6"/>
+      <c r="F193" s="6"/>
+      <c r="G193" s="6"/>
+    </row>
+    <row r="194" customHeight="1" spans="1:7">
+      <c r="A194" s="2">
+        <f t="shared" si="3"/>
+        <v>188</v>
+      </c>
+      <c r="B194" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C194" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D194" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="E194" s="6"/>
+      <c r="F194" s="6"/>
+      <c r="G194" s="6"/>
+    </row>
+    <row r="195" customHeight="1" spans="1:7">
+      <c r="A195" s="2">
+        <f t="shared" si="3"/>
+        <v>189</v>
+      </c>
+      <c r="B195" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C195" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D195" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="E195" s="6"/>
+      <c r="F195" s="6"/>
+      <c r="G195" s="6"/>
+    </row>
+    <row r="196" customHeight="1" spans="1:7">
+      <c r="A196" s="2">
+        <f t="shared" si="3"/>
+        <v>190</v>
+      </c>
+      <c r="B196" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C196" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="D196" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="E196" s="6"/>
+      <c r="F196" s="6"/>
+      <c r="G196" s="6"/>
+    </row>
+    <row r="197" customHeight="1" spans="1:7">
+      <c r="A197" s="2">
+        <f t="shared" si="3"/>
+        <v>191</v>
+      </c>
+      <c r="B197" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C197" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="D197" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="E197" s="6"/>
+      <c r="F197" s="6"/>
+      <c r="G197" s="6"/>
+    </row>
+    <row r="198" customHeight="1" spans="1:7">
+      <c r="A198" s="2">
+        <f t="shared" si="3"/>
+        <v>192</v>
+      </c>
+      <c r="B198" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C198" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="D198" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="E198" s="6"/>
+      <c r="F198" s="6"/>
+      <c r="G198" s="6"/>
+    </row>
+    <row r="199" customHeight="1" spans="1:7">
+      <c r="A199" s="2">
+        <f t="shared" si="3"/>
+        <v>193</v>
+      </c>
+      <c r="B199" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C199" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="D199" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="E199" s="6"/>
+      <c r="F199" s="6"/>
+      <c r="G199" s="6"/>
+    </row>
+    <row r="200" customHeight="1" spans="1:7">
+      <c r="A200" s="2">
+        <f t="shared" si="3"/>
+        <v>194</v>
+      </c>
+      <c r="B200" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C200" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="D200" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="E200" s="6"/>
+      <c r="F200" s="6"/>
+      <c r="G200" s="6"/>
+    </row>
+    <row r="201" customHeight="1" spans="1:7">
+      <c r="A201" s="2">
+        <f t="shared" si="3"/>
+        <v>195</v>
+      </c>
+      <c r="B201" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C201" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="D201" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="E201" s="6"/>
+      <c r="F201" s="6"/>
+      <c r="G201" s="6"/>
+    </row>
+    <row r="202" customHeight="1" spans="1:7">
+      <c r="A202" s="2">
+        <f t="shared" si="3"/>
+        <v>196</v>
+      </c>
+      <c r="B202" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C202" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="D202" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="E202" s="6"/>
+      <c r="F202" s="6"/>
+      <c r="G202" s="6"/>
+    </row>
+    <row r="203" customHeight="1" spans="1:7">
+      <c r="A203" s="2">
+        <f t="shared" si="3"/>
+        <v>197</v>
+      </c>
+      <c r="B203" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C203" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D203" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="E203" s="6"/>
+      <c r="F203" s="6"/>
+      <c r="G203" s="6"/>
+    </row>
+    <row r="204" customHeight="1" spans="1:7">
+      <c r="A204" s="2">
+        <f t="shared" si="3"/>
+        <v>198</v>
+      </c>
+      <c r="B204" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C204" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D204" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="E204" s="6"/>
+      <c r="F204" s="6"/>
+      <c r="G204" s="6"/>
+    </row>
+    <row r="205" customHeight="1" spans="1:7">
+      <c r="A205" s="2">
+        <f t="shared" si="3"/>
+        <v>199</v>
+      </c>
+      <c r="B205" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C205" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D205" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="E205" s="6"/>
+      <c r="F205" s="6"/>
+      <c r="G205" s="6"/>
+    </row>
+    <row r="206" customHeight="1" spans="1:7">
+      <c r="A206" s="2">
+        <f t="shared" si="3"/>
+        <v>200</v>
+      </c>
+      <c r="B206" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C206" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="D206" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="E206" s="6"/>
+      <c r="F206" s="6"/>
+      <c r="G206" s="6"/>
+    </row>
+    <row r="207" customHeight="1" spans="1:7">
+      <c r="A207" s="2">
+        <f t="shared" si="3"/>
+        <v>201</v>
+      </c>
+      <c r="B207" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C207" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="D207" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="E207" s="6"/>
+      <c r="F207" s="6"/>
+      <c r="G207" s="6"/>
+    </row>
+    <row r="208" customHeight="1" spans="1:7">
+      <c r="A208" s="2">
+        <f t="shared" si="3"/>
+        <v>202</v>
+      </c>
+      <c r="B208" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C208" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="D208" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="E208" s="6"/>
+      <c r="F208" s="6"/>
+      <c r="G208" s="6"/>
+    </row>
+    <row r="209" customHeight="1" spans="1:7">
+      <c r="A209" s="2">
+        <f t="shared" si="3"/>
+        <v>203</v>
+      </c>
+      <c r="B209" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C209" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="D209" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="E209" s="6"/>
+      <c r="F209" s="6"/>
+      <c r="G209" s="6"/>
+    </row>
+    <row r="210" customHeight="1" spans="1:7">
+      <c r="A210" s="2">
+        <f t="shared" si="3"/>
+        <v>204</v>
+      </c>
+      <c r="B210" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C210" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D210" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="E210" s="6"/>
+      <c r="F210" s="6"/>
+      <c r="G210" s="6"/>
+    </row>
+    <row r="211" customHeight="1" spans="1:7">
+      <c r="A211" s="2">
+        <f t="shared" si="3"/>
+        <v>205</v>
+      </c>
+      <c r="B211" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C211" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D211" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="E211" s="6"/>
+      <c r="F211" s="6"/>
+      <c r="G211" s="6"/>
+    </row>
+    <row r="212" customHeight="1" spans="1:7">
+      <c r="A212" s="2">
+        <f t="shared" si="3"/>
+        <v>206</v>
+      </c>
+      <c r="B212" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C212" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="D212" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="E212" s="6"/>
+      <c r="F212" s="6"/>
+      <c r="G212" s="6"/>
+    </row>
+    <row r="213" customHeight="1" spans="1:7">
+      <c r="A213" s="2">
+        <f t="shared" si="3"/>
+        <v>207</v>
+      </c>
+      <c r="B213" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C213" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="D213" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="E213" s="6"/>
+      <c r="F213" s="6"/>
+      <c r="G213" s="6"/>
+    </row>
+    <row r="214" customHeight="1" spans="1:7">
+      <c r="A214" s="2">
+        <f t="shared" si="3"/>
+        <v>208</v>
+      </c>
+      <c r="B214" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C214" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="D214" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="E214" s="6"/>
+      <c r="F214" s="6"/>
+      <c r="G214" s="6"/>
+    </row>
+    <row r="215" customHeight="1" spans="1:7">
+      <c r="A215" s="2">
+        <f t="shared" si="3"/>
+        <v>209</v>
+      </c>
+      <c r="B215" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C215" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="D215" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="E215" s="6"/>
+      <c r="F215" s="6"/>
+      <c r="G215" s="6"/>
+    </row>
+    <row r="216" customHeight="1" spans="1:7">
+      <c r="A216" s="2">
+        <f t="shared" si="3"/>
+        <v>210</v>
+      </c>
+      <c r="B216" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C216" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="D216" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="E216" s="6"/>
+      <c r="F216" s="6"/>
+      <c r="G216" s="6"/>
+    </row>
+    <row r="217" customHeight="1" spans="1:7">
+      <c r="A217" s="2">
+        <f t="shared" si="3"/>
+        <v>211</v>
+      </c>
+      <c r="B217" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C217" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D217" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="E217" s="6"/>
+      <c r="F217" s="6"/>
+      <c r="G217" s="6"/>
+    </row>
+    <row r="218" customHeight="1" spans="1:7">
+      <c r="A218" s="2">
+        <f t="shared" si="3"/>
+        <v>212</v>
+      </c>
+      <c r="B218" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C218" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="D218" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="E218" s="6"/>
+      <c r="F218" s="6"/>
+      <c r="G218" s="6"/>
+    </row>
+    <row r="219" customHeight="1" spans="1:7">
+      <c r="A219" s="2">
+        <f t="shared" si="3"/>
+        <v>213</v>
+      </c>
+      <c r="B219" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C219" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="D219" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="E219" s="6"/>
+      <c r="F219" s="6"/>
+      <c r="G219" s="6"/>
+    </row>
+    <row r="220" customHeight="1" spans="1:7">
+      <c r="A220" s="2">
+        <f t="shared" si="3"/>
+        <v>214</v>
+      </c>
+      <c r="B220" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C220" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D220" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="E220" s="6"/>
+      <c r="F220" s="6"/>
+      <c r="G220" s="6"/>
+    </row>
+    <row r="221" customHeight="1" spans="1:7">
+      <c r="A221" s="2">
+        <f t="shared" si="3"/>
+        <v>215</v>
+      </c>
+      <c r="B221" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C221" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="D221" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="E221" s="6"/>
+      <c r="F221" s="6"/>
+      <c r="G221" s="6"/>
+    </row>
+    <row r="222" customHeight="1" spans="1:7">
+      <c r="A222" s="2">
+        <f t="shared" si="3"/>
+        <v>216</v>
+      </c>
+      <c r="B222" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C222" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="D222" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="E222" s="6"/>
+      <c r="F222" s="6"/>
+      <c r="G222" s="6"/>
+    </row>
+    <row r="223" customHeight="1" spans="1:7">
+      <c r="A223" s="2">
+        <f t="shared" si="3"/>
+        <v>217</v>
+      </c>
+      <c r="B223" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C223" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="D223" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="E223" s="6"/>
+      <c r="F223" s="6"/>
+      <c r="G223" s="6"/>
+    </row>
+    <row r="224" customHeight="1" spans="1:7">
+      <c r="A224" s="2">
+        <f t="shared" si="3"/>
+        <v>218</v>
+      </c>
+      <c r="B224" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C224" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D224" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="E224" s="6"/>
+      <c r="F224" s="6"/>
+      <c r="G224" s="6"/>
+    </row>
+    <row r="225" customHeight="1" spans="1:7">
+      <c r="A225" s="2">
+        <f t="shared" si="3"/>
+        <v>219</v>
+      </c>
+      <c r="B225" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C225" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="D225" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="E225" s="6"/>
+      <c r="F225" s="6"/>
+      <c r="G225" s="6"/>
+    </row>
+    <row r="226" customHeight="1" spans="1:7">
+      <c r="A226" s="2">
+        <f t="shared" si="3"/>
+        <v>220</v>
+      </c>
+      <c r="B226" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C226" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="D226" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="E226" s="6"/>
+      <c r="F226" s="6"/>
+      <c r="G226" s="6"/>
+    </row>
+    <row r="227" customHeight="1" spans="1:7">
+      <c r="A227" s="2">
+        <f t="shared" si="3"/>
+        <v>221</v>
+      </c>
+      <c r="B227" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C227" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="D227" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="E227" s="6"/>
+      <c r="F227" s="6"/>
+      <c r="G227" s="6"/>
+    </row>
+    <row r="228" customHeight="1" spans="1:7">
+      <c r="A228" s="2">
+        <f t="shared" si="3"/>
+        <v>222</v>
+      </c>
+      <c r="B228" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C228" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="D228" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="E228" s="6"/>
+      <c r="F228" s="6"/>
+      <c r="G228" s="6"/>
+    </row>
+    <row r="229" customHeight="1" spans="1:7">
+      <c r="A229" s="2">
+        <f t="shared" si="3"/>
+        <v>223</v>
+      </c>
+      <c r="B229" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C229" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D229" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="E229" s="6"/>
+      <c r="F229" s="6"/>
+      <c r="G229" s="6"/>
+    </row>
+    <row r="230" customHeight="1" spans="1:7">
+      <c r="A230" s="2">
+        <f t="shared" si="3"/>
+        <v>224</v>
+      </c>
+      <c r="B230" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C230" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D230" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="E230" s="6"/>
+      <c r="F230" s="6"/>
+      <c r="G230" s="6"/>
+    </row>
+    <row r="231" customHeight="1" spans="1:7">
+      <c r="A231" s="2">
+        <f t="shared" si="3"/>
+        <v>225</v>
+      </c>
+      <c r="B231" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C231" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="D231" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="E231" s="6"/>
+      <c r="F231" s="6"/>
+      <c r="G231" s="6"/>
+    </row>
+    <row r="232" customHeight="1" spans="1:7">
+      <c r="A232" s="2">
+        <f t="shared" si="3"/>
+        <v>226</v>
+      </c>
+      <c r="B232" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C232" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="D232" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="E232" s="6"/>
+      <c r="F232" s="6"/>
+      <c r="G232" s="6"/>
+    </row>
+    <row r="233" customHeight="1" spans="1:7">
+      <c r="A233" s="2">
+        <f t="shared" si="3"/>
+        <v>227</v>
+      </c>
+      <c r="B233" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C233" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D233" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="E233" s="6"/>
+      <c r="F233" s="6"/>
+      <c r="G233" s="6"/>
+    </row>
+    <row r="234" customHeight="1" spans="1:7">
+      <c r="A234" s="2">
+        <f t="shared" si="3"/>
+        <v>228</v>
+      </c>
+      <c r="B234" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C234" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D234" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="E234" s="6"/>
+      <c r="F234" s="6"/>
+      <c r="G234" s="6"/>
+    </row>
+    <row r="235" customHeight="1" spans="1:7">
+      <c r="A235" s="2">
+        <f t="shared" si="3"/>
+        <v>229</v>
+      </c>
+      <c r="B235" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C235" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="D235" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="E235" s="6"/>
+      <c r="F235" s="6"/>
+      <c r="G235" s="6"/>
+    </row>
+    <row r="236" customHeight="1" spans="1:7">
+      <c r="A236" s="2">
+        <f t="shared" si="3"/>
+        <v>230</v>
+      </c>
+      <c r="B236" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C236" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="D236" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="E236" s="6"/>
+      <c r="F236" s="6"/>
+      <c r="G236" s="6"/>
+    </row>
+    <row r="237" customHeight="1" spans="1:7">
+      <c r="A237" s="2">
+        <f t="shared" si="3"/>
+        <v>231</v>
+      </c>
+      <c r="B237" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C237" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="D237" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="E237" s="6"/>
+      <c r="F237" s="6"/>
+      <c r="G237" s="6"/>
+    </row>
+    <row r="238" customHeight="1" spans="1:7">
+      <c r="A238" s="2">
+        <f t="shared" si="3"/>
+        <v>232</v>
+      </c>
+      <c r="B238" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C238" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="D238" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="E238" s="6"/>
+      <c r="F238" s="6"/>
+      <c r="G238" s="6"/>
+    </row>
+    <row r="239" customHeight="1" spans="1:7">
+      <c r="A239" s="2">
+        <f t="shared" si="3"/>
+        <v>233</v>
+      </c>
+      <c r="B239" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C239" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="D239" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="E239" s="6"/>
+      <c r="F239" s="6"/>
+      <c r="G239" s="6"/>
+    </row>
+    <row r="240" customHeight="1" spans="1:7">
+      <c r="A240" s="2">
+        <f t="shared" si="3"/>
+        <v>234</v>
+      </c>
+      <c r="B240" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C240" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D240" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="E240" s="6"/>
+      <c r="F240" s="6"/>
+      <c r="G240" s="6"/>
+    </row>
+    <row r="241" customHeight="1" spans="1:7">
+      <c r="A241" s="2">
+        <f t="shared" si="3"/>
+        <v>235</v>
+      </c>
+      <c r="B241" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C241" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="D241" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="E241" s="6"/>
+      <c r="F241" s="6"/>
+      <c r="G241" s="6"/>
+    </row>
+    <row r="242" customHeight="1" spans="1:7">
+      <c r="A242" s="2">
+        <f t="shared" si="3"/>
+        <v>236</v>
+      </c>
+      <c r="B242" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C242" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="D242" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="E242" s="6"/>
+      <c r="F242" s="6"/>
+      <c r="G242" s="6"/>
+    </row>
+    <row r="243" customHeight="1" spans="1:7">
+      <c r="A243" s="2">
+        <f t="shared" si="3"/>
+        <v>237</v>
+      </c>
+      <c r="B243" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C243" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="D243" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="E243" s="6"/>
+      <c r="F243" s="6"/>
+      <c r="G243" s="6"/>
+    </row>
+    <row r="244" customHeight="1" spans="1:7">
+      <c r="A244" s="2">
+        <f t="shared" si="3"/>
+        <v>238</v>
+      </c>
+      <c r="B244" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C244" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="D244" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="E244" s="6"/>
+      <c r="F244" s="6"/>
+      <c r="G244" s="6"/>
+    </row>
+    <row r="245" customHeight="1" spans="1:7">
+      <c r="A245" s="2">
+        <f t="shared" si="3"/>
+        <v>239</v>
+      </c>
+      <c r="B245" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C245" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="D245" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="E245" s="6"/>
+      <c r="F245" s="6"/>
+      <c r="G245" s="6"/>
+    </row>
+    <row r="246" customHeight="1" spans="1:7">
+      <c r="A246" s="2">
+        <f t="shared" si="3"/>
+        <v>240</v>
+      </c>
+      <c r="B246" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C246" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="D246" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="E246" s="6"/>
+      <c r="F246" s="6"/>
+      <c r="G246" s="6"/>
+    </row>
+    <row r="247" customHeight="1" spans="1:7">
+      <c r="A247" s="2">
+        <f t="shared" si="3"/>
+        <v>241</v>
+      </c>
+      <c r="B247" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C247" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="D247" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="E247" s="6"/>
+      <c r="F247" s="6"/>
+      <c r="G247" s="6"/>
+    </row>
+    <row r="248" customHeight="1" spans="1:7">
+      <c r="A248" s="2">
+        <f t="shared" si="3"/>
+        <v>242</v>
+      </c>
+      <c r="B248" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C248" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="D248" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="E248" s="6"/>
+      <c r="F248" s="6"/>
+      <c r="G248" s="6"/>
+    </row>
+    <row r="249" customHeight="1" spans="1:7">
+      <c r="A249" s="2">
+        <f t="shared" si="3"/>
+        <v>243</v>
+      </c>
+      <c r="B249" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C249" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="D249" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="E249" s="6"/>
+      <c r="F249" s="6"/>
+      <c r="G249" s="6"/>
+    </row>
+    <row r="250" customHeight="1" spans="1:7">
+      <c r="A250" s="2">
+        <f t="shared" si="3"/>
+        <v>244</v>
+      </c>
+      <c r="B250" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C250" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="D250" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="E250" s="6"/>
+      <c r="F250" s="6"/>
+      <c r="G250" s="6"/>
+    </row>
+    <row r="251" customHeight="1" spans="1:7">
+      <c r="A251" s="2">
+        <f t="shared" si="3"/>
+        <v>245</v>
+      </c>
+      <c r="B251" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C251" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="D251" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="E251" s="6"/>
+      <c r="F251" s="6"/>
+      <c r="G251" s="6"/>
+    </row>
+    <row r="252" customHeight="1" spans="1:7">
+      <c r="A252" s="2">
+        <f t="shared" si="3"/>
+        <v>246</v>
+      </c>
+      <c r="B252" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C252" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="D252" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="E252" s="6"/>
+      <c r="F252" s="6"/>
+      <c r="G252" s="6"/>
+    </row>
+    <row r="253" customHeight="1" spans="1:7">
+      <c r="A253" s="2">
+        <f t="shared" si="3"/>
+        <v>247</v>
+      </c>
+      <c r="B253" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C253" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="D253" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="E253" s="6"/>
+      <c r="F253" s="6"/>
+      <c r="G253" s="6"/>
+    </row>
+    <row r="254" customHeight="1" spans="1:7">
+      <c r="A254" s="2">
+        <f t="shared" si="3"/>
+        <v>248</v>
+      </c>
+      <c r="B254" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C254" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="D254" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="E254" s="6"/>
+      <c r="F254" s="6"/>
+      <c r="G254" s="6"/>
+    </row>
+    <row r="255" customHeight="1" spans="1:7">
+      <c r="A255" s="2">
+        <f t="shared" ref="A255:A318" si="4">A254+1</f>
+        <v>249</v>
+      </c>
+      <c r="B255" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C255" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="D255" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="E255" s="6"/>
+      <c r="F255" s="6"/>
+      <c r="G255" s="6"/>
+    </row>
+    <row r="256" customHeight="1" spans="1:7">
+      <c r="A256" s="2">
+        <f t="shared" si="4"/>
+        <v>250</v>
+      </c>
+      <c r="B256" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C256" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="D256" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="E256" s="6"/>
+      <c r="F256" s="6"/>
+      <c r="G256" s="6"/>
+    </row>
+    <row r="257" customHeight="1" spans="1:7">
+      <c r="A257" s="2">
+        <f t="shared" si="4"/>
+        <v>251</v>
+      </c>
+      <c r="B257" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C257" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="D257" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="E257" s="6"/>
+      <c r="F257" s="6"/>
+      <c r="G257" s="6"/>
+    </row>
+    <row r="258" customHeight="1" spans="1:7">
+      <c r="A258" s="2">
+        <f t="shared" si="4"/>
+        <v>252</v>
+      </c>
+      <c r="B258" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C258" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="D258" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="E258" s="6"/>
+      <c r="F258" s="6"/>
+      <c r="G258" s="6"/>
+    </row>
+    <row r="259" customHeight="1" spans="1:7">
+      <c r="A259" s="2">
+        <f t="shared" si="4"/>
+        <v>253</v>
+      </c>
+      <c r="B259" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C259" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="D259" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="E259" s="6"/>
+      <c r="F259" s="6"/>
+      <c r="G259" s="6"/>
+    </row>
+    <row r="260" customHeight="1" spans="1:7">
+      <c r="A260" s="2">
+        <f t="shared" si="4"/>
+        <v>254</v>
+      </c>
+      <c r="B260" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C260" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="D260" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="E260" s="6"/>
+      <c r="F260" s="6"/>
+      <c r="G260" s="6"/>
+    </row>
+    <row r="261" customHeight="1" spans="1:7">
+      <c r="A261" s="2">
+        <f t="shared" si="4"/>
+        <v>255</v>
+      </c>
+      <c r="B261" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C261" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D261" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="E261" s="6"/>
+      <c r="F261" s="6"/>
+      <c r="G261" s="6"/>
+    </row>
+    <row r="262" customHeight="1" spans="1:7">
+      <c r="A262" s="2">
+        <f t="shared" si="4"/>
+        <v>256</v>
+      </c>
+      <c r="B262" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C262" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D262" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="E262" s="6"/>
+      <c r="F262" s="6"/>
+      <c r="G262" s="6"/>
+    </row>
+    <row r="263" customHeight="1" spans="1:7">
+      <c r="A263" s="2">
+        <f t="shared" si="4"/>
+        <v>257</v>
+      </c>
+      <c r="B263" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C263" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="D263" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="E263" s="6"/>
+      <c r="F263" s="6"/>
+      <c r="G263" s="6"/>
+    </row>
+    <row r="264" customHeight="1" spans="1:7">
+      <c r="A264" s="2">
+        <f t="shared" si="4"/>
+        <v>258</v>
+      </c>
+      <c r="B264" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C264" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="D264" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="E264" s="6"/>
+      <c r="F264" s="6"/>
+      <c r="G264" s="6"/>
+    </row>
+    <row r="265" customHeight="1" spans="1:7">
+      <c r="A265" s="2">
+        <f t="shared" si="4"/>
+        <v>259</v>
+      </c>
+      <c r="B265" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C265" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="D265" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="E265" s="6"/>
+      <c r="F265" s="6"/>
+      <c r="G265" s="6"/>
+    </row>
+    <row r="266" customHeight="1" spans="1:7">
+      <c r="A266" s="2">
+        <f t="shared" si="4"/>
+        <v>260</v>
+      </c>
+      <c r="B266" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C266" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D266" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="E266" s="6"/>
+      <c r="F266" s="6"/>
+      <c r="G266" s="6"/>
+    </row>
+    <row r="267" customHeight="1" spans="1:7">
+      <c r="A267" s="2">
+        <f t="shared" si="4"/>
+        <v>261</v>
+      </c>
+      <c r="B267" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C267" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D267" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="E267" s="6"/>
+      <c r="F267" s="6"/>
+      <c r="G267" s="6"/>
+    </row>
+    <row r="268" customHeight="1" spans="1:7">
+      <c r="A268" s="2">
+        <f t="shared" si="4"/>
+        <v>262</v>
+      </c>
+      <c r="B268" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C268" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="D268" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="E268" s="6"/>
+      <c r="F268" s="6"/>
+      <c r="G268" s="6"/>
+    </row>
+    <row r="269" customHeight="1" spans="1:7">
+      <c r="A269" s="2">
+        <f t="shared" si="4"/>
+        <v>263</v>
+      </c>
+      <c r="B269" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C269" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D269" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="E269" s="6"/>
+      <c r="F269" s="6"/>
+      <c r="G269" s="6"/>
+    </row>
+    <row r="270" customHeight="1" spans="1:7">
+      <c r="A270" s="2">
+        <f t="shared" si="4"/>
+        <v>264</v>
+      </c>
+      <c r="B270" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C270" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="D270" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="E270" s="6"/>
+      <c r="F270" s="6"/>
+      <c r="G270" s="6"/>
+    </row>
+    <row r="271" customHeight="1" spans="1:7">
+      <c r="A271" s="2">
+        <f t="shared" si="4"/>
+        <v>265</v>
+      </c>
+      <c r="B271" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C271" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="D271" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="E271" s="6"/>
+      <c r="F271" s="6"/>
+      <c r="G271" s="6"/>
+    </row>
+    <row r="272" customHeight="1" spans="1:7">
+      <c r="A272" s="2">
+        <f t="shared" si="4"/>
+        <v>266</v>
+      </c>
+      <c r="B272" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C272" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D272" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="E272" s="6"/>
+      <c r="F272" s="6"/>
+      <c r="G272" s="6"/>
+    </row>
+    <row r="273" customHeight="1" spans="1:7">
+      <c r="A273" s="2">
+        <f t="shared" si="4"/>
+        <v>267</v>
+      </c>
+      <c r="B273" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C273" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D273" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="E273" s="6"/>
+      <c r="F273" s="6"/>
+      <c r="G273" s="6"/>
+    </row>
+    <row r="274" customHeight="1" spans="1:7">
+      <c r="A274" s="2">
+        <f t="shared" si="4"/>
+        <v>268</v>
+      </c>
+      <c r="B274" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C274" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="D274" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="E274" s="6"/>
+      <c r="F274" s="6"/>
+      <c r="G274" s="6"/>
+    </row>
+    <row r="275" customHeight="1" spans="1:7">
+      <c r="A275" s="2">
+        <f t="shared" si="4"/>
+        <v>269</v>
+      </c>
+      <c r="B275" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C275" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="D275" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="E275" s="6"/>
+      <c r="F275" s="6"/>
+      <c r="G275" s="6"/>
+    </row>
+    <row r="276" customHeight="1" spans="1:7">
+      <c r="A276" s="2">
+        <f t="shared" si="4"/>
+        <v>270</v>
+      </c>
+      <c r="B276" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C276" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="D276" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="E276" s="6"/>
+      <c r="F276" s="6"/>
+      <c r="G276" s="6"/>
+    </row>
+    <row r="277" customHeight="1" spans="1:7">
+      <c r="A277" s="2">
+        <f t="shared" si="4"/>
+        <v>271</v>
+      </c>
+      <c r="B277" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C277" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="D277" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="E277" s="6"/>
+      <c r="F277" s="6"/>
+      <c r="G277" s="6"/>
+    </row>
+    <row r="278" customHeight="1" spans="1:7">
+      <c r="A278" s="2">
+        <f t="shared" si="4"/>
+        <v>272</v>
+      </c>
+      <c r="B278" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C278" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="D278" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="E278" s="6"/>
+      <c r="F278" s="6"/>
+      <c r="G278" s="6"/>
+    </row>
+    <row r="279" customHeight="1" spans="1:7">
+      <c r="A279" s="2">
+        <f t="shared" si="4"/>
+        <v>273</v>
+      </c>
+      <c r="B279" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C279" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="D279" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="E279" s="6"/>
+      <c r="F279" s="6"/>
+      <c r="G279" s="6"/>
+    </row>
+    <row r="280" customHeight="1" spans="1:7">
+      <c r="A280" s="2">
+        <f t="shared" si="4"/>
+        <v>274</v>
+      </c>
+      <c r="B280" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C280" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="D280" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="E280" s="6"/>
+      <c r="F280" s="6"/>
+      <c r="G280" s="6"/>
+    </row>
+    <row r="281" customHeight="1" spans="1:7">
+      <c r="A281" s="2">
+        <f t="shared" si="4"/>
+        <v>275</v>
+      </c>
+      <c r="B281" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C281" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="D281" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="E281" s="6"/>
+      <c r="F281" s="6"/>
+      <c r="G281" s="6"/>
+    </row>
+    <row r="282" customHeight="1" spans="1:7">
+      <c r="A282" s="2">
+        <f t="shared" si="4"/>
+        <v>276</v>
+      </c>
+      <c r="B282" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C282" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="D282" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="E282" s="6"/>
+      <c r="F282" s="6"/>
+      <c r="G282" s="6"/>
+    </row>
+    <row r="283" customHeight="1" spans="1:7">
+      <c r="A283" s="2">
+        <f t="shared" si="4"/>
+        <v>277</v>
+      </c>
+      <c r="B283" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C283" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="D283" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="E283" s="6"/>
+      <c r="F283" s="6"/>
+      <c r="G283" s="6"/>
+    </row>
+    <row r="284" customHeight="1" spans="1:7">
+      <c r="A284" s="2">
+        <f t="shared" si="4"/>
+        <v>278</v>
+      </c>
+      <c r="B284" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C284" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="D284" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="E284" s="6"/>
+      <c r="F284" s="6"/>
+      <c r="G284" s="6"/>
+    </row>
+    <row r="285" customHeight="1" spans="1:7">
+      <c r="A285" s="2">
+        <f t="shared" si="4"/>
+        <v>279</v>
+      </c>
+      <c r="B285" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C285" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="D285" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="E285" s="6"/>
+      <c r="F285" s="6"/>
+      <c r="G285" s="6"/>
+    </row>
+    <row r="286" customHeight="1" spans="1:7">
+      <c r="A286" s="2">
+        <f t="shared" si="4"/>
+        <v>280</v>
+      </c>
+      <c r="B286" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C286" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="D286" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="E286" s="6"/>
+      <c r="F286" s="6"/>
+      <c r="G286" s="6"/>
+    </row>
+    <row r="287" customHeight="1" spans="1:7">
+      <c r="A287" s="2">
+        <f t="shared" si="4"/>
+        <v>281</v>
+      </c>
+      <c r="B287" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C287" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="D287" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="E287" s="6"/>
+      <c r="F287" s="6"/>
+      <c r="G287" s="6"/>
+    </row>
+    <row r="288" customHeight="1" spans="1:7">
+      <c r="A288" s="2">
+        <f t="shared" si="4"/>
+        <v>282</v>
+      </c>
+      <c r="B288" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C288" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="D288" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="E288" s="6"/>
+      <c r="F288" s="6"/>
+      <c r="G288" s="6"/>
+    </row>
+    <row r="289" customHeight="1" spans="1:7">
+      <c r="A289" s="2">
+        <f t="shared" si="4"/>
+        <v>283</v>
+      </c>
+      <c r="B289" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C289" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="D289" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="E289" s="6"/>
+      <c r="F289" s="6"/>
+      <c r="G289" s="6"/>
+    </row>
+    <row r="290" customHeight="1" spans="1:7">
+      <c r="A290" s="2">
+        <f t="shared" si="4"/>
+        <v>284</v>
+      </c>
+      <c r="B290" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C290" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="D290" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="E290" s="6"/>
+      <c r="F290" s="6"/>
+      <c r="G290" s="6"/>
+    </row>
+    <row r="291" customHeight="1" spans="1:7">
+      <c r="A291" s="2">
+        <f t="shared" si="4"/>
+        <v>285</v>
+      </c>
+      <c r="B291" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C291" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="D291" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="E291" s="6"/>
+      <c r="F291" s="6"/>
+      <c r="G291" s="6"/>
+    </row>
+    <row r="292" customHeight="1" spans="1:7">
+      <c r="A292" s="2">
+        <f t="shared" si="4"/>
+        <v>286</v>
+      </c>
+      <c r="B292" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C292" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="D292" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="E292" s="6"/>
+      <c r="F292" s="6"/>
+      <c r="G292" s="6"/>
+    </row>
+    <row r="293" customHeight="1" spans="1:7">
+      <c r="A293" s="2">
+        <f t="shared" si="4"/>
+        <v>287</v>
+      </c>
+      <c r="B293" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C293" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D293" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="E293" s="6"/>
+      <c r="F293" s="6"/>
+      <c r="G293" s="6"/>
+    </row>
+    <row r="294" customHeight="1" spans="1:7">
+      <c r="A294" s="2">
+        <f t="shared" si="4"/>
+        <v>288</v>
+      </c>
+      <c r="B294" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C294" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="D294" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="E294" s="6"/>
+      <c r="F294" s="6"/>
+      <c r="G294" s="6"/>
+    </row>
+    <row r="295" customHeight="1" spans="1:7">
+      <c r="A295" s="2">
+        <f t="shared" si="4"/>
+        <v>289</v>
+      </c>
+      <c r="B295" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C295" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="D295" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="E295" s="6"/>
+      <c r="F295" s="6"/>
+      <c r="G295" s="6"/>
+    </row>
+    <row r="296" customHeight="1" spans="1:7">
+      <c r="A296" s="2">
+        <f t="shared" si="4"/>
+        <v>290</v>
+      </c>
+      <c r="B296" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C296" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="D296" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="E296" s="6"/>
+      <c r="F296" s="6"/>
+      <c r="G296" s="6"/>
+    </row>
+    <row r="297" customHeight="1" spans="1:7">
+      <c r="A297" s="2">
+        <f t="shared" si="4"/>
+        <v>291</v>
+      </c>
+      <c r="B297" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C297" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="D297" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="E297" s="6"/>
+      <c r="F297" s="6"/>
+      <c r="G297" s="6"/>
+    </row>
+    <row r="298" customHeight="1" spans="1:7">
+      <c r="A298" s="2">
+        <f t="shared" si="4"/>
+        <v>292</v>
+      </c>
+      <c r="B298" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C298" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="D298" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="E298" s="6"/>
+      <c r="F298" s="6"/>
+      <c r="G298" s="6"/>
+    </row>
+    <row r="299" customHeight="1" spans="1:7">
+      <c r="A299" s="2">
+        <f t="shared" si="4"/>
+        <v>293</v>
+      </c>
+      <c r="B299" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C299" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="D299" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="E299" s="6"/>
+      <c r="F299" s="6"/>
+      <c r="G299" s="6"/>
+    </row>
+    <row r="300" customHeight="1" spans="1:7">
+      <c r="A300" s="2">
+        <f t="shared" si="4"/>
+        <v>294</v>
+      </c>
+      <c r="B300" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C300" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="D300" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="E300" s="6"/>
+      <c r="F300" s="6"/>
+      <c r="G300" s="6"/>
+    </row>
+    <row r="301" customHeight="1" spans="1:7">
+      <c r="A301" s="2">
+        <f t="shared" si="4"/>
+        <v>295</v>
+      </c>
+      <c r="B301" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C301" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D301" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="E301" s="6"/>
+      <c r="F301" s="6"/>
+      <c r="G301" s="6"/>
+    </row>
+    <row r="302" customHeight="1" spans="1:7">
+      <c r="A302" s="2">
+        <f t="shared" si="4"/>
+        <v>296</v>
+      </c>
+      <c r="B302" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C302" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="D302" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="E302" s="6"/>
+      <c r="F302" s="6"/>
+      <c r="G302" s="6"/>
+    </row>
+    <row r="303" customHeight="1" spans="1:7">
+      <c r="A303" s="2">
+        <f t="shared" si="4"/>
+        <v>297</v>
+      </c>
+      <c r="B303" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C303" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="D303" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="E303" s="6"/>
+      <c r="F303" s="6"/>
+      <c r="G303" s="6"/>
+    </row>
+    <row r="304" customHeight="1" spans="1:7">
+      <c r="A304" s="2">
+        <f t="shared" si="4"/>
+        <v>298</v>
+      </c>
+      <c r="B304" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C304" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D304" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="E304" s="6"/>
+      <c r="F304" s="6"/>
+      <c r="G304" s="6"/>
+    </row>
+    <row r="305" customHeight="1" spans="1:7">
+      <c r="A305" s="2">
+        <f t="shared" si="4"/>
+        <v>299</v>
+      </c>
+      <c r="B305" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C305" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="D305" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="E305" s="6"/>
+      <c r="F305" s="6"/>
+      <c r="G305" s="6"/>
+    </row>
+    <row r="306" customHeight="1" spans="1:7">
+      <c r="A306" s="2">
+        <f t="shared" si="4"/>
+        <v>300</v>
+      </c>
+      <c r="B306" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C306" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="D306" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="E306" s="6"/>
+      <c r="F306" s="6"/>
+      <c r="G306" s="6"/>
+    </row>
+    <row r="307" customHeight="1" spans="1:7">
+      <c r="A307" s="2">
+        <f t="shared" si="4"/>
+        <v>301</v>
+      </c>
+      <c r="B307" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C307" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="D307" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="E307" s="6"/>
+      <c r="F307" s="6"/>
+      <c r="G307" s="6"/>
+    </row>
+    <row r="308" customHeight="1" spans="1:7">
+      <c r="A308" s="2">
+        <f t="shared" si="4"/>
+        <v>302</v>
+      </c>
+      <c r="B308" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C308" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="D308" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="E308" s="6"/>
+      <c r="F308" s="6"/>
+      <c r="G308" s="6"/>
+    </row>
+    <row r="309" customHeight="1" spans="1:7">
+      <c r="A309" s="2">
+        <f t="shared" si="4"/>
+        <v>303</v>
+      </c>
+      <c r="B309" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C309" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="D309" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="E309" s="6"/>
+      <c r="F309" s="6"/>
+      <c r="G309" s="6"/>
+    </row>
+    <row r="310" customHeight="1" spans="1:7">
+      <c r="A310" s="2">
+        <f t="shared" si="4"/>
+        <v>304</v>
+      </c>
+      <c r="B310" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C310" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="D310" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="E310" s="6"/>
+      <c r="F310" s="6"/>
+      <c r="G310" s="6"/>
+    </row>
+    <row r="311" customHeight="1" spans="1:7">
+      <c r="A311" s="2">
+        <f t="shared" si="4"/>
+        <v>305</v>
+      </c>
+      <c r="B311" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C311" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="D311" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="E311" s="6"/>
+      <c r="F311" s="6"/>
+      <c r="G311" s="6"/>
+    </row>
+    <row r="312" customHeight="1" spans="1:7">
+      <c r="A312" s="2">
+        <f t="shared" si="4"/>
+        <v>306</v>
+      </c>
+      <c r="B312" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C312" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="D312" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="E312" s="6"/>
+      <c r="F312" s="6"/>
+      <c r="G312" s="6"/>
+    </row>
+    <row r="313" customHeight="1" spans="1:7">
+      <c r="A313" s="2">
+        <f t="shared" si="4"/>
+        <v>307</v>
+      </c>
+      <c r="B313" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C313" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D313" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="E313" s="6"/>
+      <c r="F313" s="6"/>
+      <c r="G313" s="6"/>
+    </row>
+    <row r="314" customHeight="1" spans="1:7">
+      <c r="A314" s="2">
+        <f t="shared" si="4"/>
+        <v>308</v>
+      </c>
+      <c r="B314" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C314" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="D314" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="E314" s="6"/>
+      <c r="F314" s="6"/>
+      <c r="G314" s="6"/>
+    </row>
+    <row r="315" customHeight="1" spans="1:7">
+      <c r="A315" s="2">
+        <f t="shared" si="4"/>
+        <v>309</v>
+      </c>
+      <c r="B315" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C315" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="D315" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="E315" s="6"/>
+      <c r="F315" s="6"/>
+      <c r="G315" s="6"/>
+    </row>
+    <row r="316" customHeight="1" spans="1:7">
+      <c r="A316" s="2">
+        <f t="shared" si="4"/>
+        <v>310</v>
+      </c>
+      <c r="B316" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C316" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="D316" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="E316" s="6"/>
+      <c r="F316" s="6"/>
+      <c r="G316" s="6"/>
+    </row>
+    <row r="317" customHeight="1" spans="1:7">
+      <c r="A317" s="2">
+        <f t="shared" si="4"/>
+        <v>311</v>
+      </c>
+      <c r="B317" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C317" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="D317" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="E317" s="6"/>
+      <c r="F317" s="6"/>
+      <c r="G317" s="6"/>
+    </row>
+    <row r="318" customHeight="1" spans="1:7">
+      <c r="A318" s="2">
+        <f t="shared" si="4"/>
+        <v>312</v>
+      </c>
+      <c r="B318" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C318" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="D318" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="E318" s="6"/>
+      <c r="F318" s="6"/>
+      <c r="G318" s="6"/>
+    </row>
+    <row r="319" customHeight="1" spans="1:7">
+      <c r="A319" s="2">
+        <f t="shared" ref="A319:A382" si="5">A318+1</f>
+        <v>313</v>
+      </c>
+      <c r="B319" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C319" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="D319" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="E319" s="6"/>
+      <c r="F319" s="6"/>
+      <c r="G319" s="6"/>
+    </row>
+    <row r="320" customHeight="1" spans="1:7">
+      <c r="A320" s="2">
+        <f t="shared" si="5"/>
+        <v>314</v>
+      </c>
+      <c r="B320" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C320" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="D320" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="E320" s="6"/>
+      <c r="F320" s="6"/>
+      <c r="G320" s="6"/>
+    </row>
+    <row r="321" customHeight="1" spans="1:7">
+      <c r="A321" s="2">
+        <f t="shared" si="5"/>
+        <v>315</v>
+      </c>
+      <c r="B321" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C321" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="D321" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="E321" s="6"/>
+      <c r="F321" s="6"/>
+      <c r="G321" s="6"/>
+    </row>
+    <row r="322" customHeight="1" spans="1:7">
+      <c r="A322" s="2">
+        <f t="shared" si="5"/>
+        <v>316</v>
+      </c>
+      <c r="B322" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C322" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="D322" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="E322" s="6"/>
+      <c r="F322" s="6"/>
+      <c r="G322" s="6"/>
+    </row>
+    <row r="323" customHeight="1" spans="1:7">
+      <c r="A323" s="2">
+        <f t="shared" si="5"/>
+        <v>317</v>
+      </c>
+      <c r="B323" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C323" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="D323" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="E323" s="6"/>
+      <c r="F323" s="6"/>
+      <c r="G323" s="6"/>
+    </row>
+    <row r="324" customHeight="1" spans="1:7">
+      <c r="A324" s="2">
+        <f t="shared" si="5"/>
+        <v>318</v>
+      </c>
+      <c r="B324" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C324" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D324" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="E324" s="6"/>
+      <c r="F324" s="6"/>
+      <c r="G324" s="6"/>
+    </row>
+    <row r="325" customHeight="1" spans="1:7">
+      <c r="A325" s="2">
+        <f t="shared" si="5"/>
+        <v>319</v>
+      </c>
+      <c r="B325" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C325" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="D325" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="E325" s="6"/>
+      <c r="F325" s="6"/>
+      <c r="G325" s="6"/>
+    </row>
+    <row r="326" customHeight="1" spans="1:7">
+      <c r="A326" s="2">
+        <f t="shared" si="5"/>
+        <v>320</v>
+      </c>
+      <c r="B326" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C326" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="D326" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="E326" s="6"/>
+      <c r="F326" s="6"/>
+      <c r="G326" s="6"/>
+    </row>
+    <row r="327" customHeight="1" spans="1:7">
+      <c r="A327" s="2">
+        <f t="shared" si="5"/>
+        <v>321</v>
+      </c>
+      <c r="B327" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C327" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="D327" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="E327" s="6"/>
+      <c r="F327" s="6"/>
+      <c r="G327" s="6"/>
+    </row>
+    <row r="328" customHeight="1" spans="1:7">
+      <c r="A328" s="2">
+        <f t="shared" si="5"/>
+        <v>322</v>
+      </c>
+      <c r="B328" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C328" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="D328" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="E328" s="6"/>
+      <c r="F328" s="6"/>
+      <c r="G328" s="6"/>
+    </row>
+    <row r="329" customHeight="1" spans="1:7">
+      <c r="A329" s="2">
+        <f t="shared" si="5"/>
+        <v>323</v>
+      </c>
+      <c r="B329" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C329" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="D329" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="E329" s="6"/>
+      <c r="F329" s="6"/>
+      <c r="G329" s="6"/>
+    </row>
+    <row r="330" customHeight="1" spans="1:7">
+      <c r="A330" s="2">
+        <f t="shared" si="5"/>
+        <v>324</v>
+      </c>
+      <c r="B330" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C330" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="D330" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="E330" s="6"/>
+      <c r="F330" s="6"/>
+      <c r="G330" s="6"/>
+    </row>
+    <row r="331" customHeight="1" spans="1:7">
+      <c r="A331" s="2">
+        <f t="shared" si="5"/>
+        <v>325</v>
+      </c>
+      <c r="B331" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C331" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="D331" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="E331" s="6"/>
+      <c r="F331" s="6"/>
+      <c r="G331" s="6"/>
+    </row>
+    <row r="332" customHeight="1" spans="1:7">
+      <c r="A332" s="2">
+        <f t="shared" si="5"/>
+        <v>326</v>
+      </c>
+      <c r="B332" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C332" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="D332" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="E332" s="6"/>
+      <c r="F332" s="6"/>
+      <c r="G332" s="6"/>
+    </row>
+    <row r="333" customHeight="1" spans="1:7">
+      <c r="A333" s="2">
+        <f t="shared" si="5"/>
+        <v>327</v>
+      </c>
+      <c r="B333" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C333" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="D333" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="E333" s="6"/>
+      <c r="F333" s="6"/>
+      <c r="G333" s="6"/>
+    </row>
+    <row r="334" customHeight="1" spans="1:7">
+      <c r="A334" s="2">
+        <f t="shared" si="5"/>
+        <v>328</v>
+      </c>
+      <c r="B334" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C334" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="D334" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="E334" s="6"/>
+      <c r="F334" s="6"/>
+      <c r="G334" s="6"/>
+    </row>
+    <row r="335" customHeight="1" spans="1:7">
+      <c r="A335" s="2">
+        <f t="shared" si="5"/>
+        <v>329</v>
+      </c>
+      <c r="B335" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C335" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D335" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="E335" s="6"/>
+      <c r="F335" s="6"/>
+      <c r="G335" s="6"/>
+    </row>
+    <row r="336" customHeight="1" spans="1:7">
+      <c r="A336" s="2">
+        <f t="shared" si="5"/>
+        <v>330</v>
+      </c>
+      <c r="B336" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C336" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="D336" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="E336" s="6"/>
+      <c r="F336" s="6"/>
+      <c r="G336" s="6"/>
+    </row>
+    <row r="337" customHeight="1" spans="1:7">
+      <c r="A337" s="2">
+        <f t="shared" si="5"/>
+        <v>331</v>
+      </c>
+      <c r="B337" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C337" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="D337" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="E337" s="6"/>
+      <c r="F337" s="6"/>
+      <c r="G337" s="6"/>
+    </row>
+    <row r="338" customHeight="1" spans="1:7">
+      <c r="A338" s="2">
+        <f t="shared" si="5"/>
+        <v>332</v>
+      </c>
+      <c r="B338" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C338" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="D338" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="E338" s="6"/>
+      <c r="F338" s="6"/>
+      <c r="G338" s="6"/>
+    </row>
+    <row r="339" customHeight="1" spans="1:7">
+      <c r="A339" s="2">
+        <f t="shared" si="5"/>
+        <v>333</v>
+      </c>
+      <c r="B339" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C339" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="D339" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="E339" s="6"/>
+      <c r="F339" s="6"/>
+      <c r="G339" s="6"/>
+    </row>
+    <row r="340" customHeight="1" spans="1:7">
+      <c r="A340" s="2">
+        <f t="shared" si="5"/>
+        <v>334</v>
+      </c>
+      <c r="B340" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C340" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="D340" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="E340" s="6"/>
+      <c r="F340" s="6"/>
+      <c r="G340" s="6"/>
+    </row>
+    <row r="341" customHeight="1" spans="1:7">
+      <c r="A341" s="2">
+        <f t="shared" si="5"/>
+        <v>335</v>
+      </c>
+      <c r="B341" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C341" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="D341" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="E341" s="6"/>
+      <c r="F341" s="6"/>
+      <c r="G341" s="6"/>
+    </row>
+    <row r="342" customHeight="1" spans="1:7">
+      <c r="A342" s="2">
+        <f t="shared" si="5"/>
+        <v>336</v>
+      </c>
+      <c r="B342" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C342" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="D342" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="E342" s="6"/>
+      <c r="F342" s="6"/>
+      <c r="G342" s="6"/>
+    </row>
+    <row r="343" customHeight="1" spans="1:7">
+      <c r="A343" s="2">
+        <f t="shared" si="5"/>
+        <v>337</v>
+      </c>
+      <c r="B343" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C343" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="D343" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="E343" s="6"/>
+      <c r="F343" s="6"/>
+      <c r="G343" s="6"/>
+    </row>
+    <row r="344" customHeight="1" spans="1:7">
+      <c r="A344" s="2">
+        <f t="shared" si="5"/>
+        <v>338</v>
+      </c>
+      <c r="B344" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C344" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="D344" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="E344" s="6"/>
+      <c r="F344" s="6"/>
+      <c r="G344" s="6"/>
+    </row>
+    <row r="345" customHeight="1" spans="1:7">
+      <c r="A345" s="2">
+        <f t="shared" si="5"/>
+        <v>339</v>
+      </c>
+      <c r="B345" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C345" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="D345" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="E345" s="6"/>
+      <c r="F345" s="6"/>
+      <c r="G345" s="6"/>
+    </row>
+    <row r="346" customHeight="1" spans="1:7">
+      <c r="A346" s="2">
+        <f t="shared" si="5"/>
+        <v>340</v>
+      </c>
+      <c r="B346" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C346" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="D346" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="E346" s="6"/>
+      <c r="F346" s="6"/>
+      <c r="G346" s="6"/>
+    </row>
+    <row r="347" customHeight="1" spans="1:7">
+      <c r="A347" s="2">
+        <f t="shared" si="5"/>
+        <v>341</v>
+      </c>
+      <c r="B347" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C347" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="D347" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="E347" s="6"/>
+      <c r="F347" s="6"/>
+      <c r="G347" s="6"/>
+    </row>
+    <row r="348" customHeight="1" spans="1:7">
+      <c r="A348" s="2">
+        <f t="shared" si="5"/>
+        <v>342</v>
+      </c>
+      <c r="B348" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C348" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="D348" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="E348" s="6"/>
+      <c r="F348" s="6"/>
+      <c r="G348" s="6"/>
+    </row>
+    <row r="349" customHeight="1" spans="1:7">
+      <c r="A349" s="2">
+        <f t="shared" si="5"/>
+        <v>343</v>
+      </c>
+      <c r="B349" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C349" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="D349" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="E349" s="6"/>
+      <c r="F349" s="6"/>
+      <c r="G349" s="6"/>
+    </row>
+    <row r="350" customHeight="1" spans="1:7">
+      <c r="A350" s="2">
+        <f t="shared" si="5"/>
+        <v>344</v>
+      </c>
+      <c r="B350" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C350" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="D350" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="E350" s="6"/>
+      <c r="F350" s="6"/>
+      <c r="G350" s="6"/>
+    </row>
+    <row r="351" customHeight="1" spans="1:7">
+      <c r="A351" s="2">
+        <f t="shared" si="5"/>
+        <v>345</v>
+      </c>
+      <c r="B351" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C351" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="D351" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="E351" s="6"/>
+      <c r="F351" s="6"/>
+      <c r="G351" s="6"/>
+    </row>
+    <row r="352" customHeight="1" spans="1:7">
+      <c r="A352" s="2">
+        <f t="shared" si="5"/>
+        <v>346</v>
+      </c>
+      <c r="B352" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C352" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D352" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="E352" s="6"/>
+      <c r="F352" s="6"/>
+      <c r="G352" s="6"/>
+    </row>
+    <row r="353" customHeight="1" spans="1:7">
+      <c r="A353" s="2">
+        <f t="shared" si="5"/>
+        <v>347</v>
+      </c>
+      <c r="B353" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C353" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="D353" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="E353" s="6"/>
+      <c r="F353" s="6"/>
+      <c r="G353" s="6"/>
+    </row>
+    <row r="354" customHeight="1" spans="1:7">
+      <c r="A354" s="2">
+        <f t="shared" si="5"/>
+        <v>348</v>
+      </c>
+      <c r="B354" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C354" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D354" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="E354" s="6"/>
+      <c r="F354" s="6"/>
+      <c r="G354" s="6"/>
+    </row>
+    <row r="355" customHeight="1" spans="1:7">
+      <c r="A355" s="2">
+        <f t="shared" si="5"/>
+        <v>349</v>
+      </c>
+      <c r="B355" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C355" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D355" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="E355" s="6"/>
+      <c r="F355" s="6"/>
+      <c r="G355" s="6"/>
+    </row>
+    <row r="356" customHeight="1" spans="1:7">
+      <c r="A356" s="2">
+        <f t="shared" si="5"/>
+        <v>350</v>
+      </c>
+      <c r="B356" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C356" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D356" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="E356" s="6"/>
+      <c r="F356" s="6"/>
+      <c r="G356" s="6"/>
+    </row>
+    <row r="357" customHeight="1" spans="1:7">
+      <c r="A357" s="2">
+        <f t="shared" si="5"/>
+        <v>351</v>
+      </c>
+      <c r="B357" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C357" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D357" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="E357" s="6"/>
+      <c r="F357" s="6"/>
+      <c r="G357" s="6"/>
+    </row>
+    <row r="358" customHeight="1" spans="1:7">
+      <c r="A358" s="2">
+        <f t="shared" si="5"/>
+        <v>352</v>
+      </c>
+      <c r="B358" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C358" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D358" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="E358" s="6"/>
+      <c r="F358" s="6"/>
+      <c r="G358" s="6"/>
+    </row>
+    <row r="359" customHeight="1" spans="1:7">
+      <c r="A359" s="2">
+        <f t="shared" si="5"/>
+        <v>353</v>
+      </c>
+      <c r="B359" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C359" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="D359" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="E359" s="6"/>
+      <c r="F359" s="6"/>
+      <c r="G359" s="6"/>
+    </row>
+    <row r="360" customHeight="1" spans="1:7">
+      <c r="A360" s="2">
+        <f t="shared" si="5"/>
+        <v>354</v>
+      </c>
+      <c r="B360" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C360" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D360" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="E360" s="6"/>
+      <c r="F360" s="6"/>
+      <c r="G360" s="6"/>
+    </row>
+    <row r="361" customHeight="1" spans="1:7">
+      <c r="A361" s="2">
+        <f t="shared" si="5"/>
+        <v>355</v>
+      </c>
+      <c r="B361" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C361" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="D361" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="E361" s="6"/>
+      <c r="F361" s="6"/>
+      <c r="G361" s="6"/>
+    </row>
+    <row r="362" customHeight="1" spans="1:7">
+      <c r="A362" s="2">
+        <f t="shared" si="5"/>
+        <v>356</v>
+      </c>
+      <c r="B362" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C362" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D362" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="E362" s="6"/>
+      <c r="F362" s="6"/>
+      <c r="G362" s="6"/>
+    </row>
+    <row r="363" customHeight="1" spans="1:7">
+      <c r="A363" s="2">
+        <f t="shared" si="5"/>
+        <v>357</v>
+      </c>
+      <c r="B363" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C363" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D363" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="E363" s="6"/>
+      <c r="F363" s="6"/>
+      <c r="G363" s="6"/>
+    </row>
+    <row r="364" customHeight="1" spans="1:7">
+      <c r="A364" s="2">
+        <f t="shared" si="5"/>
+        <v>358</v>
+      </c>
+      <c r="B364" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C364" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D364" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="E364" s="6"/>
+      <c r="F364" s="6"/>
+      <c r="G364" s="6"/>
+    </row>
+    <row r="365" customHeight="1" spans="1:7">
+      <c r="A365" s="2">
+        <f t="shared" si="5"/>
+        <v>359</v>
+      </c>
+      <c r="B365" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C365" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="D365" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="E365" s="6"/>
+      <c r="F365" s="6"/>
+      <c r="G365" s="6"/>
+    </row>
+    <row r="366" customHeight="1" spans="1:7">
+      <c r="A366" s="2">
+        <f t="shared" si="5"/>
+        <v>360</v>
+      </c>
+      <c r="B366" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C366" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="D366" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="E366" s="6"/>
+      <c r="F366" s="6"/>
+      <c r="G366" s="6"/>
+    </row>
+    <row r="367" customHeight="1" spans="1:7">
+      <c r="A367" s="2">
+        <f t="shared" si="5"/>
+        <v>361</v>
+      </c>
+      <c r="B367" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C367" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="D367" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="E367" s="6"/>
+      <c r="F367" s="6"/>
+      <c r="G367" s="6"/>
+    </row>
+    <row r="368" customHeight="1" spans="1:7">
+      <c r="A368" s="2">
+        <f t="shared" si="5"/>
+        <v>362</v>
+      </c>
+      <c r="B368" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C368" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="D368" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="E368" s="6"/>
+      <c r="F368" s="6"/>
+      <c r="G368" s="6"/>
+    </row>
+    <row r="369" customHeight="1" spans="1:7">
+      <c r="A369" s="2">
+        <f t="shared" si="5"/>
+        <v>363</v>
+      </c>
+      <c r="B369" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C369" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="D369" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="E369" s="6"/>
+      <c r="F369" s="6"/>
+      <c r="G369" s="6"/>
+    </row>
+    <row r="370" customHeight="1" spans="1:7">
+      <c r="A370" s="2">
+        <f t="shared" si="5"/>
+        <v>364</v>
+      </c>
+      <c r="B370" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C370" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="D370" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="E370" s="6"/>
+      <c r="F370" s="6"/>
+      <c r="G370" s="6"/>
+    </row>
+    <row r="371" customHeight="1" spans="1:7">
+      <c r="A371" s="2">
+        <f t="shared" si="5"/>
+        <v>365</v>
+      </c>
+      <c r="B371" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C371" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="D371" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="E371" s="6"/>
+      <c r="F371" s="6"/>
+      <c r="G371" s="6"/>
+    </row>
+    <row r="372" customHeight="1" spans="1:7">
+      <c r="A372" s="2">
+        <f t="shared" si="5"/>
+        <v>366</v>
+      </c>
+      <c r="B372" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C372" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="D372" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="E372" s="6"/>
+      <c r="F372" s="6"/>
+      <c r="G372" s="6"/>
+    </row>
+    <row r="373" customHeight="1" spans="1:7">
+      <c r="A373" s="2">
+        <f t="shared" si="5"/>
+        <v>367</v>
+      </c>
+      <c r="B373" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C373" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="D373" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="E373" s="6"/>
+      <c r="F373" s="6"/>
+      <c r="G373" s="6"/>
+    </row>
+    <row r="374" customHeight="1" spans="1:7">
+      <c r="A374" s="2">
+        <f t="shared" si="5"/>
+        <v>368</v>
+      </c>
+      <c r="B374" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C374" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="D374" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="E374" s="6"/>
+      <c r="F374" s="6"/>
+      <c r="G374" s="6"/>
+    </row>
+    <row r="375" customHeight="1" spans="1:7">
+      <c r="A375" s="2">
+        <f t="shared" si="5"/>
+        <v>369</v>
+      </c>
+      <c r="B375" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C375" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="D375" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="E375" s="6"/>
+      <c r="F375" s="6"/>
+      <c r="G375" s="6"/>
+    </row>
+    <row r="376" customHeight="1" spans="1:7">
+      <c r="A376" s="2">
+        <f t="shared" si="5"/>
+        <v>370</v>
+      </c>
+      <c r="B376" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C376" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="D376" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="E376" s="6"/>
+      <c r="F376" s="6"/>
+      <c r="G376" s="6"/>
+    </row>
+    <row r="377" customHeight="1" spans="1:7">
+      <c r="A377" s="2">
+        <f t="shared" si="5"/>
+        <v>371</v>
+      </c>
+      <c r="B377" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C377" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="D377" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="E377" s="6"/>
+      <c r="F377" s="6"/>
+      <c r="G377" s="6"/>
+    </row>
+    <row r="378" customHeight="1" spans="1:7">
+      <c r="A378" s="2">
+        <f t="shared" si="5"/>
+        <v>372</v>
+      </c>
+      <c r="B378" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C378" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="D378" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="E378" s="6"/>
+      <c r="F378" s="6"/>
+      <c r="G378" s="6"/>
+    </row>
+    <row r="379" customHeight="1" spans="1:7">
+      <c r="A379" s="2">
+        <f t="shared" si="5"/>
+        <v>373</v>
+      </c>
+      <c r="B379" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C379" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="D379" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="E379" s="6"/>
+      <c r="F379" s="6"/>
+      <c r="G379" s="6"/>
+    </row>
+    <row r="380" customHeight="1" spans="1:7">
+      <c r="A380" s="2">
+        <f t="shared" si="5"/>
+        <v>374</v>
+      </c>
+      <c r="B380" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C380" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="D380" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="E380" s="6"/>
+      <c r="F380" s="6"/>
+      <c r="G380" s="6"/>
+    </row>
+    <row r="381" customHeight="1" spans="1:7">
+      <c r="A381" s="2">
+        <f t="shared" si="5"/>
+        <v>375</v>
+      </c>
+      <c r="B381" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C381" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="D381" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="E381" s="6"/>
+      <c r="F381" s="6"/>
+      <c r="G381" s="6"/>
+    </row>
+    <row r="382" customHeight="1" spans="1:7">
+      <c r="A382" s="2">
+        <f t="shared" si="5"/>
+        <v>376</v>
+      </c>
+      <c r="B382" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C382" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D382" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="E382" s="6"/>
+      <c r="F382" s="6"/>
+      <c r="G382" s="6"/>
+    </row>
+    <row r="383" customHeight="1" spans="1:7">
+      <c r="A383" s="2">
+        <f t="shared" ref="A383:A446" si="6">A382+1</f>
+        <v>377</v>
+      </c>
+      <c r="B383" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C383" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="D383" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="E383" s="6"/>
+      <c r="F383" s="6"/>
+      <c r="G383" s="6"/>
+    </row>
+    <row r="384" customHeight="1" spans="1:7">
+      <c r="A384" s="2">
+        <f t="shared" si="6"/>
+        <v>378</v>
+      </c>
+      <c r="B384" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C384" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="D384" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="E384" s="6"/>
+      <c r="F384" s="6"/>
+      <c r="G384" s="6"/>
+    </row>
+    <row r="385" customHeight="1" spans="1:7">
+      <c r="A385" s="2">
+        <f t="shared" si="6"/>
+        <v>379</v>
+      </c>
+      <c r="B385" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C385" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="D385" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="E385" s="6"/>
+      <c r="F385" s="6"/>
+      <c r="G385" s="6"/>
+    </row>
+    <row r="386" customHeight="1" spans="1:7">
+      <c r="A386" s="2">
+        <f t="shared" si="6"/>
+        <v>380</v>
+      </c>
+      <c r="B386" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C386" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="D386" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="E386" s="6"/>
+      <c r="F386" s="6"/>
+      <c r="G386" s="6"/>
+    </row>
+    <row r="387" customHeight="1" spans="1:7">
+      <c r="A387" s="2">
+        <f t="shared" si="6"/>
+        <v>381</v>
+      </c>
+      <c r="B387" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C387" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="D387" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="E387" s="6"/>
+      <c r="F387" s="6"/>
+      <c r="G387" s="6"/>
+    </row>
+    <row r="388" customHeight="1" spans="1:7">
+      <c r="A388" s="2">
+        <f t="shared" si="6"/>
+        <v>382</v>
+      </c>
+      <c r="B388" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C388" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="D388" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="E388" s="6"/>
+      <c r="F388" s="6"/>
+      <c r="G388" s="6"/>
+    </row>
+    <row r="389" customHeight="1" spans="1:7">
+      <c r="A389" s="2">
+        <f t="shared" si="6"/>
+        <v>383</v>
+      </c>
+      <c r="B389" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C389" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="D389" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="E389" s="6"/>
+      <c r="F389" s="6"/>
+      <c r="G389" s="6"/>
+    </row>
+    <row r="390" customHeight="1" spans="1:7">
+      <c r="A390" s="2">
+        <f t="shared" si="6"/>
+        <v>384</v>
+      </c>
+      <c r="B390" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C390" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="D390" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="E390" s="6"/>
+      <c r="F390" s="6"/>
+      <c r="G390" s="6"/>
+    </row>
+    <row r="391" customHeight="1" spans="1:7">
+      <c r="A391" s="2">
+        <f t="shared" si="6"/>
+        <v>385</v>
+      </c>
+      <c r="B391" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C391" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="D391" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="E391" s="6"/>
+      <c r="F391" s="6"/>
+      <c r="G391" s="6"/>
+    </row>
+    <row r="392" customHeight="1" spans="1:7">
+      <c r="A392" s="2">
+        <f t="shared" si="6"/>
+        <v>386</v>
+      </c>
+      <c r="B392" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C392" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="D392" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="E392" s="6"/>
+      <c r="F392" s="6"/>
+      <c r="G392" s="6"/>
+    </row>
+    <row r="393" customHeight="1" spans="1:7">
+      <c r="A393" s="2">
+        <f t="shared" si="6"/>
+        <v>387</v>
+      </c>
+      <c r="B393" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C393" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="D393" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="E393" s="6"/>
+      <c r="F393" s="6"/>
+      <c r="G393" s="6"/>
+    </row>
+    <row r="394" customHeight="1" spans="1:7">
+      <c r="A394" s="2">
+        <f t="shared" si="6"/>
+        <v>388</v>
+      </c>
+      <c r="B394" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C394" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D394" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="E394" s="6"/>
+      <c r="F394" s="6"/>
+      <c r="G394" s="6"/>
+    </row>
+    <row r="395" customHeight="1" spans="1:7">
+      <c r="A395" s="2">
+        <f t="shared" si="6"/>
+        <v>389</v>
+      </c>
+      <c r="B395" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C395" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="D395" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="E395" s="6"/>
+      <c r="F395" s="6"/>
+      <c r="G395" s="6"/>
+    </row>
+    <row r="396" customHeight="1" spans="1:7">
+      <c r="A396" s="2">
+        <f t="shared" si="6"/>
+        <v>390</v>
+      </c>
+      <c r="B396" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C396" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="D396" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="E396" s="6"/>
+      <c r="F396" s="6"/>
+      <c r="G396" s="6"/>
+    </row>
+    <row r="397" customHeight="1" spans="1:7">
+      <c r="A397" s="2">
+        <f t="shared" si="6"/>
+        <v>391</v>
+      </c>
+      <c r="B397" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C397" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="D397" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="E397" s="6"/>
+      <c r="F397" s="6"/>
+      <c r="G397" s="6"/>
+    </row>
+    <row r="398" customHeight="1" spans="1:7">
+      <c r="A398" s="2">
+        <f t="shared" si="6"/>
+        <v>392</v>
+      </c>
+      <c r="B398" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C398" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="D398" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="E398" s="6"/>
+      <c r="F398" s="6"/>
+      <c r="G398" s="6"/>
+    </row>
+    <row r="399" customHeight="1" spans="1:7">
+      <c r="A399" s="2">
+        <f t="shared" si="6"/>
+        <v>393</v>
+      </c>
+      <c r="B399" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C399" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="D399" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="E399" s="6"/>
+      <c r="F399" s="6"/>
+      <c r="G399" s="6"/>
+    </row>
+    <row r="400" customHeight="1" spans="1:7">
+      <c r="A400" s="2">
+        <f t="shared" si="6"/>
+        <v>394</v>
+      </c>
+      <c r="B400" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C400" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="D400" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="E400" s="6"/>
+      <c r="F400" s="6"/>
+      <c r="G400" s="6"/>
+    </row>
+    <row r="401" customHeight="1" spans="1:7">
+      <c r="A401" s="2">
+        <f t="shared" si="6"/>
+        <v>395</v>
+      </c>
+      <c r="B401" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C401" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="D401" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="E401" s="6"/>
+      <c r="F401" s="6"/>
+      <c r="G401" s="6"/>
+    </row>
+    <row r="402" customHeight="1" spans="1:7">
+      <c r="A402" s="2">
+        <f t="shared" si="6"/>
+        <v>396</v>
+      </c>
+      <c r="B402" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C402" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="D402" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="E402" s="6"/>
+      <c r="F402" s="6"/>
+      <c r="G402" s="6"/>
+    </row>
+    <row r="403" customHeight="1" spans="1:7">
+      <c r="A403" s="2">
+        <f t="shared" si="6"/>
+        <v>397</v>
+      </c>
+      <c r="B403" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C403" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="D403" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="E403" s="6"/>
+      <c r="F403" s="6"/>
+      <c r="G403" s="6"/>
+    </row>
+    <row r="404" customHeight="1" spans="1:7">
+      <c r="A404" s="2">
+        <f t="shared" si="6"/>
+        <v>398</v>
+      </c>
+      <c r="B404" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C404" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="D404" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="E404" s="6"/>
+      <c r="F404" s="6"/>
+      <c r="G404" s="6"/>
+    </row>
+    <row r="405" customHeight="1" spans="1:7">
+      <c r="A405" s="2">
+        <f t="shared" si="6"/>
+        <v>399</v>
+      </c>
+      <c r="B405" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C405" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="D405" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="E405" s="6"/>
+      <c r="F405" s="6"/>
+      <c r="G405" s="6"/>
+    </row>
+    <row r="406" customHeight="1" spans="1:7">
+      <c r="A406" s="2">
+        <f t="shared" si="6"/>
+        <v>400</v>
+      </c>
+      <c r="B406" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C406" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="D406" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="E406" s="6"/>
+      <c r="F406" s="6"/>
+      <c r="G406" s="6"/>
+    </row>
+    <row r="407" customHeight="1" spans="1:7">
+      <c r="A407" s="2">
+        <f t="shared" si="6"/>
+        <v>401</v>
+      </c>
+      <c r="B407" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C407" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D407" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="E407" s="6"/>
+      <c r="F407" s="6"/>
+      <c r="G407" s="6"/>
+    </row>
+    <row r="408" customHeight="1" spans="1:7">
+      <c r="A408" s="2">
+        <f t="shared" si="6"/>
+        <v>402</v>
+      </c>
+      <c r="B408" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C408" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D408" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="E408" s="6"/>
+      <c r="F408" s="6"/>
+      <c r="G408" s="6"/>
+    </row>
+    <row r="409" customHeight="1" spans="1:7">
+      <c r="A409" s="2">
+        <f t="shared" si="6"/>
+        <v>403</v>
+      </c>
+      <c r="B409" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C409" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="D409" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="E409" s="6"/>
+      <c r="F409" s="6"/>
+      <c r="G409" s="6"/>
+    </row>
+    <row r="410" customHeight="1" spans="1:7">
+      <c r="A410" s="2">
+        <f t="shared" si="6"/>
+        <v>404</v>
+      </c>
+      <c r="B410" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C410" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D410" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="E410" s="6"/>
+      <c r="F410" s="6"/>
+      <c r="G410" s="6"/>
+    </row>
+    <row r="411" customHeight="1" spans="1:7">
+      <c r="A411" s="2">
+        <f t="shared" si="6"/>
+        <v>405</v>
+      </c>
+      <c r="B411" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C411" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="D411" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="E411" s="6"/>
+      <c r="F411" s="6"/>
+      <c r="G411" s="6"/>
+    </row>
+    <row r="412" customHeight="1" spans="1:7">
+      <c r="A412" s="2">
+        <f t="shared" si="6"/>
+        <v>406</v>
+      </c>
+      <c r="B412" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C412" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="D412" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="E412" s="6"/>
+      <c r="F412" s="6"/>
+      <c r="G412" s="6"/>
+    </row>
+    <row r="413" customHeight="1" spans="1:7">
+      <c r="A413" s="2">
+        <f t="shared" si="6"/>
+        <v>407</v>
+      </c>
+      <c r="B413" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C413" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="D413" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="E413" s="6"/>
+      <c r="F413" s="6"/>
+      <c r="G413" s="6"/>
+    </row>
+    <row r="414" customHeight="1" spans="1:7">
+      <c r="A414" s="2">
+        <f t="shared" si="6"/>
+        <v>408</v>
+      </c>
+      <c r="B414" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C414" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="D414" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="E414" s="6"/>
+      <c r="F414" s="6"/>
+      <c r="G414" s="6"/>
+    </row>
+    <row r="415" customHeight="1" spans="1:7">
+      <c r="A415" s="2">
+        <f t="shared" si="6"/>
+        <v>409</v>
+      </c>
+      <c r="B415" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C415" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="D415" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="E415" s="6"/>
+      <c r="F415" s="6"/>
+      <c r="G415" s="6"/>
+    </row>
+    <row r="416" customHeight="1" spans="1:7">
+      <c r="A416" s="2">
+        <f t="shared" si="6"/>
+        <v>410</v>
+      </c>
+      <c r="B416" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C416" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="D416" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="E416" s="6"/>
+      <c r="F416" s="6"/>
+      <c r="G416" s="6"/>
+    </row>
+    <row r="417" customHeight="1" spans="1:7">
+      <c r="A417" s="2">
+        <f t="shared" si="6"/>
+        <v>411</v>
+      </c>
+      <c r="B417" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C417" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="D417" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="E417" s="6"/>
+      <c r="F417" s="6"/>
+      <c r="G417" s="6"/>
+    </row>
+    <row r="418" customHeight="1" spans="1:7">
+      <c r="A418" s="2">
+        <f t="shared" si="6"/>
+        <v>412</v>
+      </c>
+      <c r="B418" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C418" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="D418" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="E418" s="6"/>
+      <c r="F418" s="6"/>
+      <c r="G418" s="6"/>
+    </row>
+    <row r="419" customHeight="1" spans="1:7">
+      <c r="A419" s="2">
+        <f t="shared" si="6"/>
+        <v>413</v>
+      </c>
+      <c r="B419" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C419" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="D419" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="E419" s="6"/>
+      <c r="F419" s="6"/>
+      <c r="G419" s="6"/>
+    </row>
+    <row r="420" customHeight="1" spans="1:7">
+      <c r="A420" s="2">
+        <f t="shared" si="6"/>
+        <v>414</v>
+      </c>
+      <c r="B420" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C420" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="D420" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="E420" s="6"/>
+      <c r="F420" s="6"/>
+      <c r="G420" s="6"/>
+    </row>
+    <row r="421" customHeight="1" spans="1:7">
+      <c r="A421" s="2">
+        <f t="shared" si="6"/>
+        <v>415</v>
+      </c>
+      <c r="B421" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C421" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="D421" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="E421" s="6"/>
+      <c r="F421" s="6"/>
+      <c r="G421" s="6"/>
+    </row>
+    <row r="422" customHeight="1" spans="1:7">
+      <c r="A422" s="2">
+        <f t="shared" si="6"/>
+        <v>416</v>
+      </c>
+      <c r="B422" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C422" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="D422" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="E422" s="6"/>
+      <c r="F422" s="6"/>
+      <c r="G422" s="6"/>
+    </row>
+    <row r="423" customHeight="1" spans="1:7">
+      <c r="A423" s="2">
+        <f t="shared" si="6"/>
+        <v>417</v>
+      </c>
+      <c r="B423" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C423" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="D423" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="E423" s="6"/>
+      <c r="F423" s="6"/>
+      <c r="G423" s="6"/>
+    </row>
+    <row r="424" customHeight="1" spans="1:7">
+      <c r="A424" s="2">
+        <f t="shared" si="6"/>
+        <v>418</v>
+      </c>
+      <c r="B424" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C424" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D424" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="E424" s="6"/>
+      <c r="F424" s="6"/>
+      <c r="G424" s="6"/>
+    </row>
+    <row r="425" customHeight="1" spans="1:7">
+      <c r="A425" s="2">
+        <f t="shared" si="6"/>
+        <v>419</v>
+      </c>
+      <c r="B425" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C425" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D425" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="E425" s="6"/>
+      <c r="F425" s="6"/>
+      <c r="G425" s="6"/>
+    </row>
+    <row r="426" customHeight="1" spans="1:7">
+      <c r="A426" s="2">
+        <f t="shared" si="6"/>
+        <v>420</v>
+      </c>
+      <c r="B426" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C426" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="D426" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="E426" s="6"/>
+      <c r="F426" s="6"/>
+      <c r="G426" s="6"/>
+    </row>
+    <row r="427" customHeight="1" spans="1:7">
+      <c r="A427" s="2">
+        <f t="shared" si="6"/>
+        <v>421</v>
+      </c>
+      <c r="B427" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C427" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D427" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="E427" s="6"/>
+      <c r="F427" s="6"/>
+      <c r="G427" s="6"/>
+    </row>
+    <row r="428" customHeight="1" spans="1:7">
+      <c r="A428" s="2">
+        <f t="shared" si="6"/>
+        <v>422</v>
+      </c>
+      <c r="B428" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C428" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D428" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="E428" s="6"/>
+      <c r="F428" s="6"/>
+      <c r="G428" s="6"/>
+    </row>
+    <row r="429" customHeight="1" spans="1:7">
+      <c r="A429" s="2">
+        <f t="shared" si="6"/>
+        <v>423</v>
+      </c>
+      <c r="B429" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C429" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D429" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="E429" s="6"/>
+      <c r="F429" s="6"/>
+      <c r="G429" s="6"/>
+    </row>
+    <row r="430" customHeight="1" spans="1:7">
+      <c r="A430" s="2">
+        <f t="shared" si="6"/>
+        <v>424</v>
+      </c>
+      <c r="B430" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C430" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D430" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="E430" s="6"/>
+      <c r="F430" s="6"/>
+      <c r="G430" s="6"/>
+    </row>
+    <row r="431" customHeight="1" spans="1:7">
+      <c r="A431" s="2">
+        <f t="shared" si="6"/>
+        <v>425</v>
+      </c>
+      <c r="B431" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C431" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="D431" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="E431" s="6"/>
+      <c r="F431" s="6"/>
+      <c r="G431" s="6"/>
+    </row>
+    <row r="432" customHeight="1" spans="1:7">
+      <c r="A432" s="2">
+        <f t="shared" si="6"/>
+        <v>426</v>
+      </c>
+      <c r="B432" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C432" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="D432" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="E432" s="6"/>
+      <c r="F432" s="6"/>
+      <c r="G432" s="6"/>
+    </row>
+    <row r="433" customHeight="1" spans="1:7">
+      <c r="A433" s="2">
+        <f t="shared" si="6"/>
+        <v>427</v>
+      </c>
+      <c r="B433" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C433" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="D433" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="E433" s="6"/>
+      <c r="F433" s="6"/>
+      <c r="G433" s="6"/>
+    </row>
+    <row r="434" customHeight="1" spans="1:7">
+      <c r="A434" s="2">
+        <f t="shared" si="6"/>
+        <v>428</v>
+      </c>
+      <c r="B434" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C434" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D434" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="E434" s="6"/>
+      <c r="F434" s="6"/>
+      <c r="G434" s="6"/>
+    </row>
+    <row r="435" customHeight="1" spans="1:7">
+      <c r="A435" s="2">
+        <f t="shared" si="6"/>
+        <v>429</v>
+      </c>
+      <c r="B435" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C435" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D435" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="E435" s="6"/>
+      <c r="F435" s="6"/>
+      <c r="G435" s="6"/>
+    </row>
+    <row r="436" customHeight="1" spans="1:7">
+      <c r="A436" s="2">
+        <f t="shared" si="6"/>
+        <v>430</v>
+      </c>
+      <c r="B436" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C436" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D436" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="E436" s="6"/>
+      <c r="F436" s="6"/>
+      <c r="G436" s="6"/>
+    </row>
+    <row r="437" customHeight="1" spans="1:7">
+      <c r="A437" s="2">
+        <f t="shared" si="6"/>
+        <v>431</v>
+      </c>
+      <c r="B437" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C437" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D437" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="E437" s="6"/>
+      <c r="F437" s="6"/>
+      <c r="G437" s="6"/>
+    </row>
+    <row r="438" customHeight="1" spans="1:7">
+      <c r="A438" s="2">
+        <f t="shared" si="6"/>
+        <v>432</v>
+      </c>
+      <c r="B438" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C438" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D438" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="E438" s="6"/>
+      <c r="F438" s="6"/>
+      <c r="G438" s="6"/>
+    </row>
+    <row r="439" customHeight="1" spans="1:7">
+      <c r="A439" s="2">
+        <f t="shared" si="6"/>
+        <v>433</v>
+      </c>
+      <c r="B439" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C439" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D439" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="E439" s="6"/>
+      <c r="F439" s="6"/>
+      <c r="G439" s="6"/>
+    </row>
+    <row r="440" customHeight="1" spans="1:7">
+      <c r="A440" s="2">
+        <f t="shared" si="6"/>
+        <v>434</v>
+      </c>
+      <c r="B440" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C440" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="D440" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="E440" s="6"/>
+      <c r="F440" s="6"/>
+      <c r="G440" s="6"/>
+    </row>
+    <row r="441" customHeight="1" spans="1:7">
+      <c r="A441" s="2">
+        <f t="shared" si="6"/>
+        <v>435</v>
+      </c>
+      <c r="B441" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C441" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D441" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="E441" s="6"/>
+      <c r="F441" s="6"/>
+      <c r="G441" s="6"/>
+    </row>
+    <row r="442" customHeight="1" spans="1:7">
+      <c r="A442" s="2">
+        <f t="shared" si="6"/>
+        <v>436</v>
+      </c>
+      <c r="B442" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C442" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="D442" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="E442" s="6"/>
+      <c r="F442" s="6"/>
+      <c r="G442" s="6"/>
+    </row>
+    <row r="443" customHeight="1" spans="1:7">
+      <c r="A443" s="2">
+        <f t="shared" si="6"/>
+        <v>437</v>
+      </c>
+      <c r="B443" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C443" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D443" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="E443" s="6"/>
+      <c r="F443" s="6"/>
+      <c r="G443" s="6"/>
+    </row>
+    <row r="444" customHeight="1" spans="1:7">
+      <c r="A444" s="2">
+        <f t="shared" si="6"/>
+        <v>438</v>
+      </c>
+      <c r="B444" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C444" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D444" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="E444" s="6"/>
+      <c r="F444" s="6"/>
+      <c r="G444" s="6"/>
+    </row>
+    <row r="445" customHeight="1" spans="1:7">
+      <c r="A445" s="2">
+        <f t="shared" si="6"/>
+        <v>439</v>
+      </c>
+      <c r="B445" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C445" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="D445" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="E445" s="6"/>
+      <c r="F445" s="6"/>
+      <c r="G445" s="6"/>
+    </row>
+    <row r="446" customHeight="1" spans="1:7">
+      <c r="A446" s="2">
+        <f t="shared" si="6"/>
+        <v>440</v>
+      </c>
+      <c r="B446" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C446" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="D446" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="E446" s="6"/>
+      <c r="F446" s="6"/>
+      <c r="G446" s="6"/>
+    </row>
+    <row r="447" customHeight="1" spans="1:7">
+      <c r="A447" s="2">
+        <f>A446+1</f>
+        <v>441</v>
+      </c>
+      <c r="B447" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C447" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="D447" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="E447" s="6"/>
+      <c r="F447" s="6"/>
+      <c r="G447" s="6"/>
+    </row>
+    <row r="448" customHeight="1" spans="1:7">
+      <c r="A448" s="2">
+        <f>A447+1</f>
+        <v>442</v>
+      </c>
+      <c r="B448" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C448" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="D448" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="E448" s="6"/>
+      <c r="F448" s="6"/>
+      <c r="G448" s="6"/>
+    </row>
+    <row r="449" customHeight="1" spans="1:7">
+      <c r="A449" s="2">
+        <f>A448+1</f>
+        <v>443</v>
+      </c>
+      <c r="B449" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C449" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="D449" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="E449" s="6"/>
+      <c r="F449" s="6"/>
+      <c r="G449" s="6"/>
+    </row>
+    <row r="450" customHeight="1" spans="1:7">
+      <c r="A450" s="2">
+        <f>A449+1</f>
+        <v>444</v>
+      </c>
+      <c r="B450" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C450" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="D450" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="E450" s="6"/>
+      <c r="F450" s="6"/>
+      <c r="G450" s="6"/>
+    </row>
+    <row r="451" customHeight="1" spans="1:7">
+      <c r="A451" s="2">
+        <f>A450+1</f>
+        <v>445</v>
+      </c>
+      <c r="B451" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C451" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="D451" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="E451" s="6"/>
+      <c r="F451" s="6"/>
+      <c r="G451" s="6"/>
+    </row>
+    <row r="452" customHeight="1" spans="1:7">
+      <c r="A452" s="2">
+        <f>A451+1</f>
+        <v>446</v>
+      </c>
+      <c r="B452" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C452" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="D452" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="E452" s="6"/>
+      <c r="F452" s="6"/>
+      <c r="G452" s="6"/>
+    </row>
+    <row r="453" customHeight="1" spans="1:7">
+      <c r="A453" s="2">
+        <f>A452+1</f>
+        <v>447</v>
+      </c>
+      <c r="B453" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C453" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="D453" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="E453" s="6"/>
+      <c r="F453" s="6"/>
+      <c r="G453" s="6"/>
+    </row>
+    <row r="454" customHeight="1" spans="1:7">
+      <c r="A454" s="2">
+        <f>A453+1</f>
+        <v>448</v>
+      </c>
+      <c r="B454" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C454" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="D454" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="E454" s="6"/>
+      <c r="F454" s="6"/>
+      <c r="G454" s="6"/>
+    </row>
+    <row r="455" customHeight="1" spans="1:7">
+      <c r="A455" s="2">
+        <f>A454+1</f>
+        <v>449</v>
+      </c>
+      <c r="B455" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C455" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="D455" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="E455" s="6"/>
+      <c r="F455" s="6"/>
+      <c r="G455" s="6"/>
+    </row>
+    <row r="456" customHeight="1" spans="1:7">
+      <c r="A456" s="2">
+        <f>A455+1</f>
+        <v>450</v>
+      </c>
+      <c r="B456" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C456" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="D456" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="E456" s="6"/>
+      <c r="F456" s="6"/>
+      <c r="G456" s="6"/>
+    </row>
+    <row r="457" customHeight="1" spans="1:7">
+      <c r="A457" s="2">
+        <f>A456+1</f>
+        <v>451</v>
+      </c>
+      <c r="B457" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C457" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="D457" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="E457" s="6"/>
+      <c r="F457" s="6"/>
+      <c r="G457" s="6"/>
+    </row>
+    <row r="458" customHeight="1" spans="1:7">
+      <c r="A458" s="2">
+        <f>A457+1</f>
+        <v>452</v>
+      </c>
+      <c r="B458" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C458" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="D458" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="E458" s="6"/>
+      <c r="F458" s="6"/>
+      <c r="G458" s="6"/>
+    </row>
+    <row r="459" customHeight="1" spans="1:7">
+      <c r="A459" s="2">
+        <f>A458+1</f>
+        <v>453</v>
+      </c>
+      <c r="B459" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C459" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="D459" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="E459" s="6"/>
+      <c r="F459" s="6"/>
+      <c r="G459" s="6"/>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A6:H62" etc:filterBottomFollowUsedRange="0">
-    <sortState ref="A6:H62">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A6:J62" etc:filterBottomFollowUsedRange="0">
+    <sortState ref="A6:J62">
       <sortCondition ref="B6"/>
     </sortState>
     <extLst/>
   </autoFilter>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:H4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="3" outlineLevelCol="7"/>
-  <sheetData>
-    <row r="1" spans="1:8">
-      <c r="A1" t="s">
-        <v>57</v>
-      </c>
-      <c r="B1" t="s">
-        <v>58</v>
-      </c>
-      <c r="C1" t="s">
-        <v>59</v>
-      </c>
-      <c r="D1" t="s">
-        <v>60</v>
-      </c>
-      <c r="E1" t="s">
-        <v>61</v>
-      </c>
-      <c r="F1" t="s">
-        <v>62</v>
-      </c>
-      <c r="G1" t="s">
-        <v>63</v>
-      </c>
-      <c r="H1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8">
-      <c r="A2" t="s">
-        <v>65</v>
-      </c>
-      <c r="B2" t="s">
-        <v>66</v>
-      </c>
-      <c r="C2" t="s">
-        <v>67</v>
-      </c>
-      <c r="D2" t="s">
-        <v>68</v>
-      </c>
-      <c r="E2" t="s">
-        <v>29</v>
-      </c>
-      <c r="F2">
-        <v>10</v>
-      </c>
-      <c r="G2">
-        <v>0</v>
-      </c>
-      <c r="H2">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
-      <c r="A3" t="s">
-        <v>65</v>
-      </c>
-      <c r="B3" t="s">
-        <v>66</v>
-      </c>
-      <c r="C3" t="s">
-        <v>67</v>
-      </c>
-      <c r="D3" t="s">
-        <v>68</v>
-      </c>
-      <c r="E3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F3">
-        <v>8</v>
-      </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
-      <c r="H3">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
-      <c r="A4" t="s">
-        <v>65</v>
-      </c>
-      <c r="B4" t="s">
-        <v>66</v>
-      </c>
-      <c r="C4" t="s">
-        <v>67</v>
-      </c>
-      <c r="D4" t="s">
-        <v>68</v>
-      </c>
-      <c r="E4" t="s">
-        <v>23</v>
-      </c>
-      <c r="F4">
-        <v>8</v>
-      </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="H4">
-        <v>8</v>
-      </c>
-    </row>
-  </sheetData>
+  <conditionalFormatting sqref="C6">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>

--- a/MATERIAL 1.xlsx
+++ b/MATERIAL 1.xlsx
@@ -4,16 +4,14 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24000" windowHeight="9600"/>
+    <workbookView windowWidth="24000" windowHeight="9600" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="HEADER APLIKASI" sheetId="1" r:id="rId1"/>
+    <sheet name="REKAP_INPUT" sheetId="2" r:id="rId2"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId2"/>
-  </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'HEADER APLIKASI'!$A$6:$J$62</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'HEADER APLIKASI'!$A$6:$J$459</definedName>
     <definedName name="_\aaaaaaaaaaaaa">#REF!</definedName>
     <definedName name="_\B">#N/A</definedName>
   </definedNames>
@@ -35,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1370" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1409" uniqueCount="191">
   <si>
     <t>NAMA PEKERJAAN :</t>
   </si>
@@ -575,6 +573,39 @@
   </si>
   <si>
     <t>TIANG BETON 9 METER - 200 DAN</t>
+  </si>
+  <si>
+    <t>Nama Pekerjaan</t>
+  </si>
+  <si>
+    <t>Alamat Pekerjaan</t>
+  </si>
+  <si>
+    <t>Jenis Pekerjaan</t>
+  </si>
+  <si>
+    <t>Tanggal</t>
+  </si>
+  <si>
+    <t>Jenis Konstruksi</t>
+  </si>
+  <si>
+    <t>Material</t>
+  </si>
+  <si>
+    <t>Volume Material</t>
+  </si>
+  <si>
+    <t>RATNO SANTOSO</t>
+  </si>
+  <si>
+    <t>JL MANYAR KERTOARJO 119</t>
+  </si>
+  <si>
+    <t>SAR</t>
+  </si>
+  <si>
+    <t>2026-08-13</t>
   </si>
 </sst>
 </file>
@@ -588,14 +619,7 @@
     <numFmt numFmtId="178" formatCode="_-&quot;Rp&quot;* #,##0_-;\-&quot;Rp&quot;* #,##0_-;_-&quot;Rp&quot;* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="179" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="22">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1088,13 +1112,16 @@
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
@@ -1103,125 +1130,122 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="5">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="5">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="6">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="6">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="7">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="7">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0">
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0">
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1229,14 +1253,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="distributed"/>
     </xf>
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="52">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1525,51 +1548,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="SUTM"/>
-      <sheetName val="SKUTM"/>
-      <sheetName val="SKTM"/>
-      <sheetName val="GTT 1 TIANG"/>
-      <sheetName val="GTT 2 TIANG"/>
-      <sheetName val="FOOTKLEM"/>
-      <sheetName val="APP TR (53-197 kVA)"/>
-      <sheetName val="APP TR ( 23-41,5kVA)"/>
-      <sheetName val="APP TR (6,6-16,2 kVA)"/>
-      <sheetName val="SUTR"/>
-      <sheetName val="KUBIKEL"/>
-      <sheetName val="GARDU KONVEN"/>
-      <sheetName val="SKTR &amp; SKSR"/>
-      <sheetName val="COMMISIONING"/>
-      <sheetName val="SAFETY COST"/>
-      <sheetName val="MATERIAL TAMBAHAN"/>
-      <sheetName val="RESUM  KR 037"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-      <sheetData sheetId="7"/>
-      <sheetData sheetId="8"/>
-      <sheetData sheetId="9"/>
-      <sheetData sheetId="10"/>
-      <sheetData sheetId="11"/>
-      <sheetData sheetId="12"/>
-      <sheetData sheetId="13"/>
-      <sheetData sheetId="14"/>
-      <sheetData sheetId="15"/>
-      <sheetData sheetId="16"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="WPS">
   <a:themeElements>
@@ -1895,7 +1873,7 @@
     </row>
     <row r="8" customHeight="1" spans="1:7">
       <c r="A8" s="2">
-        <f t="shared" ref="A8:A62" si="0">A7+1</f>
+        <f t="shared" ref="A8:A71" si="0">A7+1</f>
         <v>2</v>
       </c>
       <c r="B8" s="4" t="s">
@@ -2889,7 +2867,7 @@
     </row>
     <row r="63" customHeight="1" spans="1:10">
       <c r="A63" s="2">
-        <f t="shared" ref="A63:A126" si="1">A62+1</f>
+        <f t="shared" si="0"/>
         <v>57</v>
       </c>
       <c r="B63" s="4" t="s">
@@ -2901,13 +2879,13 @@
       <c r="D63" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="E63" s="6"/>
-      <c r="F63" s="6"/>
-      <c r="G63" s="6"/>
+      <c r="E63" s="3"/>
+      <c r="F63" s="3"/>
+      <c r="G63" s="3"/>
     </row>
     <row r="64" customHeight="1" spans="1:10">
       <c r="A64" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>58</v>
       </c>
       <c r="B64" s="4" t="s">
@@ -2919,13 +2897,13 @@
       <c r="D64" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="E64" s="6"/>
-      <c r="F64" s="6"/>
-      <c r="G64" s="6"/>
+      <c r="E64" s="3"/>
+      <c r="F64" s="3"/>
+      <c r="G64" s="3"/>
     </row>
     <row r="65" customHeight="1" spans="1:7">
       <c r="A65" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>59</v>
       </c>
       <c r="B65" s="4" t="s">
@@ -2937,13 +2915,13 @@
       <c r="D65" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="E65" s="6"/>
-      <c r="F65" s="6"/>
-      <c r="G65" s="6"/>
+      <c r="E65" s="3"/>
+      <c r="F65" s="3"/>
+      <c r="G65" s="3"/>
     </row>
     <row r="66" customHeight="1" spans="1:7">
       <c r="A66" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>60</v>
       </c>
       <c r="B66" s="4" t="s">
@@ -2955,13 +2933,13 @@
       <c r="D66" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="E66" s="6"/>
-      <c r="F66" s="6"/>
-      <c r="G66" s="6"/>
+      <c r="E66" s="3"/>
+      <c r="F66" s="3"/>
+      <c r="G66" s="3"/>
     </row>
     <row r="67" customHeight="1" spans="1:7">
       <c r="A67" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>61</v>
       </c>
       <c r="B67" s="4" t="s">
@@ -2973,13 +2951,13 @@
       <c r="D67" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="E67" s="6"/>
-      <c r="F67" s="6"/>
-      <c r="G67" s="6"/>
+      <c r="E67" s="3"/>
+      <c r="F67" s="3"/>
+      <c r="G67" s="3"/>
     </row>
     <row r="68" customHeight="1" spans="1:7">
       <c r="A68" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>62</v>
       </c>
       <c r="B68" s="4" t="s">
@@ -2991,13 +2969,13 @@
       <c r="D68" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="E68" s="6"/>
-      <c r="F68" s="6"/>
-      <c r="G68" s="6"/>
+      <c r="E68" s="3"/>
+      <c r="F68" s="3"/>
+      <c r="G68" s="3"/>
     </row>
     <row r="69" customHeight="1" spans="1:7">
       <c r="A69" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>63</v>
       </c>
       <c r="B69" s="4" t="s">
@@ -3009,13 +2987,13 @@
       <c r="D69" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="E69" s="6"/>
-      <c r="F69" s="6"/>
-      <c r="G69" s="6"/>
+      <c r="E69" s="3"/>
+      <c r="F69" s="3"/>
+      <c r="G69" s="3"/>
     </row>
     <row r="70" customHeight="1" spans="1:7">
       <c r="A70" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>64</v>
       </c>
       <c r="B70" s="4" t="s">
@@ -3027,13 +3005,13 @@
       <c r="D70" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="E70" s="6"/>
-      <c r="F70" s="6"/>
-      <c r="G70" s="6"/>
+      <c r="E70" s="3"/>
+      <c r="F70" s="3"/>
+      <c r="G70" s="3"/>
     </row>
     <row r="71" customHeight="1" spans="1:7">
       <c r="A71" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>65</v>
       </c>
       <c r="B71" s="4" t="s">
@@ -3045,13 +3023,13 @@
       <c r="D71" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="E71" s="6"/>
-      <c r="F71" s="6"/>
-      <c r="G71" s="6"/>
+      <c r="E71" s="3"/>
+      <c r="F71" s="3"/>
+      <c r="G71" s="3"/>
     </row>
     <row r="72" customHeight="1" spans="1:7">
       <c r="A72" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="A72:A135" si="1">A71+1</f>
         <v>66</v>
       </c>
       <c r="B72" s="4" t="s">
@@ -3063,9 +3041,9 @@
       <c r="D72" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="E72" s="6"/>
-      <c r="F72" s="6"/>
-      <c r="G72" s="6"/>
+      <c r="E72" s="3"/>
+      <c r="F72" s="3"/>
+      <c r="G72" s="3"/>
     </row>
     <row r="73" customHeight="1" spans="1:7">
       <c r="A73" s="2">
@@ -3081,9 +3059,9 @@
       <c r="D73" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="E73" s="6"/>
-      <c r="F73" s="6"/>
-      <c r="G73" s="6"/>
+      <c r="E73" s="3"/>
+      <c r="F73" s="3"/>
+      <c r="G73" s="3"/>
     </row>
     <row r="74" customHeight="1" spans="1:7">
       <c r="A74" s="2">
@@ -3099,9 +3077,9 @@
       <c r="D74" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="E74" s="6"/>
-      <c r="F74" s="6"/>
-      <c r="G74" s="6"/>
+      <c r="E74" s="3"/>
+      <c r="F74" s="3"/>
+      <c r="G74" s="3"/>
     </row>
     <row r="75" customHeight="1" spans="1:7">
       <c r="A75" s="2">
@@ -3117,9 +3095,9 @@
       <c r="D75" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="E75" s="6"/>
-      <c r="F75" s="6"/>
-      <c r="G75" s="6"/>
+      <c r="E75" s="3"/>
+      <c r="F75" s="3"/>
+      <c r="G75" s="3"/>
     </row>
     <row r="76" customHeight="1" spans="1:7">
       <c r="A76" s="2">
@@ -3135,9 +3113,9 @@
       <c r="D76" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="E76" s="6"/>
-      <c r="F76" s="6"/>
-      <c r="G76" s="6"/>
+      <c r="E76" s="3"/>
+      <c r="F76" s="3"/>
+      <c r="G76" s="3"/>
     </row>
     <row r="77" customHeight="1" spans="1:7">
       <c r="A77" s="2">
@@ -3153,9 +3131,9 @@
       <c r="D77" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="E77" s="6"/>
-      <c r="F77" s="6"/>
-      <c r="G77" s="6"/>
+      <c r="E77" s="3"/>
+      <c r="F77" s="3"/>
+      <c r="G77" s="3"/>
     </row>
     <row r="78" customHeight="1" spans="1:7">
       <c r="A78" s="2">
@@ -3171,9 +3149,9 @@
       <c r="D78" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="E78" s="6"/>
-      <c r="F78" s="6"/>
-      <c r="G78" s="6"/>
+      <c r="E78" s="3"/>
+      <c r="F78" s="3"/>
+      <c r="G78" s="3"/>
     </row>
     <row r="79" customHeight="1" spans="1:7">
       <c r="A79" s="2">
@@ -3189,9 +3167,9 @@
       <c r="D79" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="E79" s="6"/>
-      <c r="F79" s="6"/>
-      <c r="G79" s="6"/>
+      <c r="E79" s="3"/>
+      <c r="F79" s="3"/>
+      <c r="G79" s="3"/>
     </row>
     <row r="80" customHeight="1" spans="1:7">
       <c r="A80" s="2">
@@ -3207,9 +3185,9 @@
       <c r="D80" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="E80" s="6"/>
-      <c r="F80" s="6"/>
-      <c r="G80" s="6"/>
+      <c r="E80" s="3"/>
+      <c r="F80" s="3"/>
+      <c r="G80" s="3"/>
     </row>
     <row r="81" customHeight="1" spans="1:7">
       <c r="A81" s="2">
@@ -3225,9 +3203,9 @@
       <c r="D81" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="E81" s="6"/>
-      <c r="F81" s="6"/>
-      <c r="G81" s="6"/>
+      <c r="E81" s="3"/>
+      <c r="F81" s="3"/>
+      <c r="G81" s="3"/>
     </row>
     <row r="82" customHeight="1" spans="1:7">
       <c r="A82" s="2">
@@ -3243,9 +3221,9 @@
       <c r="D82" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="E82" s="6"/>
-      <c r="F82" s="6"/>
-      <c r="G82" s="6"/>
+      <c r="E82" s="3"/>
+      <c r="F82" s="3"/>
+      <c r="G82" s="3"/>
     </row>
     <row r="83" customHeight="1" spans="1:7">
       <c r="A83" s="2">
@@ -3261,9 +3239,9 @@
       <c r="D83" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="E83" s="6"/>
-      <c r="F83" s="6"/>
-      <c r="G83" s="6"/>
+      <c r="E83" s="3"/>
+      <c r="F83" s="3"/>
+      <c r="G83" s="3"/>
     </row>
     <row r="84" customHeight="1" spans="1:7">
       <c r="A84" s="2">
@@ -3279,9 +3257,9 @@
       <c r="D84" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="E84" s="6"/>
-      <c r="F84" s="6"/>
-      <c r="G84" s="6"/>
+      <c r="E84" s="3"/>
+      <c r="F84" s="3"/>
+      <c r="G84" s="3"/>
     </row>
     <row r="85" customHeight="1" spans="1:7">
       <c r="A85" s="2">
@@ -3297,9 +3275,9 @@
       <c r="D85" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="E85" s="6"/>
-      <c r="F85" s="6"/>
-      <c r="G85" s="6"/>
+      <c r="E85" s="3"/>
+      <c r="F85" s="3"/>
+      <c r="G85" s="3"/>
     </row>
     <row r="86" customHeight="1" spans="1:7">
       <c r="A86" s="2">
@@ -3315,9 +3293,9 @@
       <c r="D86" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="E86" s="6"/>
-      <c r="F86" s="6"/>
-      <c r="G86" s="6"/>
+      <c r="E86" s="3"/>
+      <c r="F86" s="3"/>
+      <c r="G86" s="3"/>
     </row>
     <row r="87" customHeight="1" spans="1:7">
       <c r="A87" s="2">
@@ -3333,9 +3311,9 @@
       <c r="D87" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="E87" s="6"/>
-      <c r="F87" s="6"/>
-      <c r="G87" s="6"/>
+      <c r="E87" s="3"/>
+      <c r="F87" s="3"/>
+      <c r="G87" s="3"/>
     </row>
     <row r="88" customHeight="1" spans="1:7">
       <c r="A88" s="2">
@@ -3351,9 +3329,9 @@
       <c r="D88" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="E88" s="6"/>
-      <c r="F88" s="6"/>
-      <c r="G88" s="6"/>
+      <c r="E88" s="3"/>
+      <c r="F88" s="3"/>
+      <c r="G88" s="3"/>
     </row>
     <row r="89" customHeight="1" spans="1:7">
       <c r="A89" s="2">
@@ -3369,9 +3347,9 @@
       <c r="D89" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="E89" s="6"/>
-      <c r="F89" s="6"/>
-      <c r="G89" s="6"/>
+      <c r="E89" s="3"/>
+      <c r="F89" s="3"/>
+      <c r="G89" s="3"/>
     </row>
     <row r="90" customHeight="1" spans="1:7">
       <c r="A90" s="2">
@@ -3387,9 +3365,9 @@
       <c r="D90" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="E90" s="6"/>
-      <c r="F90" s="6"/>
-      <c r="G90" s="6"/>
+      <c r="E90" s="3"/>
+      <c r="F90" s="3"/>
+      <c r="G90" s="3"/>
     </row>
     <row r="91" customHeight="1" spans="1:7">
       <c r="A91" s="2">
@@ -3405,9 +3383,9 @@
       <c r="D91" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="E91" s="6"/>
-      <c r="F91" s="6"/>
-      <c r="G91" s="6"/>
+      <c r="E91" s="3"/>
+      <c r="F91" s="3"/>
+      <c r="G91" s="3"/>
     </row>
     <row r="92" customHeight="1" spans="1:7">
       <c r="A92" s="2">
@@ -3423,9 +3401,9 @@
       <c r="D92" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="E92" s="6"/>
-      <c r="F92" s="6"/>
-      <c r="G92" s="6"/>
+      <c r="E92" s="3"/>
+      <c r="F92" s="3"/>
+      <c r="G92" s="3"/>
     </row>
     <row r="93" customHeight="1" spans="1:7">
       <c r="A93" s="2">
@@ -3441,9 +3419,9 @@
       <c r="D93" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="E93" s="6"/>
-      <c r="F93" s="6"/>
-      <c r="G93" s="6"/>
+      <c r="E93" s="3"/>
+      <c r="F93" s="3"/>
+      <c r="G93" s="3"/>
     </row>
     <row r="94" customHeight="1" spans="1:7">
       <c r="A94" s="2">
@@ -3459,9 +3437,9 @@
       <c r="D94" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="E94" s="6"/>
-      <c r="F94" s="6"/>
-      <c r="G94" s="6"/>
+      <c r="E94" s="3"/>
+      <c r="F94" s="3"/>
+      <c r="G94" s="3"/>
     </row>
     <row r="95" customHeight="1" spans="1:7">
       <c r="A95" s="2">
@@ -3477,9 +3455,9 @@
       <c r="D95" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="E95" s="6"/>
-      <c r="F95" s="6"/>
-      <c r="G95" s="6"/>
+      <c r="E95" s="3"/>
+      <c r="F95" s="3"/>
+      <c r="G95" s="3"/>
     </row>
     <row r="96" customHeight="1" spans="1:7">
       <c r="A96" s="2">
@@ -3495,9 +3473,9 @@
       <c r="D96" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="E96" s="6"/>
-      <c r="F96" s="6"/>
-      <c r="G96" s="6"/>
+      <c r="E96" s="3"/>
+      <c r="F96" s="3"/>
+      <c r="G96" s="3"/>
     </row>
     <row r="97" customHeight="1" spans="1:7">
       <c r="A97" s="2">
@@ -3513,9 +3491,9 @@
       <c r="D97" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="E97" s="6"/>
-      <c r="F97" s="6"/>
-      <c r="G97" s="6"/>
+      <c r="E97" s="3"/>
+      <c r="F97" s="3"/>
+      <c r="G97" s="3"/>
     </row>
     <row r="98" customHeight="1" spans="1:7">
       <c r="A98" s="2">
@@ -3531,9 +3509,9 @@
       <c r="D98" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="E98" s="6"/>
-      <c r="F98" s="6"/>
-      <c r="G98" s="6"/>
+      <c r="E98" s="3"/>
+      <c r="F98" s="3"/>
+      <c r="G98" s="3"/>
     </row>
     <row r="99" customHeight="1" spans="1:7">
       <c r="A99" s="2">
@@ -3549,9 +3527,9 @@
       <c r="D99" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="E99" s="6"/>
-      <c r="F99" s="6"/>
-      <c r="G99" s="6"/>
+      <c r="E99" s="3"/>
+      <c r="F99" s="3"/>
+      <c r="G99" s="3"/>
     </row>
     <row r="100" customHeight="1" spans="1:7">
       <c r="A100" s="2">
@@ -3567,9 +3545,9 @@
       <c r="D100" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="E100" s="6"/>
-      <c r="F100" s="6"/>
-      <c r="G100" s="6"/>
+      <c r="E100" s="3"/>
+      <c r="F100" s="3"/>
+      <c r="G100" s="3"/>
     </row>
     <row r="101" customHeight="1" spans="1:7">
       <c r="A101" s="2">
@@ -3585,9 +3563,9 @@
       <c r="D101" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="E101" s="6"/>
-      <c r="F101" s="6"/>
-      <c r="G101" s="6"/>
+      <c r="E101" s="3"/>
+      <c r="F101" s="3"/>
+      <c r="G101" s="3"/>
     </row>
     <row r="102" customHeight="1" spans="1:7">
       <c r="A102" s="2">
@@ -3603,9 +3581,9 @@
       <c r="D102" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="E102" s="6"/>
-      <c r="F102" s="6"/>
-      <c r="G102" s="6"/>
+      <c r="E102" s="3"/>
+      <c r="F102" s="3"/>
+      <c r="G102" s="3"/>
     </row>
     <row r="103" customHeight="1" spans="1:7">
       <c r="A103" s="2">
@@ -3621,9 +3599,9 @@
       <c r="D103" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="E103" s="6"/>
-      <c r="F103" s="6"/>
-      <c r="G103" s="6"/>
+      <c r="E103" s="3"/>
+      <c r="F103" s="3"/>
+      <c r="G103" s="3"/>
     </row>
     <row r="104" customHeight="1" spans="1:7">
       <c r="A104" s="2">
@@ -3639,9 +3617,9 @@
       <c r="D104" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="E104" s="6"/>
-      <c r="F104" s="6"/>
-      <c r="G104" s="6"/>
+      <c r="E104" s="3"/>
+      <c r="F104" s="3"/>
+      <c r="G104" s="3"/>
     </row>
     <row r="105" customHeight="1" spans="1:7">
       <c r="A105" s="2">
@@ -3657,9 +3635,9 @@
       <c r="D105" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="E105" s="6"/>
-      <c r="F105" s="6"/>
-      <c r="G105" s="6"/>
+      <c r="E105" s="3"/>
+      <c r="F105" s="3"/>
+      <c r="G105" s="3"/>
     </row>
     <row r="106" customHeight="1" spans="1:7">
       <c r="A106" s="2">
@@ -3675,9 +3653,9 @@
       <c r="D106" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="E106" s="6"/>
-      <c r="F106" s="6"/>
-      <c r="G106" s="6"/>
+      <c r="E106" s="3"/>
+      <c r="F106" s="3"/>
+      <c r="G106" s="3"/>
     </row>
     <row r="107" customHeight="1" spans="1:7">
       <c r="A107" s="2">
@@ -3693,9 +3671,9 @@
       <c r="D107" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="E107" s="6"/>
-      <c r="F107" s="6"/>
-      <c r="G107" s="6"/>
+      <c r="E107" s="3"/>
+      <c r="F107" s="3"/>
+      <c r="G107" s="3"/>
     </row>
     <row r="108" customHeight="1" spans="1:7">
       <c r="A108" s="2">
@@ -3711,9 +3689,9 @@
       <c r="D108" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="E108" s="6"/>
-      <c r="F108" s="6"/>
-      <c r="G108" s="6"/>
+      <c r="E108" s="3"/>
+      <c r="F108" s="3"/>
+      <c r="G108" s="3"/>
     </row>
     <row r="109" customHeight="1" spans="1:7">
       <c r="A109" s="2">
@@ -3729,9 +3707,9 @@
       <c r="D109" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="E109" s="6"/>
-      <c r="F109" s="6"/>
-      <c r="G109" s="6"/>
+      <c r="E109" s="3"/>
+      <c r="F109" s="3"/>
+      <c r="G109" s="3"/>
     </row>
     <row r="110" customHeight="1" spans="1:7">
       <c r="A110" s="2">
@@ -3747,9 +3725,9 @@
       <c r="D110" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="E110" s="6"/>
-      <c r="F110" s="6"/>
-      <c r="G110" s="6"/>
+      <c r="E110" s="3"/>
+      <c r="F110" s="3"/>
+      <c r="G110" s="3"/>
     </row>
     <row r="111" customHeight="1" spans="1:7">
       <c r="A111" s="2">
@@ -3765,9 +3743,9 @@
       <c r="D111" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="E111" s="6"/>
-      <c r="F111" s="6"/>
-      <c r="G111" s="6"/>
+      <c r="E111" s="3"/>
+      <c r="F111" s="3"/>
+      <c r="G111" s="3"/>
     </row>
     <row r="112" customHeight="1" spans="1:7">
       <c r="A112" s="2">
@@ -3783,9 +3761,9 @@
       <c r="D112" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="E112" s="6"/>
-      <c r="F112" s="6"/>
-      <c r="G112" s="6"/>
+      <c r="E112" s="3"/>
+      <c r="F112" s="3"/>
+      <c r="G112" s="3"/>
     </row>
     <row r="113" customHeight="1" spans="1:7">
       <c r="A113" s="2">
@@ -3801,9 +3779,9 @@
       <c r="D113" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="E113" s="6"/>
-      <c r="F113" s="6"/>
-      <c r="G113" s="6"/>
+      <c r="E113" s="3"/>
+      <c r="F113" s="3"/>
+      <c r="G113" s="3"/>
     </row>
     <row r="114" customHeight="1" spans="1:7">
       <c r="A114" s="2">
@@ -3819,9 +3797,9 @@
       <c r="D114" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="E114" s="6"/>
-      <c r="F114" s="6"/>
-      <c r="G114" s="6"/>
+      <c r="E114" s="3"/>
+      <c r="F114" s="3"/>
+      <c r="G114" s="3"/>
     </row>
     <row r="115" customHeight="1" spans="1:7">
       <c r="A115" s="2">
@@ -3837,9 +3815,9 @@
       <c r="D115" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="E115" s="6"/>
-      <c r="F115" s="6"/>
-      <c r="G115" s="6"/>
+      <c r="E115" s="3"/>
+      <c r="F115" s="3"/>
+      <c r="G115" s="3"/>
     </row>
     <row r="116" customHeight="1" spans="1:7">
       <c r="A116" s="2">
@@ -3855,9 +3833,9 @@
       <c r="D116" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="E116" s="6"/>
-      <c r="F116" s="6"/>
-      <c r="G116" s="6"/>
+      <c r="E116" s="3"/>
+      <c r="F116" s="3"/>
+      <c r="G116" s="3"/>
     </row>
     <row r="117" customHeight="1" spans="1:7">
       <c r="A117" s="2">
@@ -3873,9 +3851,9 @@
       <c r="D117" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="E117" s="6"/>
-      <c r="F117" s="6"/>
-      <c r="G117" s="6"/>
+      <c r="E117" s="3"/>
+      <c r="F117" s="3"/>
+      <c r="G117" s="3"/>
     </row>
     <row r="118" customHeight="1" spans="1:7">
       <c r="A118" s="2">
@@ -3891,9 +3869,9 @@
       <c r="D118" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="E118" s="6"/>
-      <c r="F118" s="6"/>
-      <c r="G118" s="6"/>
+      <c r="E118" s="3"/>
+      <c r="F118" s="3"/>
+      <c r="G118" s="3"/>
     </row>
     <row r="119" customHeight="1" spans="1:7">
       <c r="A119" s="2">
@@ -3909,9 +3887,9 @@
       <c r="D119" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="E119" s="6"/>
-      <c r="F119" s="6"/>
-      <c r="G119" s="6"/>
+      <c r="E119" s="3"/>
+      <c r="F119" s="3"/>
+      <c r="G119" s="3"/>
     </row>
     <row r="120" customHeight="1" spans="1:7">
       <c r="A120" s="2">
@@ -3927,9 +3905,9 @@
       <c r="D120" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="E120" s="6"/>
-      <c r="F120" s="6"/>
-      <c r="G120" s="6"/>
+      <c r="E120" s="3"/>
+      <c r="F120" s="3"/>
+      <c r="G120" s="3"/>
     </row>
     <row r="121" customHeight="1" spans="1:7">
       <c r="A121" s="2">
@@ -3945,9 +3923,9 @@
       <c r="D121" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="E121" s="6"/>
-      <c r="F121" s="6"/>
-      <c r="G121" s="6"/>
+      <c r="E121" s="3"/>
+      <c r="F121" s="3"/>
+      <c r="G121" s="3"/>
     </row>
     <row r="122" customHeight="1" spans="1:7">
       <c r="A122" s="2">
@@ -3963,9 +3941,9 @@
       <c r="D122" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="E122" s="6"/>
-      <c r="F122" s="6"/>
-      <c r="G122" s="6"/>
+      <c r="E122" s="3"/>
+      <c r="F122" s="3"/>
+      <c r="G122" s="3"/>
     </row>
     <row r="123" customHeight="1" spans="1:7">
       <c r="A123" s="2">
@@ -3981,9 +3959,9 @@
       <c r="D123" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="E123" s="6"/>
-      <c r="F123" s="6"/>
-      <c r="G123" s="6"/>
+      <c r="E123" s="3"/>
+      <c r="F123" s="3"/>
+      <c r="G123" s="3"/>
     </row>
     <row r="124" customHeight="1" spans="1:7">
       <c r="A124" s="2">
@@ -3999,9 +3977,9 @@
       <c r="D124" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="E124" s="6"/>
-      <c r="F124" s="6"/>
-      <c r="G124" s="6"/>
+      <c r="E124" s="3"/>
+      <c r="F124" s="3"/>
+      <c r="G124" s="3"/>
     </row>
     <row r="125" customHeight="1" spans="1:7">
       <c r="A125" s="2">
@@ -4017,9 +3995,9 @@
       <c r="D125" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="E125" s="6"/>
-      <c r="F125" s="6"/>
-      <c r="G125" s="6"/>
+      <c r="E125" s="3"/>
+      <c r="F125" s="3"/>
+      <c r="G125" s="3"/>
     </row>
     <row r="126" customHeight="1" spans="1:7">
       <c r="A126" s="2">
@@ -4035,13 +4013,13 @@
       <c r="D126" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="E126" s="6"/>
-      <c r="F126" s="6"/>
-      <c r="G126" s="6"/>
+      <c r="E126" s="3"/>
+      <c r="F126" s="3"/>
+      <c r="G126" s="3"/>
     </row>
     <row r="127" customHeight="1" spans="1:7">
       <c r="A127" s="2">
-        <f t="shared" ref="A127:A190" si="2">A126+1</f>
+        <f t="shared" si="1"/>
         <v>121</v>
       </c>
       <c r="B127" s="4" t="s">
@@ -4053,13 +4031,13 @@
       <c r="D127" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="E127" s="6"/>
-      <c r="F127" s="6"/>
-      <c r="G127" s="6"/>
+      <c r="E127" s="3"/>
+      <c r="F127" s="3"/>
+      <c r="G127" s="3"/>
     </row>
     <row r="128" customHeight="1" spans="1:7">
       <c r="A128" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>122</v>
       </c>
       <c r="B128" s="4" t="s">
@@ -4071,13 +4049,13 @@
       <c r="D128" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="E128" s="6"/>
-      <c r="F128" s="6"/>
-      <c r="G128" s="6"/>
+      <c r="E128" s="3"/>
+      <c r="F128" s="3"/>
+      <c r="G128" s="3"/>
     </row>
     <row r="129" customHeight="1" spans="1:7">
       <c r="A129" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>123</v>
       </c>
       <c r="B129" s="4" t="s">
@@ -4089,13 +4067,13 @@
       <c r="D129" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="E129" s="6"/>
-      <c r="F129" s="6"/>
-      <c r="G129" s="6"/>
+      <c r="E129" s="3"/>
+      <c r="F129" s="3"/>
+      <c r="G129" s="3"/>
     </row>
     <row r="130" customHeight="1" spans="1:7">
       <c r="A130" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>124</v>
       </c>
       <c r="B130" s="4" t="s">
@@ -4107,13 +4085,13 @@
       <c r="D130" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="E130" s="6"/>
-      <c r="F130" s="6"/>
-      <c r="G130" s="6"/>
+      <c r="E130" s="3"/>
+      <c r="F130" s="3"/>
+      <c r="G130" s="3"/>
     </row>
     <row r="131" customHeight="1" spans="1:7">
       <c r="A131" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>125</v>
       </c>
       <c r="B131" s="4" t="s">
@@ -4125,13 +4103,13 @@
       <c r="D131" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="E131" s="6"/>
-      <c r="F131" s="6"/>
-      <c r="G131" s="6"/>
+      <c r="E131" s="3"/>
+      <c r="F131" s="3"/>
+      <c r="G131" s="3"/>
     </row>
     <row r="132" customHeight="1" spans="1:7">
       <c r="A132" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>126</v>
       </c>
       <c r="B132" s="4" t="s">
@@ -4143,13 +4121,13 @@
       <c r="D132" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="E132" s="6"/>
-      <c r="F132" s="6"/>
-      <c r="G132" s="6"/>
+      <c r="E132" s="3"/>
+      <c r="F132" s="3"/>
+      <c r="G132" s="3"/>
     </row>
     <row r="133" customHeight="1" spans="1:7">
       <c r="A133" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>127</v>
       </c>
       <c r="B133" s="4" t="s">
@@ -4161,13 +4139,13 @@
       <c r="D133" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="E133" s="6"/>
-      <c r="F133" s="6"/>
-      <c r="G133" s="6"/>
+      <c r="E133" s="3"/>
+      <c r="F133" s="3"/>
+      <c r="G133" s="3"/>
     </row>
     <row r="134" customHeight="1" spans="1:7">
       <c r="A134" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>128</v>
       </c>
       <c r="B134" s="4" t="s">
@@ -4179,13 +4157,13 @@
       <c r="D134" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="E134" s="6"/>
-      <c r="F134" s="6"/>
-      <c r="G134" s="6"/>
+      <c r="E134" s="3"/>
+      <c r="F134" s="3"/>
+      <c r="G134" s="3"/>
     </row>
     <row r="135" customHeight="1" spans="1:7">
       <c r="A135" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>129</v>
       </c>
       <c r="B135" s="4" t="s">
@@ -4197,13 +4175,13 @@
       <c r="D135" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="E135" s="6"/>
-      <c r="F135" s="6"/>
-      <c r="G135" s="6"/>
+      <c r="E135" s="3"/>
+      <c r="F135" s="3"/>
+      <c r="G135" s="3"/>
     </row>
     <row r="136" customHeight="1" spans="1:7">
       <c r="A136" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="A136:A199" si="2">A135+1</f>
         <v>130</v>
       </c>
       <c r="B136" s="4" t="s">
@@ -4215,9 +4193,9 @@
       <c r="D136" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="E136" s="6"/>
-      <c r="F136" s="6"/>
-      <c r="G136" s="6"/>
+      <c r="E136" s="3"/>
+      <c r="F136" s="3"/>
+      <c r="G136" s="3"/>
     </row>
     <row r="137" customHeight="1" spans="1:7">
       <c r="A137" s="2">
@@ -4233,9 +4211,9 @@
       <c r="D137" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="E137" s="6"/>
-      <c r="F137" s="6"/>
-      <c r="G137" s="6"/>
+      <c r="E137" s="3"/>
+      <c r="F137" s="3"/>
+      <c r="G137" s="3"/>
     </row>
     <row r="138" customHeight="1" spans="1:7">
       <c r="A138" s="2">
@@ -4251,9 +4229,9 @@
       <c r="D138" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="E138" s="6"/>
-      <c r="F138" s="6"/>
-      <c r="G138" s="6"/>
+      <c r="E138" s="3"/>
+      <c r="F138" s="3"/>
+      <c r="G138" s="3"/>
     </row>
     <row r="139" customHeight="1" spans="1:7">
       <c r="A139" s="2">
@@ -4269,9 +4247,9 @@
       <c r="D139" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="E139" s="6"/>
-      <c r="F139" s="6"/>
-      <c r="G139" s="6"/>
+      <c r="E139" s="3"/>
+      <c r="F139" s="3"/>
+      <c r="G139" s="3"/>
     </row>
     <row r="140" customHeight="1" spans="1:7">
       <c r="A140" s="2">
@@ -4287,9 +4265,9 @@
       <c r="D140" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="E140" s="6"/>
-      <c r="F140" s="6"/>
-      <c r="G140" s="6"/>
+      <c r="E140" s="3"/>
+      <c r="F140" s="3"/>
+      <c r="G140" s="3"/>
     </row>
     <row r="141" customHeight="1" spans="1:7">
       <c r="A141" s="2">
@@ -4305,9 +4283,9 @@
       <c r="D141" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="E141" s="6"/>
-      <c r="F141" s="6"/>
-      <c r="G141" s="6"/>
+      <c r="E141" s="3"/>
+      <c r="F141" s="3"/>
+      <c r="G141" s="3"/>
     </row>
     <row r="142" customHeight="1" spans="1:7">
       <c r="A142" s="2">
@@ -4323,9 +4301,9 @@
       <c r="D142" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="E142" s="6"/>
-      <c r="F142" s="6"/>
-      <c r="G142" s="6"/>
+      <c r="E142" s="3"/>
+      <c r="F142" s="3"/>
+      <c r="G142" s="3"/>
     </row>
     <row r="143" customHeight="1" spans="1:7">
       <c r="A143" s="2">
@@ -4341,9 +4319,9 @@
       <c r="D143" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="E143" s="6"/>
-      <c r="F143" s="6"/>
-      <c r="G143" s="6"/>
+      <c r="E143" s="3"/>
+      <c r="F143" s="3"/>
+      <c r="G143" s="3"/>
     </row>
     <row r="144" customHeight="1" spans="1:7">
       <c r="A144" s="2">
@@ -4359,9 +4337,9 @@
       <c r="D144" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="E144" s="6"/>
-      <c r="F144" s="6"/>
-      <c r="G144" s="6"/>
+      <c r="E144" s="3"/>
+      <c r="F144" s="3"/>
+      <c r="G144" s="3"/>
     </row>
     <row r="145" customHeight="1" spans="1:7">
       <c r="A145" s="2">
@@ -4377,9 +4355,9 @@
       <c r="D145" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="E145" s="6"/>
-      <c r="F145" s="6"/>
-      <c r="G145" s="6"/>
+      <c r="E145" s="3"/>
+      <c r="F145" s="3"/>
+      <c r="G145" s="3"/>
     </row>
     <row r="146" customHeight="1" spans="1:7">
       <c r="A146" s="2">
@@ -4395,9 +4373,9 @@
       <c r="D146" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="E146" s="6"/>
-      <c r="F146" s="6"/>
-      <c r="G146" s="6"/>
+      <c r="E146" s="3"/>
+      <c r="F146" s="3"/>
+      <c r="G146" s="3"/>
     </row>
     <row r="147" customHeight="1" spans="1:7">
       <c r="A147" s="2">
@@ -4413,9 +4391,9 @@
       <c r="D147" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="E147" s="6"/>
-      <c r="F147" s="6"/>
-      <c r="G147" s="6"/>
+      <c r="E147" s="3"/>
+      <c r="F147" s="3"/>
+      <c r="G147" s="3"/>
     </row>
     <row r="148" customHeight="1" spans="1:7">
       <c r="A148" s="2">
@@ -4431,9 +4409,9 @@
       <c r="D148" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="E148" s="6"/>
-      <c r="F148" s="6"/>
-      <c r="G148" s="6"/>
+      <c r="E148" s="3"/>
+      <c r="F148" s="3"/>
+      <c r="G148" s="3"/>
     </row>
     <row r="149" customHeight="1" spans="1:7">
       <c r="A149" s="2">
@@ -4449,9 +4427,9 @@
       <c r="D149" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="E149" s="6"/>
-      <c r="F149" s="6"/>
-      <c r="G149" s="6"/>
+      <c r="E149" s="3"/>
+      <c r="F149" s="3"/>
+      <c r="G149" s="3"/>
     </row>
     <row r="150" customHeight="1" spans="1:7">
       <c r="A150" s="2">
@@ -4467,9 +4445,9 @@
       <c r="D150" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="E150" s="6"/>
-      <c r="F150" s="6"/>
-      <c r="G150" s="6"/>
+      <c r="E150" s="3"/>
+      <c r="F150" s="3"/>
+      <c r="G150" s="3"/>
     </row>
     <row r="151" customHeight="1" spans="1:7">
       <c r="A151" s="2">
@@ -4485,9 +4463,9 @@
       <c r="D151" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="E151" s="6"/>
-      <c r="F151" s="6"/>
-      <c r="G151" s="6"/>
+      <c r="E151" s="3"/>
+      <c r="F151" s="3"/>
+      <c r="G151" s="3"/>
     </row>
     <row r="152" customHeight="1" spans="1:7">
       <c r="A152" s="2">
@@ -4503,9 +4481,9 @@
       <c r="D152" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="E152" s="6"/>
-      <c r="F152" s="6"/>
-      <c r="G152" s="6"/>
+      <c r="E152" s="3"/>
+      <c r="F152" s="3"/>
+      <c r="G152" s="3"/>
     </row>
     <row r="153" customHeight="1" spans="1:7">
       <c r="A153" s="2">
@@ -4521,9 +4499,9 @@
       <c r="D153" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="E153" s="6"/>
-      <c r="F153" s="6"/>
-      <c r="G153" s="6"/>
+      <c r="E153" s="3"/>
+      <c r="F153" s="3"/>
+      <c r="G153" s="3"/>
     </row>
     <row r="154" customHeight="1" spans="1:7">
       <c r="A154" s="2">
@@ -4539,9 +4517,9 @@
       <c r="D154" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="E154" s="6"/>
-      <c r="F154" s="6"/>
-      <c r="G154" s="6"/>
+      <c r="E154" s="3"/>
+      <c r="F154" s="3"/>
+      <c r="G154" s="3"/>
     </row>
     <row r="155" customHeight="1" spans="1:7">
       <c r="A155" s="2">
@@ -4557,9 +4535,9 @@
       <c r="D155" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="E155" s="6"/>
-      <c r="F155" s="6"/>
-      <c r="G155" s="6"/>
+      <c r="E155" s="3"/>
+      <c r="F155" s="3"/>
+      <c r="G155" s="3"/>
     </row>
     <row r="156" customHeight="1" spans="1:7">
       <c r="A156" s="2">
@@ -4575,9 +4553,9 @@
       <c r="D156" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="E156" s="6"/>
-      <c r="F156" s="6"/>
-      <c r="G156" s="6"/>
+      <c r="E156" s="3"/>
+      <c r="F156" s="3"/>
+      <c r="G156" s="3"/>
     </row>
     <row r="157" customHeight="1" spans="1:7">
       <c r="A157" s="2">
@@ -4593,9 +4571,9 @@
       <c r="D157" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="E157" s="6"/>
-      <c r="F157" s="6"/>
-      <c r="G157" s="6"/>
+      <c r="E157" s="3"/>
+      <c r="F157" s="3"/>
+      <c r="G157" s="3"/>
     </row>
     <row r="158" customHeight="1" spans="1:7">
       <c r="A158" s="2">
@@ -4611,9 +4589,9 @@
       <c r="D158" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="E158" s="6"/>
-      <c r="F158" s="6"/>
-      <c r="G158" s="6"/>
+      <c r="E158" s="3"/>
+      <c r="F158" s="3"/>
+      <c r="G158" s="3"/>
     </row>
     <row r="159" customHeight="1" spans="1:7">
       <c r="A159" s="2">
@@ -4629,9 +4607,9 @@
       <c r="D159" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="E159" s="6"/>
-      <c r="F159" s="6"/>
-      <c r="G159" s="6"/>
+      <c r="E159" s="3"/>
+      <c r="F159" s="3"/>
+      <c r="G159" s="3"/>
     </row>
     <row r="160" customHeight="1" spans="1:7">
       <c r="A160" s="2">
@@ -4647,9 +4625,9 @@
       <c r="D160" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="E160" s="6"/>
-      <c r="F160" s="6"/>
-      <c r="G160" s="6"/>
+      <c r="E160" s="3"/>
+      <c r="F160" s="3"/>
+      <c r="G160" s="3"/>
     </row>
     <row r="161" customHeight="1" spans="1:7">
       <c r="A161" s="2">
@@ -4665,9 +4643,9 @@
       <c r="D161" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="E161" s="6"/>
-      <c r="F161" s="6"/>
-      <c r="G161" s="6"/>
+      <c r="E161" s="3"/>
+      <c r="F161" s="3"/>
+      <c r="G161" s="3"/>
     </row>
     <row r="162" customHeight="1" spans="1:7">
       <c r="A162" s="2">
@@ -4683,9 +4661,9 @@
       <c r="D162" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="E162" s="6"/>
-      <c r="F162" s="6"/>
-      <c r="G162" s="6"/>
+      <c r="E162" s="3"/>
+      <c r="F162" s="3"/>
+      <c r="G162" s="3"/>
     </row>
     <row r="163" customHeight="1" spans="1:7">
       <c r="A163" s="2">
@@ -4701,9 +4679,9 @@
       <c r="D163" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="E163" s="6"/>
-      <c r="F163" s="6"/>
-      <c r="G163" s="6"/>
+      <c r="E163" s="3"/>
+      <c r="F163" s="3"/>
+      <c r="G163" s="3"/>
     </row>
     <row r="164" customHeight="1" spans="1:7">
       <c r="A164" s="2">
@@ -4719,9 +4697,9 @@
       <c r="D164" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="E164" s="6"/>
-      <c r="F164" s="6"/>
-      <c r="G164" s="6"/>
+      <c r="E164" s="3"/>
+      <c r="F164" s="3"/>
+      <c r="G164" s="3"/>
     </row>
     <row r="165" customHeight="1" spans="1:7">
       <c r="A165" s="2">
@@ -4737,9 +4715,9 @@
       <c r="D165" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="E165" s="6"/>
-      <c r="F165" s="6"/>
-      <c r="G165" s="6"/>
+      <c r="E165" s="3"/>
+      <c r="F165" s="3"/>
+      <c r="G165" s="3"/>
     </row>
     <row r="166" customHeight="1" spans="1:7">
       <c r="A166" s="2">
@@ -4755,9 +4733,9 @@
       <c r="D166" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="E166" s="6"/>
-      <c r="F166" s="6"/>
-      <c r="G166" s="6"/>
+      <c r="E166" s="3"/>
+      <c r="F166" s="3"/>
+      <c r="G166" s="3"/>
     </row>
     <row r="167" customHeight="1" spans="1:7">
       <c r="A167" s="2">
@@ -4773,9 +4751,9 @@
       <c r="D167" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="E167" s="6"/>
-      <c r="F167" s="6"/>
-      <c r="G167" s="6"/>
+      <c r="E167" s="3"/>
+      <c r="F167" s="3"/>
+      <c r="G167" s="3"/>
     </row>
     <row r="168" customHeight="1" spans="1:7">
       <c r="A168" s="2">
@@ -4791,9 +4769,9 @@
       <c r="D168" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="E168" s="6"/>
-      <c r="F168" s="6"/>
-      <c r="G168" s="6"/>
+      <c r="E168" s="3"/>
+      <c r="F168" s="3"/>
+      <c r="G168" s="3"/>
     </row>
     <row r="169" customHeight="1" spans="1:7">
       <c r="A169" s="2">
@@ -4809,9 +4787,9 @@
       <c r="D169" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="E169" s="6"/>
-      <c r="F169" s="6"/>
-      <c r="G169" s="6"/>
+      <c r="E169" s="3"/>
+      <c r="F169" s="3"/>
+      <c r="G169" s="3"/>
     </row>
     <row r="170" customHeight="1" spans="1:7">
       <c r="A170" s="2">
@@ -4827,9 +4805,9 @@
       <c r="D170" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="E170" s="6"/>
-      <c r="F170" s="6"/>
-      <c r="G170" s="6"/>
+      <c r="E170" s="3"/>
+      <c r="F170" s="3"/>
+      <c r="G170" s="3"/>
     </row>
     <row r="171" customHeight="1" spans="1:7">
       <c r="A171" s="2">
@@ -4845,9 +4823,9 @@
       <c r="D171" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="E171" s="6"/>
-      <c r="F171" s="6"/>
-      <c r="G171" s="6"/>
+      <c r="E171" s="3"/>
+      <c r="F171" s="3"/>
+      <c r="G171" s="3"/>
     </row>
     <row r="172" customHeight="1" spans="1:7">
       <c r="A172" s="2">
@@ -4863,9 +4841,9 @@
       <c r="D172" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="E172" s="6"/>
-      <c r="F172" s="6"/>
-      <c r="G172" s="6"/>
+      <c r="E172" s="3"/>
+      <c r="F172" s="3"/>
+      <c r="G172" s="3"/>
     </row>
     <row r="173" customHeight="1" spans="1:7">
       <c r="A173" s="2">
@@ -4881,9 +4859,9 @@
       <c r="D173" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="E173" s="6"/>
-      <c r="F173" s="6"/>
-      <c r="G173" s="6"/>
+      <c r="E173" s="3"/>
+      <c r="F173" s="3"/>
+      <c r="G173" s="3"/>
     </row>
     <row r="174" customHeight="1" spans="1:7">
       <c r="A174" s="2">
@@ -4899,9 +4877,9 @@
       <c r="D174" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="E174" s="6"/>
-      <c r="F174" s="6"/>
-      <c r="G174" s="6"/>
+      <c r="E174" s="3"/>
+      <c r="F174" s="3"/>
+      <c r="G174" s="3"/>
     </row>
     <row r="175" customHeight="1" spans="1:7">
       <c r="A175" s="2">
@@ -4917,9 +4895,9 @@
       <c r="D175" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="E175" s="6"/>
-      <c r="F175" s="6"/>
-      <c r="G175" s="6"/>
+      <c r="E175" s="3"/>
+      <c r="F175" s="3"/>
+      <c r="G175" s="3"/>
     </row>
     <row r="176" customHeight="1" spans="1:7">
       <c r="A176" s="2">
@@ -4935,9 +4913,9 @@
       <c r="D176" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="E176" s="6"/>
-      <c r="F176" s="6"/>
-      <c r="G176" s="6"/>
+      <c r="E176" s="3"/>
+      <c r="F176" s="3"/>
+      <c r="G176" s="3"/>
     </row>
     <row r="177" customHeight="1" spans="1:7">
       <c r="A177" s="2">
@@ -4953,9 +4931,9 @@
       <c r="D177" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="E177" s="6"/>
-      <c r="F177" s="6"/>
-      <c r="G177" s="6"/>
+      <c r="E177" s="3"/>
+      <c r="F177" s="3"/>
+      <c r="G177" s="3"/>
     </row>
     <row r="178" customHeight="1" spans="1:7">
       <c r="A178" s="2">
@@ -4971,9 +4949,9 @@
       <c r="D178" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="E178" s="6"/>
-      <c r="F178" s="6"/>
-      <c r="G178" s="6"/>
+      <c r="E178" s="3"/>
+      <c r="F178" s="3"/>
+      <c r="G178" s="3"/>
     </row>
     <row r="179" customHeight="1" spans="1:7">
       <c r="A179" s="2">
@@ -4989,9 +4967,9 @@
       <c r="D179" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="E179" s="6"/>
-      <c r="F179" s="6"/>
-      <c r="G179" s="6"/>
+      <c r="E179" s="3"/>
+      <c r="F179" s="3"/>
+      <c r="G179" s="3"/>
     </row>
     <row r="180" customHeight="1" spans="1:7">
       <c r="A180" s="2">
@@ -5007,9 +4985,9 @@
       <c r="D180" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="E180" s="6"/>
-      <c r="F180" s="6"/>
-      <c r="G180" s="6"/>
+      <c r="E180" s="3"/>
+      <c r="F180" s="3"/>
+      <c r="G180" s="3"/>
     </row>
     <row r="181" customHeight="1" spans="1:7">
       <c r="A181" s="2">
@@ -5025,9 +5003,9 @@
       <c r="D181" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="E181" s="6"/>
-      <c r="F181" s="6"/>
-      <c r="G181" s="6"/>
+      <c r="E181" s="3"/>
+      <c r="F181" s="3"/>
+      <c r="G181" s="3"/>
     </row>
     <row r="182" customHeight="1" spans="1:7">
       <c r="A182" s="2">
@@ -5043,9 +5021,9 @@
       <c r="D182" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="E182" s="6"/>
-      <c r="F182" s="6"/>
-      <c r="G182" s="6"/>
+      <c r="E182" s="3"/>
+      <c r="F182" s="3"/>
+      <c r="G182" s="3"/>
     </row>
     <row r="183" customHeight="1" spans="1:7">
       <c r="A183" s="2">
@@ -5061,9 +5039,9 @@
       <c r="D183" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="E183" s="6"/>
-      <c r="F183" s="6"/>
-      <c r="G183" s="6"/>
+      <c r="E183" s="3"/>
+      <c r="F183" s="3"/>
+      <c r="G183" s="3"/>
     </row>
     <row r="184" customHeight="1" spans="1:7">
       <c r="A184" s="2">
@@ -5079,9 +5057,9 @@
       <c r="D184" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="E184" s="6"/>
-      <c r="F184" s="6"/>
-      <c r="G184" s="6"/>
+      <c r="E184" s="3"/>
+      <c r="F184" s="3"/>
+      <c r="G184" s="3"/>
     </row>
     <row r="185" customHeight="1" spans="1:7">
       <c r="A185" s="2">
@@ -5097,9 +5075,9 @@
       <c r="D185" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="E185" s="6"/>
-      <c r="F185" s="6"/>
-      <c r="G185" s="6"/>
+      <c r="E185" s="3"/>
+      <c r="F185" s="3"/>
+      <c r="G185" s="3"/>
     </row>
     <row r="186" customHeight="1" spans="1:7">
       <c r="A186" s="2">
@@ -5115,9 +5093,9 @@
       <c r="D186" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="E186" s="6"/>
-      <c r="F186" s="6"/>
-      <c r="G186" s="6"/>
+      <c r="E186" s="3"/>
+      <c r="F186" s="3"/>
+      <c r="G186" s="3"/>
     </row>
     <row r="187" customHeight="1" spans="1:7">
       <c r="A187" s="2">
@@ -5133,9 +5111,9 @@
       <c r="D187" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="E187" s="6"/>
-      <c r="F187" s="6"/>
-      <c r="G187" s="6"/>
+      <c r="E187" s="3"/>
+      <c r="F187" s="3"/>
+      <c r="G187" s="3"/>
     </row>
     <row r="188" customHeight="1" spans="1:7">
       <c r="A188" s="2">
@@ -5151,9 +5129,9 @@
       <c r="D188" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="E188" s="6"/>
-      <c r="F188" s="6"/>
-      <c r="G188" s="6"/>
+      <c r="E188" s="3"/>
+      <c r="F188" s="3"/>
+      <c r="G188" s="3"/>
     </row>
     <row r="189" customHeight="1" spans="1:7">
       <c r="A189" s="2">
@@ -5169,9 +5147,9 @@
       <c r="D189" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="E189" s="6"/>
-      <c r="F189" s="6"/>
-      <c r="G189" s="6"/>
+      <c r="E189" s="3"/>
+      <c r="F189" s="3"/>
+      <c r="G189" s="3"/>
     </row>
     <row r="190" customHeight="1" spans="1:7">
       <c r="A190" s="2">
@@ -5187,13 +5165,13 @@
       <c r="D190" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="E190" s="6"/>
-      <c r="F190" s="6"/>
-      <c r="G190" s="6"/>
+      <c r="E190" s="3"/>
+      <c r="F190" s="3"/>
+      <c r="G190" s="3"/>
     </row>
     <row r="191" customHeight="1" spans="1:7">
       <c r="A191" s="2">
-        <f t="shared" ref="A191:A254" si="3">A190+1</f>
+        <f t="shared" si="2"/>
         <v>185</v>
       </c>
       <c r="B191" s="4" t="s">
@@ -5205,13 +5183,13 @@
       <c r="D191" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="E191" s="6"/>
-      <c r="F191" s="6"/>
-      <c r="G191" s="6"/>
+      <c r="E191" s="3"/>
+      <c r="F191" s="3"/>
+      <c r="G191" s="3"/>
     </row>
     <row r="192" customHeight="1" spans="1:7">
       <c r="A192" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>186</v>
       </c>
       <c r="B192" s="4" t="s">
@@ -5223,13 +5201,13 @@
       <c r="D192" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="E192" s="6"/>
-      <c r="F192" s="6"/>
-      <c r="G192" s="6"/>
+      <c r="E192" s="3"/>
+      <c r="F192" s="3"/>
+      <c r="G192" s="3"/>
     </row>
     <row r="193" customHeight="1" spans="1:7">
       <c r="A193" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>187</v>
       </c>
       <c r="B193" s="4" t="s">
@@ -5241,13 +5219,13 @@
       <c r="D193" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="E193" s="6"/>
-      <c r="F193" s="6"/>
-      <c r="G193" s="6"/>
+      <c r="E193" s="3"/>
+      <c r="F193" s="3"/>
+      <c r="G193" s="3"/>
     </row>
     <row r="194" customHeight="1" spans="1:7">
       <c r="A194" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>188</v>
       </c>
       <c r="B194" s="4" t="s">
@@ -5259,13 +5237,13 @@
       <c r="D194" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="E194" s="6"/>
-      <c r="F194" s="6"/>
-      <c r="G194" s="6"/>
+      <c r="E194" s="3"/>
+      <c r="F194" s="3"/>
+      <c r="G194" s="3"/>
     </row>
     <row r="195" customHeight="1" spans="1:7">
       <c r="A195" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>189</v>
       </c>
       <c r="B195" s="4" t="s">
@@ -5277,13 +5255,13 @@
       <c r="D195" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="E195" s="6"/>
-      <c r="F195" s="6"/>
-      <c r="G195" s="6"/>
+      <c r="E195" s="3"/>
+      <c r="F195" s="3"/>
+      <c r="G195" s="3"/>
     </row>
     <row r="196" customHeight="1" spans="1:7">
       <c r="A196" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>190</v>
       </c>
       <c r="B196" s="4" t="s">
@@ -5295,13 +5273,13 @@
       <c r="D196" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="E196" s="6"/>
-      <c r="F196" s="6"/>
-      <c r="G196" s="6"/>
+      <c r="E196" s="3"/>
+      <c r="F196" s="3"/>
+      <c r="G196" s="3"/>
     </row>
     <row r="197" customHeight="1" spans="1:7">
       <c r="A197" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>191</v>
       </c>
       <c r="B197" s="4" t="s">
@@ -5313,13 +5291,13 @@
       <c r="D197" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="E197" s="6"/>
-      <c r="F197" s="6"/>
-      <c r="G197" s="6"/>
+      <c r="E197" s="3"/>
+      <c r="F197" s="3"/>
+      <c r="G197" s="3"/>
     </row>
     <row r="198" customHeight="1" spans="1:7">
       <c r="A198" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>192</v>
       </c>
       <c r="B198" s="4" t="s">
@@ -5331,13 +5309,13 @@
       <c r="D198" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="E198" s="6"/>
-      <c r="F198" s="6"/>
-      <c r="G198" s="6"/>
+      <c r="E198" s="3"/>
+      <c r="F198" s="3"/>
+      <c r="G198" s="3"/>
     </row>
     <row r="199" customHeight="1" spans="1:7">
       <c r="A199" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>193</v>
       </c>
       <c r="B199" s="4" t="s">
@@ -5349,13 +5327,13 @@
       <c r="D199" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="E199" s="6"/>
-      <c r="F199" s="6"/>
-      <c r="G199" s="6"/>
+      <c r="E199" s="3"/>
+      <c r="F199" s="3"/>
+      <c r="G199" s="3"/>
     </row>
     <row r="200" customHeight="1" spans="1:7">
       <c r="A200" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="A200:A263" si="3">A199+1</f>
         <v>194</v>
       </c>
       <c r="B200" s="4" t="s">
@@ -5367,9 +5345,9 @@
       <c r="D200" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="E200" s="6"/>
-      <c r="F200" s="6"/>
-      <c r="G200" s="6"/>
+      <c r="E200" s="3"/>
+      <c r="F200" s="3"/>
+      <c r="G200" s="3"/>
     </row>
     <row r="201" customHeight="1" spans="1:7">
       <c r="A201" s="2">
@@ -5385,9 +5363,9 @@
       <c r="D201" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="E201" s="6"/>
-      <c r="F201" s="6"/>
-      <c r="G201" s="6"/>
+      <c r="E201" s="3"/>
+      <c r="F201" s="3"/>
+      <c r="G201" s="3"/>
     </row>
     <row r="202" customHeight="1" spans="1:7">
       <c r="A202" s="2">
@@ -5403,9 +5381,9 @@
       <c r="D202" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="E202" s="6"/>
-      <c r="F202" s="6"/>
-      <c r="G202" s="6"/>
+      <c r="E202" s="3"/>
+      <c r="F202" s="3"/>
+      <c r="G202" s="3"/>
     </row>
     <row r="203" customHeight="1" spans="1:7">
       <c r="A203" s="2">
@@ -5421,9 +5399,9 @@
       <c r="D203" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="E203" s="6"/>
-      <c r="F203" s="6"/>
-      <c r="G203" s="6"/>
+      <c r="E203" s="3"/>
+      <c r="F203" s="3"/>
+      <c r="G203" s="3"/>
     </row>
     <row r="204" customHeight="1" spans="1:7">
       <c r="A204" s="2">
@@ -5439,9 +5417,9 @@
       <c r="D204" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="E204" s="6"/>
-      <c r="F204" s="6"/>
-      <c r="G204" s="6"/>
+      <c r="E204" s="3"/>
+      <c r="F204" s="3"/>
+      <c r="G204" s="3"/>
     </row>
     <row r="205" customHeight="1" spans="1:7">
       <c r="A205" s="2">
@@ -5457,9 +5435,9 @@
       <c r="D205" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="E205" s="6"/>
-      <c r="F205" s="6"/>
-      <c r="G205" s="6"/>
+      <c r="E205" s="3"/>
+      <c r="F205" s="3"/>
+      <c r="G205" s="3"/>
     </row>
     <row r="206" customHeight="1" spans="1:7">
       <c r="A206" s="2">
@@ -5475,9 +5453,9 @@
       <c r="D206" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="E206" s="6"/>
-      <c r="F206" s="6"/>
-      <c r="G206" s="6"/>
+      <c r="E206" s="3"/>
+      <c r="F206" s="3"/>
+      <c r="G206" s="3"/>
     </row>
     <row r="207" customHeight="1" spans="1:7">
       <c r="A207" s="2">
@@ -5493,9 +5471,9 @@
       <c r="D207" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="E207" s="6"/>
-      <c r="F207" s="6"/>
-      <c r="G207" s="6"/>
+      <c r="E207" s="3"/>
+      <c r="F207" s="3"/>
+      <c r="G207" s="3"/>
     </row>
     <row r="208" customHeight="1" spans="1:7">
       <c r="A208" s="2">
@@ -5511,9 +5489,9 @@
       <c r="D208" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="E208" s="6"/>
-      <c r="F208" s="6"/>
-      <c r="G208" s="6"/>
+      <c r="E208" s="3"/>
+      <c r="F208" s="3"/>
+      <c r="G208" s="3"/>
     </row>
     <row r="209" customHeight="1" spans="1:7">
       <c r="A209" s="2">
@@ -5529,9 +5507,9 @@
       <c r="D209" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="E209" s="6"/>
-      <c r="F209" s="6"/>
-      <c r="G209" s="6"/>
+      <c r="E209" s="3"/>
+      <c r="F209" s="3"/>
+      <c r="G209" s="3"/>
     </row>
     <row r="210" customHeight="1" spans="1:7">
       <c r="A210" s="2">
@@ -5547,9 +5525,9 @@
       <c r="D210" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="E210" s="6"/>
-      <c r="F210" s="6"/>
-      <c r="G210" s="6"/>
+      <c r="E210" s="3"/>
+      <c r="F210" s="3"/>
+      <c r="G210" s="3"/>
     </row>
     <row r="211" customHeight="1" spans="1:7">
       <c r="A211" s="2">
@@ -5565,9 +5543,9 @@
       <c r="D211" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="E211" s="6"/>
-      <c r="F211" s="6"/>
-      <c r="G211" s="6"/>
+      <c r="E211" s="3"/>
+      <c r="F211" s="3"/>
+      <c r="G211" s="3"/>
     </row>
     <row r="212" customHeight="1" spans="1:7">
       <c r="A212" s="2">
@@ -5583,9 +5561,9 @@
       <c r="D212" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="E212" s="6"/>
-      <c r="F212" s="6"/>
-      <c r="G212" s="6"/>
+      <c r="E212" s="3"/>
+      <c r="F212" s="3"/>
+      <c r="G212" s="3"/>
     </row>
     <row r="213" customHeight="1" spans="1:7">
       <c r="A213" s="2">
@@ -5601,9 +5579,9 @@
       <c r="D213" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="E213" s="6"/>
-      <c r="F213" s="6"/>
-      <c r="G213" s="6"/>
+      <c r="E213" s="3"/>
+      <c r="F213" s="3"/>
+      <c r="G213" s="3"/>
     </row>
     <row r="214" customHeight="1" spans="1:7">
       <c r="A214" s="2">
@@ -5619,9 +5597,9 @@
       <c r="D214" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="E214" s="6"/>
-      <c r="F214" s="6"/>
-      <c r="G214" s="6"/>
+      <c r="E214" s="3"/>
+      <c r="F214" s="3"/>
+      <c r="G214" s="3"/>
     </row>
     <row r="215" customHeight="1" spans="1:7">
       <c r="A215" s="2">
@@ -5637,9 +5615,9 @@
       <c r="D215" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="E215" s="6"/>
-      <c r="F215" s="6"/>
-      <c r="G215" s="6"/>
+      <c r="E215" s="3"/>
+      <c r="F215" s="3"/>
+      <c r="G215" s="3"/>
     </row>
     <row r="216" customHeight="1" spans="1:7">
       <c r="A216" s="2">
@@ -5655,9 +5633,9 @@
       <c r="D216" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="E216" s="6"/>
-      <c r="F216" s="6"/>
-      <c r="G216" s="6"/>
+      <c r="E216" s="3"/>
+      <c r="F216" s="3"/>
+      <c r="G216" s="3"/>
     </row>
     <row r="217" customHeight="1" spans="1:7">
       <c r="A217" s="2">
@@ -5673,9 +5651,9 @@
       <c r="D217" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="E217" s="6"/>
-      <c r="F217" s="6"/>
-      <c r="G217" s="6"/>
+      <c r="E217" s="3"/>
+      <c r="F217" s="3"/>
+      <c r="G217" s="3"/>
     </row>
     <row r="218" customHeight="1" spans="1:7">
       <c r="A218" s="2">
@@ -5691,9 +5669,9 @@
       <c r="D218" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="E218" s="6"/>
-      <c r="F218" s="6"/>
-      <c r="G218" s="6"/>
+      <c r="E218" s="3"/>
+      <c r="F218" s="3"/>
+      <c r="G218" s="3"/>
     </row>
     <row r="219" customHeight="1" spans="1:7">
       <c r="A219" s="2">
@@ -5709,9 +5687,9 @@
       <c r="D219" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="E219" s="6"/>
-      <c r="F219" s="6"/>
-      <c r="G219" s="6"/>
+      <c r="E219" s="3"/>
+      <c r="F219" s="3"/>
+      <c r="G219" s="3"/>
     </row>
     <row r="220" customHeight="1" spans="1:7">
       <c r="A220" s="2">
@@ -5727,9 +5705,9 @@
       <c r="D220" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="E220" s="6"/>
-      <c r="F220" s="6"/>
-      <c r="G220" s="6"/>
+      <c r="E220" s="3"/>
+      <c r="F220" s="3"/>
+      <c r="G220" s="3"/>
     </row>
     <row r="221" customHeight="1" spans="1:7">
       <c r="A221" s="2">
@@ -5745,9 +5723,9 @@
       <c r="D221" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="E221" s="6"/>
-      <c r="F221" s="6"/>
-      <c r="G221" s="6"/>
+      <c r="E221" s="3"/>
+      <c r="F221" s="3"/>
+      <c r="G221" s="3"/>
     </row>
     <row r="222" customHeight="1" spans="1:7">
       <c r="A222" s="2">
@@ -5763,9 +5741,9 @@
       <c r="D222" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="E222" s="6"/>
-      <c r="F222" s="6"/>
-      <c r="G222" s="6"/>
+      <c r="E222" s="3"/>
+      <c r="F222" s="3"/>
+      <c r="G222" s="3"/>
     </row>
     <row r="223" customHeight="1" spans="1:7">
       <c r="A223" s="2">
@@ -5781,9 +5759,9 @@
       <c r="D223" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="E223" s="6"/>
-      <c r="F223" s="6"/>
-      <c r="G223" s="6"/>
+      <c r="E223" s="3"/>
+      <c r="F223" s="3"/>
+      <c r="G223" s="3"/>
     </row>
     <row r="224" customHeight="1" spans="1:7">
       <c r="A224" s="2">
@@ -5799,9 +5777,9 @@
       <c r="D224" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="E224" s="6"/>
-      <c r="F224" s="6"/>
-      <c r="G224" s="6"/>
+      <c r="E224" s="3"/>
+      <c r="F224" s="3"/>
+      <c r="G224" s="3"/>
     </row>
     <row r="225" customHeight="1" spans="1:7">
       <c r="A225" s="2">
@@ -5817,9 +5795,9 @@
       <c r="D225" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="E225" s="6"/>
-      <c r="F225" s="6"/>
-      <c r="G225" s="6"/>
+      <c r="E225" s="3"/>
+      <c r="F225" s="3"/>
+      <c r="G225" s="3"/>
     </row>
     <row r="226" customHeight="1" spans="1:7">
       <c r="A226" s="2">
@@ -5835,9 +5813,9 @@
       <c r="D226" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="E226" s="6"/>
-      <c r="F226" s="6"/>
-      <c r="G226" s="6"/>
+      <c r="E226" s="3"/>
+      <c r="F226" s="3"/>
+      <c r="G226" s="3"/>
     </row>
     <row r="227" customHeight="1" spans="1:7">
       <c r="A227" s="2">
@@ -5853,9 +5831,9 @@
       <c r="D227" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="E227" s="6"/>
-      <c r="F227" s="6"/>
-      <c r="G227" s="6"/>
+      <c r="E227" s="3"/>
+      <c r="F227" s="3"/>
+      <c r="G227" s="3"/>
     </row>
     <row r="228" customHeight="1" spans="1:7">
       <c r="A228" s="2">
@@ -5871,9 +5849,9 @@
       <c r="D228" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="E228" s="6"/>
-      <c r="F228" s="6"/>
-      <c r="G228" s="6"/>
+      <c r="E228" s="3"/>
+      <c r="F228" s="3"/>
+      <c r="G228" s="3"/>
     </row>
     <row r="229" customHeight="1" spans="1:7">
       <c r="A229" s="2">
@@ -5889,9 +5867,9 @@
       <c r="D229" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="E229" s="6"/>
-      <c r="F229" s="6"/>
-      <c r="G229" s="6"/>
+      <c r="E229" s="3"/>
+      <c r="F229" s="3"/>
+      <c r="G229" s="3"/>
     </row>
     <row r="230" customHeight="1" spans="1:7">
       <c r="A230" s="2">
@@ -5907,9 +5885,9 @@
       <c r="D230" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="E230" s="6"/>
-      <c r="F230" s="6"/>
-      <c r="G230" s="6"/>
+      <c r="E230" s="3"/>
+      <c r="F230" s="3"/>
+      <c r="G230" s="3"/>
     </row>
     <row r="231" customHeight="1" spans="1:7">
       <c r="A231" s="2">
@@ -5925,9 +5903,9 @@
       <c r="D231" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="E231" s="6"/>
-      <c r="F231" s="6"/>
-      <c r="G231" s="6"/>
+      <c r="E231" s="3"/>
+      <c r="F231" s="3"/>
+      <c r="G231" s="3"/>
     </row>
     <row r="232" customHeight="1" spans="1:7">
       <c r="A232" s="2">
@@ -5943,9 +5921,9 @@
       <c r="D232" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="E232" s="6"/>
-      <c r="F232" s="6"/>
-      <c r="G232" s="6"/>
+      <c r="E232" s="3"/>
+      <c r="F232" s="3"/>
+      <c r="G232" s="3"/>
     </row>
     <row r="233" customHeight="1" spans="1:7">
       <c r="A233" s="2">
@@ -5961,9 +5939,9 @@
       <c r="D233" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="E233" s="6"/>
-      <c r="F233" s="6"/>
-      <c r="G233" s="6"/>
+      <c r="E233" s="3"/>
+      <c r="F233" s="3"/>
+      <c r="G233" s="3"/>
     </row>
     <row r="234" customHeight="1" spans="1:7">
       <c r="A234" s="2">
@@ -5979,9 +5957,9 @@
       <c r="D234" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="E234" s="6"/>
-      <c r="F234" s="6"/>
-      <c r="G234" s="6"/>
+      <c r="E234" s="3"/>
+      <c r="F234" s="3"/>
+      <c r="G234" s="3"/>
     </row>
     <row r="235" customHeight="1" spans="1:7">
       <c r="A235" s="2">
@@ -5997,9 +5975,9 @@
       <c r="D235" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="E235" s="6"/>
-      <c r="F235" s="6"/>
-      <c r="G235" s="6"/>
+      <c r="E235" s="3"/>
+      <c r="F235" s="3"/>
+      <c r="G235" s="3"/>
     </row>
     <row r="236" customHeight="1" spans="1:7">
       <c r="A236" s="2">
@@ -6015,9 +5993,9 @@
       <c r="D236" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="E236" s="6"/>
-      <c r="F236" s="6"/>
-      <c r="G236" s="6"/>
+      <c r="E236" s="3"/>
+      <c r="F236" s="3"/>
+      <c r="G236" s="3"/>
     </row>
     <row r="237" customHeight="1" spans="1:7">
       <c r="A237" s="2">
@@ -6033,9 +6011,9 @@
       <c r="D237" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="E237" s="6"/>
-      <c r="F237" s="6"/>
-      <c r="G237" s="6"/>
+      <c r="E237" s="3"/>
+      <c r="F237" s="3"/>
+      <c r="G237" s="3"/>
     </row>
     <row r="238" customHeight="1" spans="1:7">
       <c r="A238" s="2">
@@ -6051,9 +6029,9 @@
       <c r="D238" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="E238" s="6"/>
-      <c r="F238" s="6"/>
-      <c r="G238" s="6"/>
+      <c r="E238" s="3"/>
+      <c r="F238" s="3"/>
+      <c r="G238" s="3"/>
     </row>
     <row r="239" customHeight="1" spans="1:7">
       <c r="A239" s="2">
@@ -6069,9 +6047,9 @@
       <c r="D239" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="E239" s="6"/>
-      <c r="F239" s="6"/>
-      <c r="G239" s="6"/>
+      <c r="E239" s="3"/>
+      <c r="F239" s="3"/>
+      <c r="G239" s="3"/>
     </row>
     <row r="240" customHeight="1" spans="1:7">
       <c r="A240" s="2">
@@ -6087,9 +6065,9 @@
       <c r="D240" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="E240" s="6"/>
-      <c r="F240" s="6"/>
-      <c r="G240" s="6"/>
+      <c r="E240" s="3"/>
+      <c r="F240" s="3"/>
+      <c r="G240" s="3"/>
     </row>
     <row r="241" customHeight="1" spans="1:7">
       <c r="A241" s="2">
@@ -6105,9 +6083,9 @@
       <c r="D241" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="E241" s="6"/>
-      <c r="F241" s="6"/>
-      <c r="G241" s="6"/>
+      <c r="E241" s="3"/>
+      <c r="F241" s="3"/>
+      <c r="G241" s="3"/>
     </row>
     <row r="242" customHeight="1" spans="1:7">
       <c r="A242" s="2">
@@ -6123,9 +6101,9 @@
       <c r="D242" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="E242" s="6"/>
-      <c r="F242" s="6"/>
-      <c r="G242" s="6"/>
+      <c r="E242" s="3"/>
+      <c r="F242" s="3"/>
+      <c r="G242" s="3"/>
     </row>
     <row r="243" customHeight="1" spans="1:7">
       <c r="A243" s="2">
@@ -6141,9 +6119,9 @@
       <c r="D243" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="E243" s="6"/>
-      <c r="F243" s="6"/>
-      <c r="G243" s="6"/>
+      <c r="E243" s="3"/>
+      <c r="F243" s="3"/>
+      <c r="G243" s="3"/>
     </row>
     <row r="244" customHeight="1" spans="1:7">
       <c r="A244" s="2">
@@ -6159,9 +6137,9 @@
       <c r="D244" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="E244" s="6"/>
-      <c r="F244" s="6"/>
-      <c r="G244" s="6"/>
+      <c r="E244" s="3"/>
+      <c r="F244" s="3"/>
+      <c r="G244" s="3"/>
     </row>
     <row r="245" customHeight="1" spans="1:7">
       <c r="A245" s="2">
@@ -6177,9 +6155,9 @@
       <c r="D245" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="E245" s="6"/>
-      <c r="F245" s="6"/>
-      <c r="G245" s="6"/>
+      <c r="E245" s="3"/>
+      <c r="F245" s="3"/>
+      <c r="G245" s="3"/>
     </row>
     <row r="246" customHeight="1" spans="1:7">
       <c r="A246" s="2">
@@ -6195,9 +6173,9 @@
       <c r="D246" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="E246" s="6"/>
-      <c r="F246" s="6"/>
-      <c r="G246" s="6"/>
+      <c r="E246" s="3"/>
+      <c r="F246" s="3"/>
+      <c r="G246" s="3"/>
     </row>
     <row r="247" customHeight="1" spans="1:7">
       <c r="A247" s="2">
@@ -6213,9 +6191,9 @@
       <c r="D247" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="E247" s="6"/>
-      <c r="F247" s="6"/>
-      <c r="G247" s="6"/>
+      <c r="E247" s="3"/>
+      <c r="F247" s="3"/>
+      <c r="G247" s="3"/>
     </row>
     <row r="248" customHeight="1" spans="1:7">
       <c r="A248" s="2">
@@ -6231,9 +6209,9 @@
       <c r="D248" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="E248" s="6"/>
-      <c r="F248" s="6"/>
-      <c r="G248" s="6"/>
+      <c r="E248" s="3"/>
+      <c r="F248" s="3"/>
+      <c r="G248" s="3"/>
     </row>
     <row r="249" customHeight="1" spans="1:7">
       <c r="A249" s="2">
@@ -6249,9 +6227,9 @@
       <c r="D249" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="E249" s="6"/>
-      <c r="F249" s="6"/>
-      <c r="G249" s="6"/>
+      <c r="E249" s="3"/>
+      <c r="F249" s="3"/>
+      <c r="G249" s="3"/>
     </row>
     <row r="250" customHeight="1" spans="1:7">
       <c r="A250" s="2">
@@ -6267,9 +6245,9 @@
       <c r="D250" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="E250" s="6"/>
-      <c r="F250" s="6"/>
-      <c r="G250" s="6"/>
+      <c r="E250" s="3"/>
+      <c r="F250" s="3"/>
+      <c r="G250" s="3"/>
     </row>
     <row r="251" customHeight="1" spans="1:7">
       <c r="A251" s="2">
@@ -6285,9 +6263,9 @@
       <c r="D251" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="E251" s="6"/>
-      <c r="F251" s="6"/>
-      <c r="G251" s="6"/>
+      <c r="E251" s="3"/>
+      <c r="F251" s="3"/>
+      <c r="G251" s="3"/>
     </row>
     <row r="252" customHeight="1" spans="1:7">
       <c r="A252" s="2">
@@ -6303,9 +6281,9 @@
       <c r="D252" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="E252" s="6"/>
-      <c r="F252" s="6"/>
-      <c r="G252" s="6"/>
+      <c r="E252" s="3"/>
+      <c r="F252" s="3"/>
+      <c r="G252" s="3"/>
     </row>
     <row r="253" customHeight="1" spans="1:7">
       <c r="A253" s="2">
@@ -6321,9 +6299,9 @@
       <c r="D253" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="E253" s="6"/>
-      <c r="F253" s="6"/>
-      <c r="G253" s="6"/>
+      <c r="E253" s="3"/>
+      <c r="F253" s="3"/>
+      <c r="G253" s="3"/>
     </row>
     <row r="254" customHeight="1" spans="1:7">
       <c r="A254" s="2">
@@ -6339,13 +6317,13 @@
       <c r="D254" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="E254" s="6"/>
-      <c r="F254" s="6"/>
-      <c r="G254" s="6"/>
+      <c r="E254" s="3"/>
+      <c r="F254" s="3"/>
+      <c r="G254" s="3"/>
     </row>
     <row r="255" customHeight="1" spans="1:7">
       <c r="A255" s="2">
-        <f t="shared" ref="A255:A318" si="4">A254+1</f>
+        <f t="shared" si="3"/>
         <v>249</v>
       </c>
       <c r="B255" s="4" t="s">
@@ -6357,13 +6335,13 @@
       <c r="D255" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="E255" s="6"/>
-      <c r="F255" s="6"/>
-      <c r="G255" s="6"/>
+      <c r="E255" s="3"/>
+      <c r="F255" s="3"/>
+      <c r="G255" s="3"/>
     </row>
     <row r="256" customHeight="1" spans="1:7">
       <c r="A256" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>250</v>
       </c>
       <c r="B256" s="4" t="s">
@@ -6375,13 +6353,13 @@
       <c r="D256" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="E256" s="6"/>
-      <c r="F256" s="6"/>
-      <c r="G256" s="6"/>
+      <c r="E256" s="3"/>
+      <c r="F256" s="3"/>
+      <c r="G256" s="3"/>
     </row>
     <row r="257" customHeight="1" spans="1:7">
       <c r="A257" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>251</v>
       </c>
       <c r="B257" s="4" t="s">
@@ -6393,13 +6371,13 @@
       <c r="D257" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="E257" s="6"/>
-      <c r="F257" s="6"/>
-      <c r="G257" s="6"/>
+      <c r="E257" s="3"/>
+      <c r="F257" s="3"/>
+      <c r="G257" s="3"/>
     </row>
     <row r="258" customHeight="1" spans="1:7">
       <c r="A258" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>252</v>
       </c>
       <c r="B258" s="4" t="s">
@@ -6411,13 +6389,13 @@
       <c r="D258" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="E258" s="6"/>
-      <c r="F258" s="6"/>
-      <c r="G258" s="6"/>
+      <c r="E258" s="3"/>
+      <c r="F258" s="3"/>
+      <c r="G258" s="3"/>
     </row>
     <row r="259" customHeight="1" spans="1:7">
       <c r="A259" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>253</v>
       </c>
       <c r="B259" s="4" t="s">
@@ -6429,13 +6407,13 @@
       <c r="D259" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="E259" s="6"/>
-      <c r="F259" s="6"/>
-      <c r="G259" s="6"/>
+      <c r="E259" s="3"/>
+      <c r="F259" s="3"/>
+      <c r="G259" s="3"/>
     </row>
     <row r="260" customHeight="1" spans="1:7">
       <c r="A260" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>254</v>
       </c>
       <c r="B260" s="4" t="s">
@@ -6447,13 +6425,13 @@
       <c r="D260" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="E260" s="6"/>
-      <c r="F260" s="6"/>
-      <c r="G260" s="6"/>
+      <c r="E260" s="3"/>
+      <c r="F260" s="3"/>
+      <c r="G260" s="3"/>
     </row>
     <row r="261" customHeight="1" spans="1:7">
       <c r="A261" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>255</v>
       </c>
       <c r="B261" s="4" t="s">
@@ -6465,13 +6443,13 @@
       <c r="D261" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="E261" s="6"/>
-      <c r="F261" s="6"/>
-      <c r="G261" s="6"/>
+      <c r="E261" s="3"/>
+      <c r="F261" s="3"/>
+      <c r="G261" s="3"/>
     </row>
     <row r="262" customHeight="1" spans="1:7">
       <c r="A262" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>256</v>
       </c>
       <c r="B262" s="4" t="s">
@@ -6483,13 +6461,13 @@
       <c r="D262" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="E262" s="6"/>
-      <c r="F262" s="6"/>
-      <c r="G262" s="6"/>
+      <c r="E262" s="3"/>
+      <c r="F262" s="3"/>
+      <c r="G262" s="3"/>
     </row>
     <row r="263" customHeight="1" spans="1:7">
       <c r="A263" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>257</v>
       </c>
       <c r="B263" s="4" t="s">
@@ -6501,13 +6479,13 @@
       <c r="D263" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="E263" s="6"/>
-      <c r="F263" s="6"/>
-      <c r="G263" s="6"/>
+      <c r="E263" s="3"/>
+      <c r="F263" s="3"/>
+      <c r="G263" s="3"/>
     </row>
     <row r="264" customHeight="1" spans="1:7">
       <c r="A264" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="A264:A327" si="4">A263+1</f>
         <v>258</v>
       </c>
       <c r="B264" s="4" t="s">
@@ -6519,9 +6497,9 @@
       <c r="D264" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="E264" s="6"/>
-      <c r="F264" s="6"/>
-      <c r="G264" s="6"/>
+      <c r="E264" s="3"/>
+      <c r="F264" s="3"/>
+      <c r="G264" s="3"/>
     </row>
     <row r="265" customHeight="1" spans="1:7">
       <c r="A265" s="2">
@@ -6537,9 +6515,9 @@
       <c r="D265" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="E265" s="6"/>
-      <c r="F265" s="6"/>
-      <c r="G265" s="6"/>
+      <c r="E265" s="3"/>
+      <c r="F265" s="3"/>
+      <c r="G265" s="3"/>
     </row>
     <row r="266" customHeight="1" spans="1:7">
       <c r="A266" s="2">
@@ -6555,9 +6533,9 @@
       <c r="D266" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="E266" s="6"/>
-      <c r="F266" s="6"/>
-      <c r="G266" s="6"/>
+      <c r="E266" s="3"/>
+      <c r="F266" s="3"/>
+      <c r="G266" s="3"/>
     </row>
     <row r="267" customHeight="1" spans="1:7">
       <c r="A267" s="2">
@@ -6573,9 +6551,9 @@
       <c r="D267" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="E267" s="6"/>
-      <c r="F267" s="6"/>
-      <c r="G267" s="6"/>
+      <c r="E267" s="3"/>
+      <c r="F267" s="3"/>
+      <c r="G267" s="3"/>
     </row>
     <row r="268" customHeight="1" spans="1:7">
       <c r="A268" s="2">
@@ -6591,9 +6569,9 @@
       <c r="D268" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="E268" s="6"/>
-      <c r="F268" s="6"/>
-      <c r="G268" s="6"/>
+      <c r="E268" s="3"/>
+      <c r="F268" s="3"/>
+      <c r="G268" s="3"/>
     </row>
     <row r="269" customHeight="1" spans="1:7">
       <c r="A269" s="2">
@@ -6609,9 +6587,9 @@
       <c r="D269" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="E269" s="6"/>
-      <c r="F269" s="6"/>
-      <c r="G269" s="6"/>
+      <c r="E269" s="3"/>
+      <c r="F269" s="3"/>
+      <c r="G269" s="3"/>
     </row>
     <row r="270" customHeight="1" spans="1:7">
       <c r="A270" s="2">
@@ -6627,3415 +6605,3415 @@
       <c r="D270" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="E270" s="6"/>
-      <c r="F270" s="6"/>
-      <c r="G270" s="6"/>
+      <c r="E270" s="3"/>
+      <c r="F270" s="3"/>
+      <c r="G270" s="3"/>
     </row>
     <row r="271" customHeight="1" spans="1:7">
       <c r="A271" s="2">
         <f t="shared" si="4"/>
         <v>265</v>
       </c>
-      <c r="B271" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C271" s="6" t="s">
+      <c r="B271" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C271" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="D271" s="6" t="s">
+      <c r="D271" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="E271" s="6"/>
-      <c r="F271" s="6"/>
-      <c r="G271" s="6"/>
+      <c r="E271" s="3"/>
+      <c r="F271" s="3"/>
+      <c r="G271" s="3"/>
     </row>
     <row r="272" customHeight="1" spans="1:7">
       <c r="A272" s="2">
         <f t="shared" si="4"/>
         <v>266</v>
       </c>
-      <c r="B272" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C272" s="6" t="s">
+      <c r="B272" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C272" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="D272" s="6" t="s">
+      <c r="D272" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="E272" s="6"/>
-      <c r="F272" s="6"/>
-      <c r="G272" s="6"/>
+      <c r="E272" s="3"/>
+      <c r="F272" s="3"/>
+      <c r="G272" s="3"/>
     </row>
     <row r="273" customHeight="1" spans="1:7">
       <c r="A273" s="2">
         <f t="shared" si="4"/>
         <v>267</v>
       </c>
-      <c r="B273" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C273" s="6" t="s">
+      <c r="B273" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C273" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="D273" s="6" t="s">
+      <c r="D273" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="E273" s="6"/>
-      <c r="F273" s="6"/>
-      <c r="G273" s="6"/>
+      <c r="E273" s="3"/>
+      <c r="F273" s="3"/>
+      <c r="G273" s="3"/>
     </row>
     <row r="274" customHeight="1" spans="1:7">
       <c r="A274" s="2">
         <f t="shared" si="4"/>
         <v>268</v>
       </c>
-      <c r="B274" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C274" s="6" t="s">
+      <c r="B274" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C274" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="D274" s="6" t="s">
+      <c r="D274" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="E274" s="6"/>
-      <c r="F274" s="6"/>
-      <c r="G274" s="6"/>
+      <c r="E274" s="3"/>
+      <c r="F274" s="3"/>
+      <c r="G274" s="3"/>
     </row>
     <row r="275" customHeight="1" spans="1:7">
       <c r="A275" s="2">
         <f t="shared" si="4"/>
         <v>269</v>
       </c>
-      <c r="B275" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C275" s="6" t="s">
+      <c r="B275" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C275" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="D275" s="6" t="s">
+      <c r="D275" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="E275" s="6"/>
-      <c r="F275" s="6"/>
-      <c r="G275" s="6"/>
+      <c r="E275" s="3"/>
+      <c r="F275" s="3"/>
+      <c r="G275" s="3"/>
     </row>
     <row r="276" customHeight="1" spans="1:7">
       <c r="A276" s="2">
         <f t="shared" si="4"/>
         <v>270</v>
       </c>
-      <c r="B276" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C276" s="6" t="s">
+      <c r="B276" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C276" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="D276" s="6" t="s">
+      <c r="D276" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="E276" s="6"/>
-      <c r="F276" s="6"/>
-      <c r="G276" s="6"/>
+      <c r="E276" s="3"/>
+      <c r="F276" s="3"/>
+      <c r="G276" s="3"/>
     </row>
     <row r="277" customHeight="1" spans="1:7">
       <c r="A277" s="2">
         <f t="shared" si="4"/>
         <v>271</v>
       </c>
-      <c r="B277" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C277" s="6" t="s">
+      <c r="B277" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C277" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="D277" s="6" t="s">
+      <c r="D277" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="E277" s="6"/>
-      <c r="F277" s="6"/>
-      <c r="G277" s="6"/>
+      <c r="E277" s="3"/>
+      <c r="F277" s="3"/>
+      <c r="G277" s="3"/>
     </row>
     <row r="278" customHeight="1" spans="1:7">
       <c r="A278" s="2">
         <f t="shared" si="4"/>
         <v>272</v>
       </c>
-      <c r="B278" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C278" s="6" t="s">
+      <c r="B278" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C278" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="D278" s="6" t="s">
+      <c r="D278" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="E278" s="6"/>
-      <c r="F278" s="6"/>
-      <c r="G278" s="6"/>
+      <c r="E278" s="3"/>
+      <c r="F278" s="3"/>
+      <c r="G278" s="3"/>
     </row>
     <row r="279" customHeight="1" spans="1:7">
       <c r="A279" s="2">
         <f t="shared" si="4"/>
         <v>273</v>
       </c>
-      <c r="B279" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C279" s="6" t="s">
+      <c r="B279" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C279" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="D279" s="6" t="s">
+      <c r="D279" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="E279" s="6"/>
-      <c r="F279" s="6"/>
-      <c r="G279" s="6"/>
+      <c r="E279" s="3"/>
+      <c r="F279" s="3"/>
+      <c r="G279" s="3"/>
     </row>
     <row r="280" customHeight="1" spans="1:7">
       <c r="A280" s="2">
         <f t="shared" si="4"/>
         <v>274</v>
       </c>
-      <c r="B280" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C280" s="6" t="s">
+      <c r="B280" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C280" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="D280" s="6" t="s">
+      <c r="D280" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="E280" s="6"/>
-      <c r="F280" s="6"/>
-      <c r="G280" s="6"/>
+      <c r="E280" s="3"/>
+      <c r="F280" s="3"/>
+      <c r="G280" s="3"/>
     </row>
     <row r="281" customHeight="1" spans="1:7">
       <c r="A281" s="2">
         <f t="shared" si="4"/>
         <v>275</v>
       </c>
-      <c r="B281" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C281" s="6" t="s">
+      <c r="B281" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C281" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="D281" s="6" t="s">
+      <c r="D281" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="E281" s="6"/>
-      <c r="F281" s="6"/>
-      <c r="G281" s="6"/>
+      <c r="E281" s="3"/>
+      <c r="F281" s="3"/>
+      <c r="G281" s="3"/>
     </row>
     <row r="282" customHeight="1" spans="1:7">
       <c r="A282" s="2">
         <f t="shared" si="4"/>
         <v>276</v>
       </c>
-      <c r="B282" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C282" s="6" t="s">
+      <c r="B282" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C282" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="D282" s="6" t="s">
+      <c r="D282" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="E282" s="6"/>
-      <c r="F282" s="6"/>
-      <c r="G282" s="6"/>
+      <c r="E282" s="3"/>
+      <c r="F282" s="3"/>
+      <c r="G282" s="3"/>
     </row>
     <row r="283" customHeight="1" spans="1:7">
       <c r="A283" s="2">
         <f t="shared" si="4"/>
         <v>277</v>
       </c>
-      <c r="B283" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C283" s="6" t="s">
+      <c r="B283" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C283" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="D283" s="6" t="s">
+      <c r="D283" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="E283" s="6"/>
-      <c r="F283" s="6"/>
-      <c r="G283" s="6"/>
+      <c r="E283" s="3"/>
+      <c r="F283" s="3"/>
+      <c r="G283" s="3"/>
     </row>
     <row r="284" customHeight="1" spans="1:7">
       <c r="A284" s="2">
         <f t="shared" si="4"/>
         <v>278</v>
       </c>
-      <c r="B284" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C284" s="6" t="s">
+      <c r="B284" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C284" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="D284" s="6" t="s">
+      <c r="D284" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="E284" s="6"/>
-      <c r="F284" s="6"/>
-      <c r="G284" s="6"/>
+      <c r="E284" s="3"/>
+      <c r="F284" s="3"/>
+      <c r="G284" s="3"/>
     </row>
     <row r="285" customHeight="1" spans="1:7">
       <c r="A285" s="2">
         <f t="shared" si="4"/>
         <v>279</v>
       </c>
-      <c r="B285" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C285" s="6" t="s">
+      <c r="B285" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C285" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D285" s="6" t="s">
+      <c r="D285" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="E285" s="6"/>
-      <c r="F285" s="6"/>
-      <c r="G285" s="6"/>
+      <c r="E285" s="3"/>
+      <c r="F285" s="3"/>
+      <c r="G285" s="3"/>
     </row>
     <row r="286" customHeight="1" spans="1:7">
       <c r="A286" s="2">
         <f t="shared" si="4"/>
         <v>280</v>
       </c>
-      <c r="B286" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C286" s="6" t="s">
+      <c r="B286" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C286" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="D286" s="6" t="s">
+      <c r="D286" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="E286" s="6"/>
-      <c r="F286" s="6"/>
-      <c r="G286" s="6"/>
+      <c r="E286" s="3"/>
+      <c r="F286" s="3"/>
+      <c r="G286" s="3"/>
     </row>
     <row r="287" customHeight="1" spans="1:7">
       <c r="A287" s="2">
         <f t="shared" si="4"/>
         <v>281</v>
       </c>
-      <c r="B287" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C287" s="6" t="s">
+      <c r="B287" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C287" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="D287" s="6" t="s">
+      <c r="D287" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="E287" s="6"/>
-      <c r="F287" s="6"/>
-      <c r="G287" s="6"/>
+      <c r="E287" s="3"/>
+      <c r="F287" s="3"/>
+      <c r="G287" s="3"/>
     </row>
     <row r="288" customHeight="1" spans="1:7">
       <c r="A288" s="2">
         <f t="shared" si="4"/>
         <v>282</v>
       </c>
-      <c r="B288" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C288" s="6" t="s">
+      <c r="B288" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C288" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="D288" s="6" t="s">
+      <c r="D288" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="E288" s="6"/>
-      <c r="F288" s="6"/>
-      <c r="G288" s="6"/>
+      <c r="E288" s="3"/>
+      <c r="F288" s="3"/>
+      <c r="G288" s="3"/>
     </row>
     <row r="289" customHeight="1" spans="1:7">
       <c r="A289" s="2">
         <f t="shared" si="4"/>
         <v>283</v>
       </c>
-      <c r="B289" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C289" s="6" t="s">
+      <c r="B289" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C289" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="D289" s="6" t="s">
+      <c r="D289" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="E289" s="6"/>
-      <c r="F289" s="6"/>
-      <c r="G289" s="6"/>
+      <c r="E289" s="3"/>
+      <c r="F289" s="3"/>
+      <c r="G289" s="3"/>
     </row>
     <row r="290" customHeight="1" spans="1:7">
       <c r="A290" s="2">
         <f t="shared" si="4"/>
         <v>284</v>
       </c>
-      <c r="B290" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C290" s="6" t="s">
+      <c r="B290" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C290" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="D290" s="6" t="s">
+      <c r="D290" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="E290" s="6"/>
-      <c r="F290" s="6"/>
-      <c r="G290" s="6"/>
+      <c r="E290" s="3"/>
+      <c r="F290" s="3"/>
+      <c r="G290" s="3"/>
     </row>
     <row r="291" customHeight="1" spans="1:7">
       <c r="A291" s="2">
         <f t="shared" si="4"/>
         <v>285</v>
       </c>
-      <c r="B291" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C291" s="6" t="s">
+      <c r="B291" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C291" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="D291" s="6" t="s">
+      <c r="D291" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="E291" s="6"/>
-      <c r="F291" s="6"/>
-      <c r="G291" s="6"/>
+      <c r="E291" s="3"/>
+      <c r="F291" s="3"/>
+      <c r="G291" s="3"/>
     </row>
     <row r="292" customHeight="1" spans="1:7">
       <c r="A292" s="2">
         <f t="shared" si="4"/>
         <v>286</v>
       </c>
-      <c r="B292" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C292" s="6" t="s">
+      <c r="B292" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C292" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="D292" s="6" t="s">
+      <c r="D292" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="E292" s="6"/>
-      <c r="F292" s="6"/>
-      <c r="G292" s="6"/>
+      <c r="E292" s="3"/>
+      <c r="F292" s="3"/>
+      <c r="G292" s="3"/>
     </row>
     <row r="293" customHeight="1" spans="1:7">
       <c r="A293" s="2">
         <f t="shared" si="4"/>
         <v>287</v>
       </c>
-      <c r="B293" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C293" s="6" t="s">
+      <c r="B293" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C293" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="D293" s="6" t="s">
+      <c r="D293" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="E293" s="6"/>
-      <c r="F293" s="6"/>
-      <c r="G293" s="6"/>
+      <c r="E293" s="3"/>
+      <c r="F293" s="3"/>
+      <c r="G293" s="3"/>
     </row>
     <row r="294" customHeight="1" spans="1:7">
       <c r="A294" s="2">
         <f t="shared" si="4"/>
         <v>288</v>
       </c>
-      <c r="B294" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C294" s="6" t="s">
+      <c r="B294" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C294" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="D294" s="6" t="s">
+      <c r="D294" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="E294" s="6"/>
-      <c r="F294" s="6"/>
-      <c r="G294" s="6"/>
+      <c r="E294" s="3"/>
+      <c r="F294" s="3"/>
+      <c r="G294" s="3"/>
     </row>
     <row r="295" customHeight="1" spans="1:7">
       <c r="A295" s="2">
         <f t="shared" si="4"/>
         <v>289</v>
       </c>
-      <c r="B295" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C295" s="6" t="s">
+      <c r="B295" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C295" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="D295" s="6" t="s">
+      <c r="D295" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="E295" s="6"/>
-      <c r="F295" s="6"/>
-      <c r="G295" s="6"/>
+      <c r="E295" s="3"/>
+      <c r="F295" s="3"/>
+      <c r="G295" s="3"/>
     </row>
     <row r="296" customHeight="1" spans="1:7">
       <c r="A296" s="2">
         <f t="shared" si="4"/>
         <v>290</v>
       </c>
-      <c r="B296" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C296" s="6" t="s">
+      <c r="B296" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C296" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="D296" s="6" t="s">
+      <c r="D296" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="E296" s="6"/>
-      <c r="F296" s="6"/>
-      <c r="G296" s="6"/>
+      <c r="E296" s="3"/>
+      <c r="F296" s="3"/>
+      <c r="G296" s="3"/>
     </row>
     <row r="297" customHeight="1" spans="1:7">
       <c r="A297" s="2">
         <f t="shared" si="4"/>
         <v>291</v>
       </c>
-      <c r="B297" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C297" s="6" t="s">
+      <c r="B297" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C297" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="D297" s="6" t="s">
+      <c r="D297" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="E297" s="6"/>
-      <c r="F297" s="6"/>
-      <c r="G297" s="6"/>
+      <c r="E297" s="3"/>
+      <c r="F297" s="3"/>
+      <c r="G297" s="3"/>
     </row>
     <row r="298" customHeight="1" spans="1:7">
       <c r="A298" s="2">
         <f t="shared" si="4"/>
         <v>292</v>
       </c>
-      <c r="B298" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C298" s="6" t="s">
+      <c r="B298" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C298" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="D298" s="6" t="s">
+      <c r="D298" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="E298" s="6"/>
-      <c r="F298" s="6"/>
-      <c r="G298" s="6"/>
+      <c r="E298" s="3"/>
+      <c r="F298" s="3"/>
+      <c r="G298" s="3"/>
     </row>
     <row r="299" customHeight="1" spans="1:7">
       <c r="A299" s="2">
         <f t="shared" si="4"/>
         <v>293</v>
       </c>
-      <c r="B299" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C299" s="6" t="s">
+      <c r="B299" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C299" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="D299" s="6" t="s">
+      <c r="D299" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="E299" s="6"/>
-      <c r="F299" s="6"/>
-      <c r="G299" s="6"/>
+      <c r="E299" s="3"/>
+      <c r="F299" s="3"/>
+      <c r="G299" s="3"/>
     </row>
     <row r="300" customHeight="1" spans="1:7">
       <c r="A300" s="2">
         <f t="shared" si="4"/>
         <v>294</v>
       </c>
-      <c r="B300" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C300" s="6" t="s">
+      <c r="B300" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C300" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="D300" s="6" t="s">
+      <c r="D300" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="E300" s="6"/>
-      <c r="F300" s="6"/>
-      <c r="G300" s="6"/>
+      <c r="E300" s="3"/>
+      <c r="F300" s="3"/>
+      <c r="G300" s="3"/>
     </row>
     <row r="301" customHeight="1" spans="1:7">
       <c r="A301" s="2">
         <f t="shared" si="4"/>
         <v>295</v>
       </c>
-      <c r="B301" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C301" s="6" t="s">
+      <c r="B301" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C301" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="D301" s="6" t="s">
+      <c r="D301" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="E301" s="6"/>
-      <c r="F301" s="6"/>
-      <c r="G301" s="6"/>
+      <c r="E301" s="3"/>
+      <c r="F301" s="3"/>
+      <c r="G301" s="3"/>
     </row>
     <row r="302" customHeight="1" spans="1:7">
       <c r="A302" s="2">
         <f t="shared" si="4"/>
         <v>296</v>
       </c>
-      <c r="B302" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C302" s="6" t="s">
+      <c r="B302" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C302" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="D302" s="6" t="s">
+      <c r="D302" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="E302" s="6"/>
-      <c r="F302" s="6"/>
-      <c r="G302" s="6"/>
+      <c r="E302" s="3"/>
+      <c r="F302" s="3"/>
+      <c r="G302" s="3"/>
     </row>
     <row r="303" customHeight="1" spans="1:7">
       <c r="A303" s="2">
         <f t="shared" si="4"/>
         <v>297</v>
       </c>
-      <c r="B303" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C303" s="6" t="s">
+      <c r="B303" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C303" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="D303" s="6" t="s">
+      <c r="D303" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="E303" s="6"/>
-      <c r="F303" s="6"/>
-      <c r="G303" s="6"/>
+      <c r="E303" s="3"/>
+      <c r="F303" s="3"/>
+      <c r="G303" s="3"/>
     </row>
     <row r="304" customHeight="1" spans="1:7">
       <c r="A304" s="2">
         <f t="shared" si="4"/>
         <v>298</v>
       </c>
-      <c r="B304" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C304" s="6" t="s">
+      <c r="B304" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C304" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="D304" s="6" t="s">
+      <c r="D304" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="E304" s="6"/>
-      <c r="F304" s="6"/>
-      <c r="G304" s="6"/>
+      <c r="E304" s="3"/>
+      <c r="F304" s="3"/>
+      <c r="G304" s="3"/>
     </row>
     <row r="305" customHeight="1" spans="1:7">
       <c r="A305" s="2">
         <f t="shared" si="4"/>
         <v>299</v>
       </c>
-      <c r="B305" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C305" s="6" t="s">
+      <c r="B305" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C305" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="D305" s="6" t="s">
+      <c r="D305" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="E305" s="6"/>
-      <c r="F305" s="6"/>
-      <c r="G305" s="6"/>
+      <c r="E305" s="3"/>
+      <c r="F305" s="3"/>
+      <c r="G305" s="3"/>
     </row>
     <row r="306" customHeight="1" spans="1:7">
       <c r="A306" s="2">
         <f t="shared" si="4"/>
         <v>300</v>
       </c>
-      <c r="B306" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C306" s="6" t="s">
+      <c r="B306" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C306" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="D306" s="6" t="s">
+      <c r="D306" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="E306" s="6"/>
-      <c r="F306" s="6"/>
-      <c r="G306" s="6"/>
+      <c r="E306" s="3"/>
+      <c r="F306" s="3"/>
+      <c r="G306" s="3"/>
     </row>
     <row r="307" customHeight="1" spans="1:7">
       <c r="A307" s="2">
         <f t="shared" si="4"/>
         <v>301</v>
       </c>
-      <c r="B307" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C307" s="6" t="s">
+      <c r="B307" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C307" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="D307" s="6" t="s">
+      <c r="D307" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="E307" s="6"/>
-      <c r="F307" s="6"/>
-      <c r="G307" s="6"/>
+      <c r="E307" s="3"/>
+      <c r="F307" s="3"/>
+      <c r="G307" s="3"/>
     </row>
     <row r="308" customHeight="1" spans="1:7">
       <c r="A308" s="2">
         <f t="shared" si="4"/>
         <v>302</v>
       </c>
-      <c r="B308" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C308" s="6" t="s">
+      <c r="B308" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C308" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="D308" s="6" t="s">
+      <c r="D308" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="E308" s="6"/>
-      <c r="F308" s="6"/>
-      <c r="G308" s="6"/>
+      <c r="E308" s="3"/>
+      <c r="F308" s="3"/>
+      <c r="G308" s="3"/>
     </row>
     <row r="309" customHeight="1" spans="1:7">
       <c r="A309" s="2">
         <f t="shared" si="4"/>
         <v>303</v>
       </c>
-      <c r="B309" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C309" s="6" t="s">
+      <c r="B309" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C309" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="D309" s="6" t="s">
+      <c r="D309" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="E309" s="6"/>
-      <c r="F309" s="6"/>
-      <c r="G309" s="6"/>
+      <c r="E309" s="3"/>
+      <c r="F309" s="3"/>
+      <c r="G309" s="3"/>
     </row>
     <row r="310" customHeight="1" spans="1:7">
       <c r="A310" s="2">
         <f t="shared" si="4"/>
         <v>304</v>
       </c>
-      <c r="B310" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C310" s="6" t="s">
+      <c r="B310" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C310" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="D310" s="6" t="s">
+      <c r="D310" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="E310" s="6"/>
-      <c r="F310" s="6"/>
-      <c r="G310" s="6"/>
+      <c r="E310" s="3"/>
+      <c r="F310" s="3"/>
+      <c r="G310" s="3"/>
     </row>
     <row r="311" customHeight="1" spans="1:7">
       <c r="A311" s="2">
         <f t="shared" si="4"/>
         <v>305</v>
       </c>
-      <c r="B311" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C311" s="6" t="s">
+      <c r="B311" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C311" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="D311" s="6" t="s">
+      <c r="D311" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="E311" s="6"/>
-      <c r="F311" s="6"/>
-      <c r="G311" s="6"/>
+      <c r="E311" s="3"/>
+      <c r="F311" s="3"/>
+      <c r="G311" s="3"/>
     </row>
     <row r="312" customHeight="1" spans="1:7">
       <c r="A312" s="2">
         <f t="shared" si="4"/>
         <v>306</v>
       </c>
-      <c r="B312" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C312" s="6" t="s">
+      <c r="B312" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C312" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="D312" s="6" t="s">
+      <c r="D312" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="E312" s="6"/>
-      <c r="F312" s="6"/>
-      <c r="G312" s="6"/>
+      <c r="E312" s="3"/>
+      <c r="F312" s="3"/>
+      <c r="G312" s="3"/>
     </row>
     <row r="313" customHeight="1" spans="1:7">
       <c r="A313" s="2">
         <f t="shared" si="4"/>
         <v>307</v>
       </c>
-      <c r="B313" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C313" s="6" t="s">
+      <c r="B313" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C313" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="D313" s="6" t="s">
+      <c r="D313" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="E313" s="6"/>
-      <c r="F313" s="6"/>
-      <c r="G313" s="6"/>
+      <c r="E313" s="3"/>
+      <c r="F313" s="3"/>
+      <c r="G313" s="3"/>
     </row>
     <row r="314" customHeight="1" spans="1:7">
       <c r="A314" s="2">
         <f t="shared" si="4"/>
         <v>308</v>
       </c>
-      <c r="B314" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C314" s="6" t="s">
+      <c r="B314" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C314" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="D314" s="6" t="s">
+      <c r="D314" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="E314" s="6"/>
-      <c r="F314" s="6"/>
-      <c r="G314" s="6"/>
+      <c r="E314" s="3"/>
+      <c r="F314" s="3"/>
+      <c r="G314" s="3"/>
     </row>
     <row r="315" customHeight="1" spans="1:7">
       <c r="A315" s="2">
         <f t="shared" si="4"/>
         <v>309</v>
       </c>
-      <c r="B315" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C315" s="6" t="s">
+      <c r="B315" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C315" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="D315" s="6" t="s">
+      <c r="D315" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="E315" s="6"/>
-      <c r="F315" s="6"/>
-      <c r="G315" s="6"/>
+      <c r="E315" s="3"/>
+      <c r="F315" s="3"/>
+      <c r="G315" s="3"/>
     </row>
     <row r="316" customHeight="1" spans="1:7">
       <c r="A316" s="2">
         <f t="shared" si="4"/>
         <v>310</v>
       </c>
-      <c r="B316" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C316" s="6" t="s">
+      <c r="B316" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C316" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="D316" s="6" t="s">
+      <c r="D316" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="E316" s="6"/>
-      <c r="F316" s="6"/>
-      <c r="G316" s="6"/>
+      <c r="E316" s="3"/>
+      <c r="F316" s="3"/>
+      <c r="G316" s="3"/>
     </row>
     <row r="317" customHeight="1" spans="1:7">
       <c r="A317" s="2">
         <f t="shared" si="4"/>
         <v>311</v>
       </c>
-      <c r="B317" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C317" s="6" t="s">
+      <c r="B317" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C317" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="D317" s="6" t="s">
+      <c r="D317" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="E317" s="6"/>
-      <c r="F317" s="6"/>
-      <c r="G317" s="6"/>
+      <c r="E317" s="3"/>
+      <c r="F317" s="3"/>
+      <c r="G317" s="3"/>
     </row>
     <row r="318" customHeight="1" spans="1:7">
       <c r="A318" s="2">
         <f t="shared" si="4"/>
         <v>312</v>
       </c>
-      <c r="B318" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C318" s="6" t="s">
+      <c r="B318" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C318" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="D318" s="6" t="s">
+      <c r="D318" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="E318" s="6"/>
-      <c r="F318" s="6"/>
-      <c r="G318" s="6"/>
+      <c r="E318" s="3"/>
+      <c r="F318" s="3"/>
+      <c r="G318" s="3"/>
     </row>
     <row r="319" customHeight="1" spans="1:7">
       <c r="A319" s="2">
-        <f t="shared" ref="A319:A382" si="5">A318+1</f>
+        <f t="shared" si="4"/>
         <v>313</v>
       </c>
-      <c r="B319" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C319" s="6" t="s">
+      <c r="B319" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C319" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="D319" s="6" t="s">
+      <c r="D319" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="E319" s="6"/>
-      <c r="F319" s="6"/>
-      <c r="G319" s="6"/>
+      <c r="E319" s="3"/>
+      <c r="F319" s="3"/>
+      <c r="G319" s="3"/>
     </row>
     <row r="320" customHeight="1" spans="1:7">
       <c r="A320" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>314</v>
       </c>
-      <c r="B320" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C320" s="6" t="s">
+      <c r="B320" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C320" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="D320" s="6" t="s">
+      <c r="D320" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="E320" s="6"/>
-      <c r="F320" s="6"/>
-      <c r="G320" s="6"/>
+      <c r="E320" s="3"/>
+      <c r="F320" s="3"/>
+      <c r="G320" s="3"/>
     </row>
     <row r="321" customHeight="1" spans="1:7">
       <c r="A321" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>315</v>
       </c>
-      <c r="B321" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C321" s="6" t="s">
+      <c r="B321" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C321" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="D321" s="6" t="s">
+      <c r="D321" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="E321" s="6"/>
-      <c r="F321" s="6"/>
-      <c r="G321" s="6"/>
+      <c r="E321" s="3"/>
+      <c r="F321" s="3"/>
+      <c r="G321" s="3"/>
     </row>
     <row r="322" customHeight="1" spans="1:7">
       <c r="A322" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>316</v>
       </c>
-      <c r="B322" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C322" s="6" t="s">
+      <c r="B322" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C322" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="D322" s="6" t="s">
+      <c r="D322" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="E322" s="6"/>
-      <c r="F322" s="6"/>
-      <c r="G322" s="6"/>
+      <c r="E322" s="3"/>
+      <c r="F322" s="3"/>
+      <c r="G322" s="3"/>
     </row>
     <row r="323" customHeight="1" spans="1:7">
       <c r="A323" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>317</v>
       </c>
-      <c r="B323" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C323" s="6" t="s">
+      <c r="B323" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C323" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="D323" s="6" t="s">
+      <c r="D323" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="E323" s="6"/>
-      <c r="F323" s="6"/>
-      <c r="G323" s="6"/>
+      <c r="E323" s="3"/>
+      <c r="F323" s="3"/>
+      <c r="G323" s="3"/>
     </row>
     <row r="324" customHeight="1" spans="1:7">
       <c r="A324" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>318</v>
       </c>
-      <c r="B324" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C324" s="6" t="s">
+      <c r="B324" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C324" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="D324" s="6" t="s">
+      <c r="D324" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="E324" s="6"/>
-      <c r="F324" s="6"/>
-      <c r="G324" s="6"/>
+      <c r="E324" s="3"/>
+      <c r="F324" s="3"/>
+      <c r="G324" s="3"/>
     </row>
     <row r="325" customHeight="1" spans="1:7">
       <c r="A325" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>319</v>
       </c>
-      <c r="B325" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C325" s="6" t="s">
+      <c r="B325" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C325" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="D325" s="6" t="s">
+      <c r="D325" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="E325" s="6"/>
-      <c r="F325" s="6"/>
-      <c r="G325" s="6"/>
+      <c r="E325" s="3"/>
+      <c r="F325" s="3"/>
+      <c r="G325" s="3"/>
     </row>
     <row r="326" customHeight="1" spans="1:7">
       <c r="A326" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>320</v>
       </c>
-      <c r="B326" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C326" s="6" t="s">
+      <c r="B326" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C326" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="D326" s="6" t="s">
+      <c r="D326" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="E326" s="6"/>
-      <c r="F326" s="6"/>
-      <c r="G326" s="6"/>
+      <c r="E326" s="3"/>
+      <c r="F326" s="3"/>
+      <c r="G326" s="3"/>
     </row>
     <row r="327" customHeight="1" spans="1:7">
       <c r="A327" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>321</v>
       </c>
-      <c r="B327" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C327" s="6" t="s">
+      <c r="B327" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C327" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="D327" s="6" t="s">
+      <c r="D327" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="E327" s="6"/>
-      <c r="F327" s="6"/>
-      <c r="G327" s="6"/>
+      <c r="E327" s="3"/>
+      <c r="F327" s="3"/>
+      <c r="G327" s="3"/>
     </row>
     <row r="328" customHeight="1" spans="1:7">
       <c r="A328" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="A328:A391" si="5">A327+1</f>
         <v>322</v>
       </c>
-      <c r="B328" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C328" s="6" t="s">
+      <c r="B328" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C328" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="D328" s="6" t="s">
+      <c r="D328" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="E328" s="6"/>
-      <c r="F328" s="6"/>
-      <c r="G328" s="6"/>
+      <c r="E328" s="3"/>
+      <c r="F328" s="3"/>
+      <c r="G328" s="3"/>
     </row>
     <row r="329" customHeight="1" spans="1:7">
       <c r="A329" s="2">
         <f t="shared" si="5"/>
         <v>323</v>
       </c>
-      <c r="B329" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C329" s="6" t="s">
+      <c r="B329" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C329" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="D329" s="6" t="s">
+      <c r="D329" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="E329" s="6"/>
-      <c r="F329" s="6"/>
-      <c r="G329" s="6"/>
+      <c r="E329" s="3"/>
+      <c r="F329" s="3"/>
+      <c r="G329" s="3"/>
     </row>
     <row r="330" customHeight="1" spans="1:7">
       <c r="A330" s="2">
         <f t="shared" si="5"/>
         <v>324</v>
       </c>
-      <c r="B330" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C330" s="6" t="s">
+      <c r="B330" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C330" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="D330" s="6" t="s">
+      <c r="D330" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="E330" s="6"/>
-      <c r="F330" s="6"/>
-      <c r="G330" s="6"/>
+      <c r="E330" s="3"/>
+      <c r="F330" s="3"/>
+      <c r="G330" s="3"/>
     </row>
     <row r="331" customHeight="1" spans="1:7">
       <c r="A331" s="2">
         <f t="shared" si="5"/>
         <v>325</v>
       </c>
-      <c r="B331" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C331" s="6" t="s">
+      <c r="B331" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C331" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="D331" s="6" t="s">
+      <c r="D331" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="E331" s="6"/>
-      <c r="F331" s="6"/>
-      <c r="G331" s="6"/>
+      <c r="E331" s="3"/>
+      <c r="F331" s="3"/>
+      <c r="G331" s="3"/>
     </row>
     <row r="332" customHeight="1" spans="1:7">
       <c r="A332" s="2">
         <f t="shared" si="5"/>
         <v>326</v>
       </c>
-      <c r="B332" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C332" s="6" t="s">
+      <c r="B332" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C332" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="D332" s="6" t="s">
+      <c r="D332" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="E332" s="6"/>
-      <c r="F332" s="6"/>
-      <c r="G332" s="6"/>
+      <c r="E332" s="3"/>
+      <c r="F332" s="3"/>
+      <c r="G332" s="3"/>
     </row>
     <row r="333" customHeight="1" spans="1:7">
       <c r="A333" s="2">
         <f t="shared" si="5"/>
         <v>327</v>
       </c>
-      <c r="B333" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C333" s="6" t="s">
+      <c r="B333" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C333" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="D333" s="6" t="s">
+      <c r="D333" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="E333" s="6"/>
-      <c r="F333" s="6"/>
-      <c r="G333" s="6"/>
+      <c r="E333" s="3"/>
+      <c r="F333" s="3"/>
+      <c r="G333" s="3"/>
     </row>
     <row r="334" customHeight="1" spans="1:7">
       <c r="A334" s="2">
         <f t="shared" si="5"/>
         <v>328</v>
       </c>
-      <c r="B334" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C334" s="6" t="s">
+      <c r="B334" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C334" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="D334" s="6" t="s">
+      <c r="D334" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="E334" s="6"/>
-      <c r="F334" s="6"/>
-      <c r="G334" s="6"/>
+      <c r="E334" s="3"/>
+      <c r="F334" s="3"/>
+      <c r="G334" s="3"/>
     </row>
     <row r="335" customHeight="1" spans="1:7">
       <c r="A335" s="2">
         <f t="shared" si="5"/>
         <v>329</v>
       </c>
-      <c r="B335" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C335" s="6" t="s">
+      <c r="B335" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C335" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="D335" s="6" t="s">
+      <c r="D335" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="E335" s="6"/>
-      <c r="F335" s="6"/>
-      <c r="G335" s="6"/>
+      <c r="E335" s="3"/>
+      <c r="F335" s="3"/>
+      <c r="G335" s="3"/>
     </row>
     <row r="336" customHeight="1" spans="1:7">
       <c r="A336" s="2">
         <f t="shared" si="5"/>
         <v>330</v>
       </c>
-      <c r="B336" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C336" s="6" t="s">
+      <c r="B336" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C336" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="D336" s="6" t="s">
+      <c r="D336" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="E336" s="6"/>
-      <c r="F336" s="6"/>
-      <c r="G336" s="6"/>
+      <c r="E336" s="3"/>
+      <c r="F336" s="3"/>
+      <c r="G336" s="3"/>
     </row>
     <row r="337" customHeight="1" spans="1:7">
       <c r="A337" s="2">
         <f t="shared" si="5"/>
         <v>331</v>
       </c>
-      <c r="B337" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C337" s="6" t="s">
+      <c r="B337" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C337" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="D337" s="6" t="s">
+      <c r="D337" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="E337" s="6"/>
-      <c r="F337" s="6"/>
-      <c r="G337" s="6"/>
+      <c r="E337" s="3"/>
+      <c r="F337" s="3"/>
+      <c r="G337" s="3"/>
     </row>
     <row r="338" customHeight="1" spans="1:7">
       <c r="A338" s="2">
         <f t="shared" si="5"/>
         <v>332</v>
       </c>
-      <c r="B338" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C338" s="6" t="s">
+      <c r="B338" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C338" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="D338" s="6" t="s">
+      <c r="D338" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="E338" s="6"/>
-      <c r="F338" s="6"/>
-      <c r="G338" s="6"/>
+      <c r="E338" s="3"/>
+      <c r="F338" s="3"/>
+      <c r="G338" s="3"/>
     </row>
     <row r="339" customHeight="1" spans="1:7">
       <c r="A339" s="2">
         <f t="shared" si="5"/>
         <v>333</v>
       </c>
-      <c r="B339" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C339" s="6" t="s">
+      <c r="B339" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C339" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="D339" s="6" t="s">
+      <c r="D339" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="E339" s="6"/>
-      <c r="F339" s="6"/>
-      <c r="G339" s="6"/>
+      <c r="E339" s="3"/>
+      <c r="F339" s="3"/>
+      <c r="G339" s="3"/>
     </row>
     <row r="340" customHeight="1" spans="1:7">
       <c r="A340" s="2">
         <f t="shared" si="5"/>
         <v>334</v>
       </c>
-      <c r="B340" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C340" s="6" t="s">
+      <c r="B340" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C340" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="D340" s="6" t="s">
+      <c r="D340" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="E340" s="6"/>
-      <c r="F340" s="6"/>
-      <c r="G340" s="6"/>
+      <c r="E340" s="3"/>
+      <c r="F340" s="3"/>
+      <c r="G340" s="3"/>
     </row>
     <row r="341" customHeight="1" spans="1:7">
       <c r="A341" s="2">
         <f t="shared" si="5"/>
         <v>335</v>
       </c>
-      <c r="B341" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C341" s="6" t="s">
+      <c r="B341" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C341" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="D341" s="6" t="s">
+      <c r="D341" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="E341" s="6"/>
-      <c r="F341" s="6"/>
-      <c r="G341" s="6"/>
+      <c r="E341" s="3"/>
+      <c r="F341" s="3"/>
+      <c r="G341" s="3"/>
     </row>
     <row r="342" customHeight="1" spans="1:7">
       <c r="A342" s="2">
         <f t="shared" si="5"/>
         <v>336</v>
       </c>
-      <c r="B342" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C342" s="6" t="s">
+      <c r="B342" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C342" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="D342" s="6" t="s">
+      <c r="D342" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="E342" s="6"/>
-      <c r="F342" s="6"/>
-      <c r="G342" s="6"/>
+      <c r="E342" s="3"/>
+      <c r="F342" s="3"/>
+      <c r="G342" s="3"/>
     </row>
     <row r="343" customHeight="1" spans="1:7">
       <c r="A343" s="2">
         <f t="shared" si="5"/>
         <v>337</v>
       </c>
-      <c r="B343" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C343" s="6" t="s">
+      <c r="B343" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C343" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="D343" s="6" t="s">
+      <c r="D343" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="E343" s="6"/>
-      <c r="F343" s="6"/>
-      <c r="G343" s="6"/>
+      <c r="E343" s="3"/>
+      <c r="F343" s="3"/>
+      <c r="G343" s="3"/>
     </row>
     <row r="344" customHeight="1" spans="1:7">
       <c r="A344" s="2">
         <f t="shared" si="5"/>
         <v>338</v>
       </c>
-      <c r="B344" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C344" s="6" t="s">
+      <c r="B344" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C344" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="D344" s="6" t="s">
+      <c r="D344" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="E344" s="6"/>
-      <c r="F344" s="6"/>
-      <c r="G344" s="6"/>
+      <c r="E344" s="3"/>
+      <c r="F344" s="3"/>
+      <c r="G344" s="3"/>
     </row>
     <row r="345" customHeight="1" spans="1:7">
       <c r="A345" s="2">
         <f t="shared" si="5"/>
         <v>339</v>
       </c>
-      <c r="B345" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C345" s="6" t="s">
+      <c r="B345" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C345" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="D345" s="6" t="s">
+      <c r="D345" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="E345" s="6"/>
-      <c r="F345" s="6"/>
-      <c r="G345" s="6"/>
+      <c r="E345" s="3"/>
+      <c r="F345" s="3"/>
+      <c r="G345" s="3"/>
     </row>
     <row r="346" customHeight="1" spans="1:7">
       <c r="A346" s="2">
         <f t="shared" si="5"/>
         <v>340</v>
       </c>
-      <c r="B346" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C346" s="6" t="s">
+      <c r="B346" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C346" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="D346" s="6" t="s">
+      <c r="D346" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="E346" s="6"/>
-      <c r="F346" s="6"/>
-      <c r="G346" s="6"/>
+      <c r="E346" s="3"/>
+      <c r="F346" s="3"/>
+      <c r="G346" s="3"/>
     </row>
     <row r="347" customHeight="1" spans="1:7">
       <c r="A347" s="2">
         <f t="shared" si="5"/>
         <v>341</v>
       </c>
-      <c r="B347" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C347" s="6" t="s">
+      <c r="B347" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C347" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="D347" s="6" t="s">
+      <c r="D347" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="E347" s="6"/>
-      <c r="F347" s="6"/>
-      <c r="G347" s="6"/>
+      <c r="E347" s="3"/>
+      <c r="F347" s="3"/>
+      <c r="G347" s="3"/>
     </row>
     <row r="348" customHeight="1" spans="1:7">
       <c r="A348" s="2">
         <f t="shared" si="5"/>
         <v>342</v>
       </c>
-      <c r="B348" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C348" s="6" t="s">
+      <c r="B348" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C348" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="D348" s="6" t="s">
+      <c r="D348" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="E348" s="6"/>
-      <c r="F348" s="6"/>
-      <c r="G348" s="6"/>
+      <c r="E348" s="3"/>
+      <c r="F348" s="3"/>
+      <c r="G348" s="3"/>
     </row>
     <row r="349" customHeight="1" spans="1:7">
       <c r="A349" s="2">
         <f t="shared" si="5"/>
         <v>343</v>
       </c>
-      <c r="B349" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C349" s="6" t="s">
+      <c r="B349" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C349" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="D349" s="6" t="s">
+      <c r="D349" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="E349" s="6"/>
-      <c r="F349" s="6"/>
-      <c r="G349" s="6"/>
+      <c r="E349" s="3"/>
+      <c r="F349" s="3"/>
+      <c r="G349" s="3"/>
     </row>
     <row r="350" customHeight="1" spans="1:7">
       <c r="A350" s="2">
         <f t="shared" si="5"/>
         <v>344</v>
       </c>
-      <c r="B350" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C350" s="6" t="s">
+      <c r="B350" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C350" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="D350" s="6" t="s">
+      <c r="D350" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="E350" s="6"/>
-      <c r="F350" s="6"/>
-      <c r="G350" s="6"/>
+      <c r="E350" s="3"/>
+      <c r="F350" s="3"/>
+      <c r="G350" s="3"/>
     </row>
     <row r="351" customHeight="1" spans="1:7">
       <c r="A351" s="2">
         <f t="shared" si="5"/>
         <v>345</v>
       </c>
-      <c r="B351" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C351" s="6" t="s">
+      <c r="B351" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C351" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="D351" s="6" t="s">
+      <c r="D351" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="E351" s="6"/>
-      <c r="F351" s="6"/>
-      <c r="G351" s="6"/>
+      <c r="E351" s="3"/>
+      <c r="F351" s="3"/>
+      <c r="G351" s="3"/>
     </row>
     <row r="352" customHeight="1" spans="1:7">
       <c r="A352" s="2">
         <f t="shared" si="5"/>
         <v>346</v>
       </c>
-      <c r="B352" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C352" s="6" t="s">
+      <c r="B352" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C352" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D352" s="6" t="s">
+      <c r="D352" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="E352" s="6"/>
-      <c r="F352" s="6"/>
-      <c r="G352" s="6"/>
+      <c r="E352" s="3"/>
+      <c r="F352" s="3"/>
+      <c r="G352" s="3"/>
     </row>
     <row r="353" customHeight="1" spans="1:7">
       <c r="A353" s="2">
         <f t="shared" si="5"/>
         <v>347</v>
       </c>
-      <c r="B353" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C353" s="6" t="s">
+      <c r="B353" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C353" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="D353" s="6" t="s">
+      <c r="D353" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="E353" s="6"/>
-      <c r="F353" s="6"/>
-      <c r="G353" s="6"/>
+      <c r="E353" s="3"/>
+      <c r="F353" s="3"/>
+      <c r="G353" s="3"/>
     </row>
     <row r="354" customHeight="1" spans="1:7">
       <c r="A354" s="2">
         <f t="shared" si="5"/>
         <v>348</v>
       </c>
-      <c r="B354" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C354" s="6" t="s">
+      <c r="B354" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C354" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="D354" s="6" t="s">
+      <c r="D354" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="E354" s="6"/>
-      <c r="F354" s="6"/>
-      <c r="G354" s="6"/>
+      <c r="E354" s="3"/>
+      <c r="F354" s="3"/>
+      <c r="G354" s="3"/>
     </row>
     <row r="355" customHeight="1" spans="1:7">
       <c r="A355" s="2">
         <f t="shared" si="5"/>
         <v>349</v>
       </c>
-      <c r="B355" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C355" s="6" t="s">
+      <c r="B355" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C355" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="D355" s="6" t="s">
+      <c r="D355" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="E355" s="6"/>
-      <c r="F355" s="6"/>
-      <c r="G355" s="6"/>
+      <c r="E355" s="3"/>
+      <c r="F355" s="3"/>
+      <c r="G355" s="3"/>
     </row>
     <row r="356" customHeight="1" spans="1:7">
       <c r="A356" s="2">
         <f t="shared" si="5"/>
         <v>350</v>
       </c>
-      <c r="B356" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C356" s="6" t="s">
+      <c r="B356" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C356" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="D356" s="6" t="s">
+      <c r="D356" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="E356" s="6"/>
-      <c r="F356" s="6"/>
-      <c r="G356" s="6"/>
+      <c r="E356" s="3"/>
+      <c r="F356" s="3"/>
+      <c r="G356" s="3"/>
     </row>
     <row r="357" customHeight="1" spans="1:7">
       <c r="A357" s="2">
         <f t="shared" si="5"/>
         <v>351</v>
       </c>
-      <c r="B357" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C357" s="6" t="s">
+      <c r="B357" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C357" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="D357" s="6" t="s">
+      <c r="D357" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="E357" s="6"/>
-      <c r="F357" s="6"/>
-      <c r="G357" s="6"/>
+      <c r="E357" s="3"/>
+      <c r="F357" s="3"/>
+      <c r="G357" s="3"/>
     </row>
     <row r="358" customHeight="1" spans="1:7">
       <c r="A358" s="2">
         <f t="shared" si="5"/>
         <v>352</v>
       </c>
-      <c r="B358" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C358" s="6" t="s">
+      <c r="B358" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C358" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D358" s="6" t="s">
+      <c r="D358" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="E358" s="6"/>
-      <c r="F358" s="6"/>
-      <c r="G358" s="6"/>
+      <c r="E358" s="3"/>
+      <c r="F358" s="3"/>
+      <c r="G358" s="3"/>
     </row>
     <row r="359" customHeight="1" spans="1:7">
       <c r="A359" s="2">
         <f t="shared" si="5"/>
         <v>353</v>
       </c>
-      <c r="B359" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C359" s="6" t="s">
+      <c r="B359" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C359" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="D359" s="6" t="s">
+      <c r="D359" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="E359" s="6"/>
-      <c r="F359" s="6"/>
-      <c r="G359" s="6"/>
+      <c r="E359" s="3"/>
+      <c r="F359" s="3"/>
+      <c r="G359" s="3"/>
     </row>
     <row r="360" customHeight="1" spans="1:7">
       <c r="A360" s="2">
         <f t="shared" si="5"/>
         <v>354</v>
       </c>
-      <c r="B360" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C360" s="6" t="s">
+      <c r="B360" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C360" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D360" s="6" t="s">
+      <c r="D360" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="E360" s="6"/>
-      <c r="F360" s="6"/>
-      <c r="G360" s="6"/>
+      <c r="E360" s="3"/>
+      <c r="F360" s="3"/>
+      <c r="G360" s="3"/>
     </row>
     <row r="361" customHeight="1" spans="1:7">
       <c r="A361" s="2">
         <f t="shared" si="5"/>
         <v>355</v>
       </c>
-      <c r="B361" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C361" s="6" t="s">
+      <c r="B361" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C361" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="D361" s="6" t="s">
+      <c r="D361" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="E361" s="6"/>
-      <c r="F361" s="6"/>
-      <c r="G361" s="6"/>
+      <c r="E361" s="3"/>
+      <c r="F361" s="3"/>
+      <c r="G361" s="3"/>
     </row>
     <row r="362" customHeight="1" spans="1:7">
       <c r="A362" s="2">
         <f t="shared" si="5"/>
         <v>356</v>
       </c>
-      <c r="B362" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C362" s="6" t="s">
+      <c r="B362" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C362" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D362" s="6" t="s">
+      <c r="D362" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="E362" s="6"/>
-      <c r="F362" s="6"/>
-      <c r="G362" s="6"/>
+      <c r="E362" s="3"/>
+      <c r="F362" s="3"/>
+      <c r="G362" s="3"/>
     </row>
     <row r="363" customHeight="1" spans="1:7">
       <c r="A363" s="2">
         <f t="shared" si="5"/>
         <v>357</v>
       </c>
-      <c r="B363" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C363" s="6" t="s">
+      <c r="B363" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C363" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="D363" s="6" t="s">
+      <c r="D363" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="E363" s="6"/>
-      <c r="F363" s="6"/>
-      <c r="G363" s="6"/>
+      <c r="E363" s="3"/>
+      <c r="F363" s="3"/>
+      <c r="G363" s="3"/>
     </row>
     <row r="364" customHeight="1" spans="1:7">
       <c r="A364" s="2">
         <f t="shared" si="5"/>
         <v>358</v>
       </c>
-      <c r="B364" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C364" s="6" t="s">
+      <c r="B364" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C364" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="D364" s="6" t="s">
+      <c r="D364" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="E364" s="6"/>
-      <c r="F364" s="6"/>
-      <c r="G364" s="6"/>
+      <c r="E364" s="3"/>
+      <c r="F364" s="3"/>
+      <c r="G364" s="3"/>
     </row>
     <row r="365" customHeight="1" spans="1:7">
       <c r="A365" s="2">
         <f t="shared" si="5"/>
         <v>359</v>
       </c>
-      <c r="B365" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C365" s="6" t="s">
+      <c r="B365" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C365" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="D365" s="6" t="s">
+      <c r="D365" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="E365" s="6"/>
-      <c r="F365" s="6"/>
-      <c r="G365" s="6"/>
+      <c r="E365" s="3"/>
+      <c r="F365" s="3"/>
+      <c r="G365" s="3"/>
     </row>
     <row r="366" customHeight="1" spans="1:7">
       <c r="A366" s="2">
         <f t="shared" si="5"/>
         <v>360</v>
       </c>
-      <c r="B366" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C366" s="6" t="s">
+      <c r="B366" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C366" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="D366" s="6" t="s">
+      <c r="D366" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="E366" s="6"/>
-      <c r="F366" s="6"/>
-      <c r="G366" s="6"/>
+      <c r="E366" s="3"/>
+      <c r="F366" s="3"/>
+      <c r="G366" s="3"/>
     </row>
     <row r="367" customHeight="1" spans="1:7">
       <c r="A367" s="2">
         <f t="shared" si="5"/>
         <v>361</v>
       </c>
-      <c r="B367" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C367" s="6" t="s">
+      <c r="B367" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C367" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="D367" s="6" t="s">
+      <c r="D367" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="E367" s="6"/>
-      <c r="F367" s="6"/>
-      <c r="G367" s="6"/>
+      <c r="E367" s="3"/>
+      <c r="F367" s="3"/>
+      <c r="G367" s="3"/>
     </row>
     <row r="368" customHeight="1" spans="1:7">
       <c r="A368" s="2">
         <f t="shared" si="5"/>
         <v>362</v>
       </c>
-      <c r="B368" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C368" s="6" t="s">
+      <c r="B368" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C368" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="D368" s="6" t="s">
+      <c r="D368" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="E368" s="6"/>
-      <c r="F368" s="6"/>
-      <c r="G368" s="6"/>
+      <c r="E368" s="3"/>
+      <c r="F368" s="3"/>
+      <c r="G368" s="3"/>
     </row>
     <row r="369" customHeight="1" spans="1:7">
       <c r="A369" s="2">
         <f t="shared" si="5"/>
         <v>363</v>
       </c>
-      <c r="B369" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C369" s="6" t="s">
+      <c r="B369" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C369" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="D369" s="6" t="s">
+      <c r="D369" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="E369" s="6"/>
-      <c r="F369" s="6"/>
-      <c r="G369" s="6"/>
+      <c r="E369" s="3"/>
+      <c r="F369" s="3"/>
+      <c r="G369" s="3"/>
     </row>
     <row r="370" customHeight="1" spans="1:7">
       <c r="A370" s="2">
         <f t="shared" si="5"/>
         <v>364</v>
       </c>
-      <c r="B370" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C370" s="6" t="s">
+      <c r="B370" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C370" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="D370" s="6" t="s">
+      <c r="D370" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="E370" s="6"/>
-      <c r="F370" s="6"/>
-      <c r="G370" s="6"/>
+      <c r="E370" s="3"/>
+      <c r="F370" s="3"/>
+      <c r="G370" s="3"/>
     </row>
     <row r="371" customHeight="1" spans="1:7">
       <c r="A371" s="2">
         <f t="shared" si="5"/>
         <v>365</v>
       </c>
-      <c r="B371" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C371" s="6" t="s">
+      <c r="B371" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C371" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="D371" s="6" t="s">
+      <c r="D371" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="E371" s="6"/>
-      <c r="F371" s="6"/>
-      <c r="G371" s="6"/>
+      <c r="E371" s="3"/>
+      <c r="F371" s="3"/>
+      <c r="G371" s="3"/>
     </row>
     <row r="372" customHeight="1" spans="1:7">
       <c r="A372" s="2">
         <f t="shared" si="5"/>
         <v>366</v>
       </c>
-      <c r="B372" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C372" s="6" t="s">
+      <c r="B372" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C372" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="D372" s="6" t="s">
+      <c r="D372" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="E372" s="6"/>
-      <c r="F372" s="6"/>
-      <c r="G372" s="6"/>
+      <c r="E372" s="3"/>
+      <c r="F372" s="3"/>
+      <c r="G372" s="3"/>
     </row>
     <row r="373" customHeight="1" spans="1:7">
       <c r="A373" s="2">
         <f t="shared" si="5"/>
         <v>367</v>
       </c>
-      <c r="B373" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C373" s="6" t="s">
+      <c r="B373" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C373" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="D373" s="6" t="s">
+      <c r="D373" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="E373" s="6"/>
-      <c r="F373" s="6"/>
-      <c r="G373" s="6"/>
+      <c r="E373" s="3"/>
+      <c r="F373" s="3"/>
+      <c r="G373" s="3"/>
     </row>
     <row r="374" customHeight="1" spans="1:7">
       <c r="A374" s="2">
         <f t="shared" si="5"/>
         <v>368</v>
       </c>
-      <c r="B374" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C374" s="6" t="s">
+      <c r="B374" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C374" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="D374" s="6" t="s">
+      <c r="D374" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="E374" s="6"/>
-      <c r="F374" s="6"/>
-      <c r="G374" s="6"/>
+      <c r="E374" s="3"/>
+      <c r="F374" s="3"/>
+      <c r="G374" s="3"/>
     </row>
     <row r="375" customHeight="1" spans="1:7">
       <c r="A375" s="2">
         <f t="shared" si="5"/>
         <v>369</v>
       </c>
-      <c r="B375" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C375" s="6" t="s">
+      <c r="B375" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C375" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="D375" s="6" t="s">
+      <c r="D375" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="E375" s="6"/>
-      <c r="F375" s="6"/>
-      <c r="G375" s="6"/>
+      <c r="E375" s="3"/>
+      <c r="F375" s="3"/>
+      <c r="G375" s="3"/>
     </row>
     <row r="376" customHeight="1" spans="1:7">
       <c r="A376" s="2">
         <f t="shared" si="5"/>
         <v>370</v>
       </c>
-      <c r="B376" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C376" s="6" t="s">
+      <c r="B376" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C376" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="D376" s="6" t="s">
+      <c r="D376" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="E376" s="6"/>
-      <c r="F376" s="6"/>
-      <c r="G376" s="6"/>
+      <c r="E376" s="3"/>
+      <c r="F376" s="3"/>
+      <c r="G376" s="3"/>
     </row>
     <row r="377" customHeight="1" spans="1:7">
       <c r="A377" s="2">
         <f t="shared" si="5"/>
         <v>371</v>
       </c>
-      <c r="B377" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C377" s="6" t="s">
+      <c r="B377" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C377" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="D377" s="6" t="s">
+      <c r="D377" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="E377" s="6"/>
-      <c r="F377" s="6"/>
-      <c r="G377" s="6"/>
+      <c r="E377" s="3"/>
+      <c r="F377" s="3"/>
+      <c r="G377" s="3"/>
     </row>
     <row r="378" customHeight="1" spans="1:7">
       <c r="A378" s="2">
         <f t="shared" si="5"/>
         <v>372</v>
       </c>
-      <c r="B378" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C378" s="6" t="s">
+      <c r="B378" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C378" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="D378" s="6" t="s">
+      <c r="D378" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="E378" s="6"/>
-      <c r="F378" s="6"/>
-      <c r="G378" s="6"/>
+      <c r="E378" s="3"/>
+      <c r="F378" s="3"/>
+      <c r="G378" s="3"/>
     </row>
     <row r="379" customHeight="1" spans="1:7">
       <c r="A379" s="2">
         <f t="shared" si="5"/>
         <v>373</v>
       </c>
-      <c r="B379" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C379" s="6" t="s">
+      <c r="B379" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C379" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="D379" s="6" t="s">
+      <c r="D379" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="E379" s="6"/>
-      <c r="F379" s="6"/>
-      <c r="G379" s="6"/>
+      <c r="E379" s="3"/>
+      <c r="F379" s="3"/>
+      <c r="G379" s="3"/>
     </row>
     <row r="380" customHeight="1" spans="1:7">
       <c r="A380" s="2">
         <f t="shared" si="5"/>
         <v>374</v>
       </c>
-      <c r="B380" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C380" s="6" t="s">
+      <c r="B380" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C380" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="D380" s="6" t="s">
+      <c r="D380" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="E380" s="6"/>
-      <c r="F380" s="6"/>
-      <c r="G380" s="6"/>
+      <c r="E380" s="3"/>
+      <c r="F380" s="3"/>
+      <c r="G380" s="3"/>
     </row>
     <row r="381" customHeight="1" spans="1:7">
       <c r="A381" s="2">
         <f t="shared" si="5"/>
         <v>375</v>
       </c>
-      <c r="B381" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C381" s="6" t="s">
+      <c r="B381" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C381" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="D381" s="6" t="s">
+      <c r="D381" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="E381" s="6"/>
-      <c r="F381" s="6"/>
-      <c r="G381" s="6"/>
+      <c r="E381" s="3"/>
+      <c r="F381" s="3"/>
+      <c r="G381" s="3"/>
     </row>
     <row r="382" customHeight="1" spans="1:7">
       <c r="A382" s="2">
         <f t="shared" si="5"/>
         <v>376</v>
       </c>
-      <c r="B382" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C382" s="6" t="s">
+      <c r="B382" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C382" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="D382" s="6" t="s">
+      <c r="D382" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="E382" s="6"/>
-      <c r="F382" s="6"/>
-      <c r="G382" s="6"/>
+      <c r="E382" s="3"/>
+      <c r="F382" s="3"/>
+      <c r="G382" s="3"/>
     </row>
     <row r="383" customHeight="1" spans="1:7">
       <c r="A383" s="2">
-        <f t="shared" ref="A383:A446" si="6">A382+1</f>
+        <f t="shared" si="5"/>
         <v>377</v>
       </c>
-      <c r="B383" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C383" s="6" t="s">
+      <c r="B383" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C383" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="D383" s="6" t="s">
+      <c r="D383" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="E383" s="6"/>
-      <c r="F383" s="6"/>
-      <c r="G383" s="6"/>
+      <c r="E383" s="3"/>
+      <c r="F383" s="3"/>
+      <c r="G383" s="3"/>
     </row>
     <row r="384" customHeight="1" spans="1:7">
       <c r="A384" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>378</v>
       </c>
-      <c r="B384" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C384" s="6" t="s">
+      <c r="B384" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C384" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="D384" s="6" t="s">
+      <c r="D384" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="E384" s="6"/>
-      <c r="F384" s="6"/>
-      <c r="G384" s="6"/>
+      <c r="E384" s="3"/>
+      <c r="F384" s="3"/>
+      <c r="G384" s="3"/>
     </row>
     <row r="385" customHeight="1" spans="1:7">
       <c r="A385" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>379</v>
       </c>
-      <c r="B385" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C385" s="6" t="s">
+      <c r="B385" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C385" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="D385" s="6" t="s">
+      <c r="D385" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="E385" s="6"/>
-      <c r="F385" s="6"/>
-      <c r="G385" s="6"/>
+      <c r="E385" s="3"/>
+      <c r="F385" s="3"/>
+      <c r="G385" s="3"/>
     </row>
     <row r="386" customHeight="1" spans="1:7">
       <c r="A386" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>380</v>
       </c>
-      <c r="B386" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C386" s="6" t="s">
+      <c r="B386" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C386" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="D386" s="6" t="s">
+      <c r="D386" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="E386" s="6"/>
-      <c r="F386" s="6"/>
-      <c r="G386" s="6"/>
+      <c r="E386" s="3"/>
+      <c r="F386" s="3"/>
+      <c r="G386" s="3"/>
     </row>
     <row r="387" customHeight="1" spans="1:7">
       <c r="A387" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>381</v>
       </c>
-      <c r="B387" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C387" s="6" t="s">
+      <c r="B387" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C387" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="D387" s="6" t="s">
+      <c r="D387" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="E387" s="6"/>
-      <c r="F387" s="6"/>
-      <c r="G387" s="6"/>
+      <c r="E387" s="3"/>
+      <c r="F387" s="3"/>
+      <c r="G387" s="3"/>
     </row>
     <row r="388" customHeight="1" spans="1:7">
       <c r="A388" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>382</v>
       </c>
-      <c r="B388" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C388" s="6" t="s">
+      <c r="B388" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C388" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="D388" s="6" t="s">
+      <c r="D388" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="E388" s="6"/>
-      <c r="F388" s="6"/>
-      <c r="G388" s="6"/>
+      <c r="E388" s="3"/>
+      <c r="F388" s="3"/>
+      <c r="G388" s="3"/>
     </row>
     <row r="389" customHeight="1" spans="1:7">
       <c r="A389" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>383</v>
       </c>
-      <c r="B389" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C389" s="6" t="s">
+      <c r="B389" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C389" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="D389" s="6" t="s">
+      <c r="D389" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="E389" s="6"/>
-      <c r="F389" s="6"/>
-      <c r="G389" s="6"/>
+      <c r="E389" s="3"/>
+      <c r="F389" s="3"/>
+      <c r="G389" s="3"/>
     </row>
     <row r="390" customHeight="1" spans="1:7">
       <c r="A390" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>384</v>
       </c>
-      <c r="B390" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C390" s="6" t="s">
+      <c r="B390" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C390" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="D390" s="6" t="s">
+      <c r="D390" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="E390" s="6"/>
-      <c r="F390" s="6"/>
-      <c r="G390" s="6"/>
+      <c r="E390" s="3"/>
+      <c r="F390" s="3"/>
+      <c r="G390" s="3"/>
     </row>
     <row r="391" customHeight="1" spans="1:7">
       <c r="A391" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>385</v>
       </c>
-      <c r="B391" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C391" s="6" t="s">
+      <c r="B391" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C391" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="D391" s="6" t="s">
+      <c r="D391" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="E391" s="6"/>
-      <c r="F391" s="6"/>
-      <c r="G391" s="6"/>
+      <c r="E391" s="3"/>
+      <c r="F391" s="3"/>
+      <c r="G391" s="3"/>
     </row>
     <row r="392" customHeight="1" spans="1:7">
       <c r="A392" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="A392:A455" si="6">A391+1</f>
         <v>386</v>
       </c>
-      <c r="B392" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C392" s="6" t="s">
+      <c r="B392" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C392" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="D392" s="6" t="s">
+      <c r="D392" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="E392" s="6"/>
-      <c r="F392" s="6"/>
-      <c r="G392" s="6"/>
+      <c r="E392" s="3"/>
+      <c r="F392" s="3"/>
+      <c r="G392" s="3"/>
     </row>
     <row r="393" customHeight="1" spans="1:7">
       <c r="A393" s="2">
         <f t="shared" si="6"/>
         <v>387</v>
       </c>
-      <c r="B393" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C393" s="6" t="s">
+      <c r="B393" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C393" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="D393" s="6" t="s">
+      <c r="D393" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="E393" s="6"/>
-      <c r="F393" s="6"/>
-      <c r="G393" s="6"/>
+      <c r="E393" s="3"/>
+      <c r="F393" s="3"/>
+      <c r="G393" s="3"/>
     </row>
     <row r="394" customHeight="1" spans="1:7">
       <c r="A394" s="2">
         <f t="shared" si="6"/>
         <v>388</v>
       </c>
-      <c r="B394" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C394" s="6" t="s">
+      <c r="B394" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C394" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="D394" s="6" t="s">
+      <c r="D394" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="E394" s="6"/>
-      <c r="F394" s="6"/>
-      <c r="G394" s="6"/>
+      <c r="E394" s="3"/>
+      <c r="F394" s="3"/>
+      <c r="G394" s="3"/>
     </row>
     <row r="395" customHeight="1" spans="1:7">
       <c r="A395" s="2">
         <f t="shared" si="6"/>
         <v>389</v>
       </c>
-      <c r="B395" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C395" s="6" t="s">
+      <c r="B395" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C395" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="D395" s="6" t="s">
+      <c r="D395" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="E395" s="6"/>
-      <c r="F395" s="6"/>
-      <c r="G395" s="6"/>
+      <c r="E395" s="3"/>
+      <c r="F395" s="3"/>
+      <c r="G395" s="3"/>
     </row>
     <row r="396" customHeight="1" spans="1:7">
       <c r="A396" s="2">
         <f t="shared" si="6"/>
         <v>390</v>
       </c>
-      <c r="B396" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C396" s="6" t="s">
+      <c r="B396" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C396" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="D396" s="6" t="s">
+      <c r="D396" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="E396" s="6"/>
-      <c r="F396" s="6"/>
-      <c r="G396" s="6"/>
+      <c r="E396" s="3"/>
+      <c r="F396" s="3"/>
+      <c r="G396" s="3"/>
     </row>
     <row r="397" customHeight="1" spans="1:7">
       <c r="A397" s="2">
         <f t="shared" si="6"/>
         <v>391</v>
       </c>
-      <c r="B397" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C397" s="6" t="s">
+      <c r="B397" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C397" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="D397" s="6" t="s">
+      <c r="D397" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="E397" s="6"/>
-      <c r="F397" s="6"/>
-      <c r="G397" s="6"/>
+      <c r="E397" s="3"/>
+      <c r="F397" s="3"/>
+      <c r="G397" s="3"/>
     </row>
     <row r="398" customHeight="1" spans="1:7">
       <c r="A398" s="2">
         <f t="shared" si="6"/>
         <v>392</v>
       </c>
-      <c r="B398" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C398" s="6" t="s">
+      <c r="B398" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C398" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="D398" s="6" t="s">
+      <c r="D398" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="E398" s="6"/>
-      <c r="F398" s="6"/>
-      <c r="G398" s="6"/>
+      <c r="E398" s="3"/>
+      <c r="F398" s="3"/>
+      <c r="G398" s="3"/>
     </row>
     <row r="399" customHeight="1" spans="1:7">
       <c r="A399" s="2">
         <f t="shared" si="6"/>
         <v>393</v>
       </c>
-      <c r="B399" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C399" s="6" t="s">
+      <c r="B399" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C399" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="D399" s="6" t="s">
+      <c r="D399" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="E399" s="6"/>
-      <c r="F399" s="6"/>
-      <c r="G399" s="6"/>
+      <c r="E399" s="3"/>
+      <c r="F399" s="3"/>
+      <c r="G399" s="3"/>
     </row>
     <row r="400" customHeight="1" spans="1:7">
       <c r="A400" s="2">
         <f t="shared" si="6"/>
         <v>394</v>
       </c>
-      <c r="B400" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C400" s="6" t="s">
+      <c r="B400" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C400" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="D400" s="6" t="s">
+      <c r="D400" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="E400" s="6"/>
-      <c r="F400" s="6"/>
-      <c r="G400" s="6"/>
+      <c r="E400" s="3"/>
+      <c r="F400" s="3"/>
+      <c r="G400" s="3"/>
     </row>
     <row r="401" customHeight="1" spans="1:7">
       <c r="A401" s="2">
         <f t="shared" si="6"/>
         <v>395</v>
       </c>
-      <c r="B401" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C401" s="6" t="s">
+      <c r="B401" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C401" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="D401" s="6" t="s">
+      <c r="D401" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="E401" s="6"/>
-      <c r="F401" s="6"/>
-      <c r="G401" s="6"/>
+      <c r="E401" s="3"/>
+      <c r="F401" s="3"/>
+      <c r="G401" s="3"/>
     </row>
     <row r="402" customHeight="1" spans="1:7">
       <c r="A402" s="2">
         <f t="shared" si="6"/>
         <v>396</v>
       </c>
-      <c r="B402" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C402" s="6" t="s">
+      <c r="B402" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C402" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="D402" s="6" t="s">
+      <c r="D402" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="E402" s="6"/>
-      <c r="F402" s="6"/>
-      <c r="G402" s="6"/>
+      <c r="E402" s="3"/>
+      <c r="F402" s="3"/>
+      <c r="G402" s="3"/>
     </row>
     <row r="403" customHeight="1" spans="1:7">
       <c r="A403" s="2">
         <f t="shared" si="6"/>
         <v>397</v>
       </c>
-      <c r="B403" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C403" s="6" t="s">
+      <c r="B403" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C403" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="D403" s="6" t="s">
+      <c r="D403" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="E403" s="6"/>
-      <c r="F403" s="6"/>
-      <c r="G403" s="6"/>
+      <c r="E403" s="3"/>
+      <c r="F403" s="3"/>
+      <c r="G403" s="3"/>
     </row>
     <row r="404" customHeight="1" spans="1:7">
       <c r="A404" s="2">
         <f t="shared" si="6"/>
         <v>398</v>
       </c>
-      <c r="B404" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C404" s="6" t="s">
+      <c r="B404" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C404" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="D404" s="6" t="s">
+      <c r="D404" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="E404" s="6"/>
-      <c r="F404" s="6"/>
-      <c r="G404" s="6"/>
+      <c r="E404" s="3"/>
+      <c r="F404" s="3"/>
+      <c r="G404" s="3"/>
     </row>
     <row r="405" customHeight="1" spans="1:7">
       <c r="A405" s="2">
         <f t="shared" si="6"/>
         <v>399</v>
       </c>
-      <c r="B405" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C405" s="6" t="s">
+      <c r="B405" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C405" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="D405" s="6" t="s">
+      <c r="D405" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="E405" s="6"/>
-      <c r="F405" s="6"/>
-      <c r="G405" s="6"/>
+      <c r="E405" s="3"/>
+      <c r="F405" s="3"/>
+      <c r="G405" s="3"/>
     </row>
     <row r="406" customHeight="1" spans="1:7">
       <c r="A406" s="2">
         <f t="shared" si="6"/>
         <v>400</v>
       </c>
-      <c r="B406" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C406" s="6" t="s">
+      <c r="B406" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C406" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="D406" s="6" t="s">
+      <c r="D406" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="E406" s="6"/>
-      <c r="F406" s="6"/>
-      <c r="G406" s="6"/>
+      <c r="E406" s="3"/>
+      <c r="F406" s="3"/>
+      <c r="G406" s="3"/>
     </row>
     <row r="407" customHeight="1" spans="1:7">
       <c r="A407" s="2">
         <f t="shared" si="6"/>
         <v>401</v>
       </c>
-      <c r="B407" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C407" s="6" t="s">
+      <c r="B407" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C407" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="D407" s="6" t="s">
+      <c r="D407" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="E407" s="6"/>
-      <c r="F407" s="6"/>
-      <c r="G407" s="6"/>
+      <c r="E407" s="3"/>
+      <c r="F407" s="3"/>
+      <c r="G407" s="3"/>
     </row>
     <row r="408" customHeight="1" spans="1:7">
       <c r="A408" s="2">
         <f t="shared" si="6"/>
         <v>402</v>
       </c>
-      <c r="B408" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C408" s="6" t="s">
+      <c r="B408" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C408" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="D408" s="6" t="s">
+      <c r="D408" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="E408" s="6"/>
-      <c r="F408" s="6"/>
-      <c r="G408" s="6"/>
+      <c r="E408" s="3"/>
+      <c r="F408" s="3"/>
+      <c r="G408" s="3"/>
     </row>
     <row r="409" customHeight="1" spans="1:7">
       <c r="A409" s="2">
         <f t="shared" si="6"/>
         <v>403</v>
       </c>
-      <c r="B409" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C409" s="6" t="s">
+      <c r="B409" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C409" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="D409" s="6" t="s">
+      <c r="D409" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="E409" s="6"/>
-      <c r="F409" s="6"/>
-      <c r="G409" s="6"/>
+      <c r="E409" s="3"/>
+      <c r="F409" s="3"/>
+      <c r="G409" s="3"/>
     </row>
     <row r="410" customHeight="1" spans="1:7">
       <c r="A410" s="2">
         <f t="shared" si="6"/>
         <v>404</v>
       </c>
-      <c r="B410" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C410" s="6" t="s">
+      <c r="B410" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C410" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="D410" s="6" t="s">
+      <c r="D410" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="E410" s="6"/>
-      <c r="F410" s="6"/>
-      <c r="G410" s="6"/>
+      <c r="E410" s="3"/>
+      <c r="F410" s="3"/>
+      <c r="G410" s="3"/>
     </row>
     <row r="411" customHeight="1" spans="1:7">
       <c r="A411" s="2">
         <f t="shared" si="6"/>
         <v>405</v>
       </c>
-      <c r="B411" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C411" s="6" t="s">
+      <c r="B411" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C411" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="D411" s="6" t="s">
+      <c r="D411" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="E411" s="6"/>
-      <c r="F411" s="6"/>
-      <c r="G411" s="6"/>
+      <c r="E411" s="3"/>
+      <c r="F411" s="3"/>
+      <c r="G411" s="3"/>
     </row>
     <row r="412" customHeight="1" spans="1:7">
       <c r="A412" s="2">
         <f t="shared" si="6"/>
         <v>406</v>
       </c>
-      <c r="B412" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C412" s="6" t="s">
+      <c r="B412" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C412" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="D412" s="6" t="s">
+      <c r="D412" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="E412" s="6"/>
-      <c r="F412" s="6"/>
-      <c r="G412" s="6"/>
+      <c r="E412" s="3"/>
+      <c r="F412" s="3"/>
+      <c r="G412" s="3"/>
     </row>
     <row r="413" customHeight="1" spans="1:7">
       <c r="A413" s="2">
         <f t="shared" si="6"/>
         <v>407</v>
       </c>
-      <c r="B413" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C413" s="6" t="s">
+      <c r="B413" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C413" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="D413" s="6" t="s">
+      <c r="D413" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="E413" s="6"/>
-      <c r="F413" s="6"/>
-      <c r="G413" s="6"/>
+      <c r="E413" s="3"/>
+      <c r="F413" s="3"/>
+      <c r="G413" s="3"/>
     </row>
     <row r="414" customHeight="1" spans="1:7">
       <c r="A414" s="2">
         <f t="shared" si="6"/>
         <v>408</v>
       </c>
-      <c r="B414" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C414" s="6" t="s">
+      <c r="B414" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C414" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="D414" s="6" t="s">
+      <c r="D414" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="E414" s="6"/>
-      <c r="F414" s="6"/>
-      <c r="G414" s="6"/>
+      <c r="E414" s="3"/>
+      <c r="F414" s="3"/>
+      <c r="G414" s="3"/>
     </row>
     <row r="415" customHeight="1" spans="1:7">
       <c r="A415" s="2">
         <f t="shared" si="6"/>
         <v>409</v>
       </c>
-      <c r="B415" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C415" s="6" t="s">
+      <c r="B415" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C415" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="D415" s="6" t="s">
+      <c r="D415" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="E415" s="6"/>
-      <c r="F415" s="6"/>
-      <c r="G415" s="6"/>
+      <c r="E415" s="3"/>
+      <c r="F415" s="3"/>
+      <c r="G415" s="3"/>
     </row>
     <row r="416" customHeight="1" spans="1:7">
       <c r="A416" s="2">
         <f t="shared" si="6"/>
         <v>410</v>
       </c>
-      <c r="B416" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C416" s="6" t="s">
+      <c r="B416" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C416" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="D416" s="6" t="s">
+      <c r="D416" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="E416" s="6"/>
-      <c r="F416" s="6"/>
-      <c r="G416" s="6"/>
+      <c r="E416" s="3"/>
+      <c r="F416" s="3"/>
+      <c r="G416" s="3"/>
     </row>
     <row r="417" customHeight="1" spans="1:7">
       <c r="A417" s="2">
         <f t="shared" si="6"/>
         <v>411</v>
       </c>
-      <c r="B417" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C417" s="6" t="s">
+      <c r="B417" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C417" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="D417" s="6" t="s">
+      <c r="D417" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="E417" s="6"/>
-      <c r="F417" s="6"/>
-      <c r="G417" s="6"/>
+      <c r="E417" s="3"/>
+      <c r="F417" s="3"/>
+      <c r="G417" s="3"/>
     </row>
     <row r="418" customHeight="1" spans="1:7">
       <c r="A418" s="2">
         <f t="shared" si="6"/>
         <v>412</v>
       </c>
-      <c r="B418" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C418" s="6" t="s">
+      <c r="B418" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C418" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="D418" s="6" t="s">
+      <c r="D418" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="E418" s="6"/>
-      <c r="F418" s="6"/>
-      <c r="G418" s="6"/>
+      <c r="E418" s="3"/>
+      <c r="F418" s="3"/>
+      <c r="G418" s="3"/>
     </row>
     <row r="419" customHeight="1" spans="1:7">
       <c r="A419" s="2">
         <f t="shared" si="6"/>
         <v>413</v>
       </c>
-      <c r="B419" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C419" s="6" t="s">
+      <c r="B419" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C419" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="D419" s="6" t="s">
+      <c r="D419" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="E419" s="6"/>
-      <c r="F419" s="6"/>
-      <c r="G419" s="6"/>
+      <c r="E419" s="3"/>
+      <c r="F419" s="3"/>
+      <c r="G419" s="3"/>
     </row>
     <row r="420" customHeight="1" spans="1:7">
       <c r="A420" s="2">
         <f t="shared" si="6"/>
         <v>414</v>
       </c>
-      <c r="B420" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C420" s="6" t="s">
+      <c r="B420" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C420" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="D420" s="6" t="s">
+      <c r="D420" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="E420" s="6"/>
-      <c r="F420" s="6"/>
-      <c r="G420" s="6"/>
+      <c r="E420" s="3"/>
+      <c r="F420" s="3"/>
+      <c r="G420" s="3"/>
     </row>
     <row r="421" customHeight="1" spans="1:7">
       <c r="A421" s="2">
         <f t="shared" si="6"/>
         <v>415</v>
       </c>
-      <c r="B421" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C421" s="6" t="s">
+      <c r="B421" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C421" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="D421" s="6" t="s">
+      <c r="D421" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="E421" s="6"/>
-      <c r="F421" s="6"/>
-      <c r="G421" s="6"/>
+      <c r="E421" s="3"/>
+      <c r="F421" s="3"/>
+      <c r="G421" s="3"/>
     </row>
     <row r="422" customHeight="1" spans="1:7">
       <c r="A422" s="2">
         <f t="shared" si="6"/>
         <v>416</v>
       </c>
-      <c r="B422" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C422" s="6" t="s">
+      <c r="B422" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C422" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="D422" s="6" t="s">
+      <c r="D422" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="E422" s="6"/>
-      <c r="F422" s="6"/>
-      <c r="G422" s="6"/>
+      <c r="E422" s="3"/>
+      <c r="F422" s="3"/>
+      <c r="G422" s="3"/>
     </row>
     <row r="423" customHeight="1" spans="1:7">
       <c r="A423" s="2">
         <f t="shared" si="6"/>
         <v>417</v>
       </c>
-      <c r="B423" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C423" s="6" t="s">
+      <c r="B423" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C423" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="D423" s="6" t="s">
+      <c r="D423" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="E423" s="6"/>
-      <c r="F423" s="6"/>
-      <c r="G423" s="6"/>
+      <c r="E423" s="3"/>
+      <c r="F423" s="3"/>
+      <c r="G423" s="3"/>
     </row>
     <row r="424" customHeight="1" spans="1:7">
       <c r="A424" s="2">
         <f t="shared" si="6"/>
         <v>418</v>
       </c>
-      <c r="B424" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C424" s="6" t="s">
+      <c r="B424" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C424" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="D424" s="6" t="s">
+      <c r="D424" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="E424" s="6"/>
-      <c r="F424" s="6"/>
-      <c r="G424" s="6"/>
+      <c r="E424" s="3"/>
+      <c r="F424" s="3"/>
+      <c r="G424" s="3"/>
     </row>
     <row r="425" customHeight="1" spans="1:7">
       <c r="A425" s="2">
         <f t="shared" si="6"/>
         <v>419</v>
       </c>
-      <c r="B425" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C425" s="6" t="s">
+      <c r="B425" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C425" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D425" s="6" t="s">
+      <c r="D425" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="E425" s="6"/>
-      <c r="F425" s="6"/>
-      <c r="G425" s="6"/>
+      <c r="E425" s="3"/>
+      <c r="F425" s="3"/>
+      <c r="G425" s="3"/>
     </row>
     <row r="426" customHeight="1" spans="1:7">
       <c r="A426" s="2">
         <f t="shared" si="6"/>
         <v>420</v>
       </c>
-      <c r="B426" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C426" s="6" t="s">
+      <c r="B426" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C426" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="D426" s="6" t="s">
+      <c r="D426" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="E426" s="6"/>
-      <c r="F426" s="6"/>
-      <c r="G426" s="6"/>
+      <c r="E426" s="3"/>
+      <c r="F426" s="3"/>
+      <c r="G426" s="3"/>
     </row>
     <row r="427" customHeight="1" spans="1:7">
       <c r="A427" s="2">
         <f t="shared" si="6"/>
         <v>421</v>
       </c>
-      <c r="B427" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C427" s="6" t="s">
+      <c r="B427" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C427" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D427" s="6" t="s">
+      <c r="D427" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="E427" s="6"/>
-      <c r="F427" s="6"/>
-      <c r="G427" s="6"/>
+      <c r="E427" s="3"/>
+      <c r="F427" s="3"/>
+      <c r="G427" s="3"/>
     </row>
     <row r="428" customHeight="1" spans="1:7">
       <c r="A428" s="2">
         <f t="shared" si="6"/>
         <v>422</v>
       </c>
-      <c r="B428" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C428" s="6" t="s">
+      <c r="B428" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C428" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="D428" s="6" t="s">
+      <c r="D428" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="E428" s="6"/>
-      <c r="F428" s="6"/>
-      <c r="G428" s="6"/>
+      <c r="E428" s="3"/>
+      <c r="F428" s="3"/>
+      <c r="G428" s="3"/>
     </row>
     <row r="429" customHeight="1" spans="1:7">
       <c r="A429" s="2">
         <f t="shared" si="6"/>
         <v>423</v>
       </c>
-      <c r="B429" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C429" s="6" t="s">
+      <c r="B429" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C429" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D429" s="6" t="s">
+      <c r="D429" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="E429" s="6"/>
-      <c r="F429" s="6"/>
-      <c r="G429" s="6"/>
+      <c r="E429" s="3"/>
+      <c r="F429" s="3"/>
+      <c r="G429" s="3"/>
     </row>
     <row r="430" customHeight="1" spans="1:7">
       <c r="A430" s="2">
         <f t="shared" si="6"/>
         <v>424</v>
       </c>
-      <c r="B430" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C430" s="6" t="s">
+      <c r="B430" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C430" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="D430" s="6" t="s">
+      <c r="D430" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="E430" s="6"/>
-      <c r="F430" s="6"/>
-      <c r="G430" s="6"/>
+      <c r="E430" s="3"/>
+      <c r="F430" s="3"/>
+      <c r="G430" s="3"/>
     </row>
     <row r="431" customHeight="1" spans="1:7">
       <c r="A431" s="2">
         <f t="shared" si="6"/>
         <v>425</v>
       </c>
-      <c r="B431" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C431" s="6" t="s">
+      <c r="B431" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C431" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="D431" s="6" t="s">
+      <c r="D431" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="E431" s="6"/>
-      <c r="F431" s="6"/>
-      <c r="G431" s="6"/>
+      <c r="E431" s="3"/>
+      <c r="F431" s="3"/>
+      <c r="G431" s="3"/>
     </row>
     <row r="432" customHeight="1" spans="1:7">
       <c r="A432" s="2">
         <f t="shared" si="6"/>
         <v>426</v>
       </c>
-      <c r="B432" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C432" s="6" t="s">
+      <c r="B432" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C432" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="D432" s="6" t="s">
+      <c r="D432" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="E432" s="6"/>
-      <c r="F432" s="6"/>
-      <c r="G432" s="6"/>
+      <c r="E432" s="3"/>
+      <c r="F432" s="3"/>
+      <c r="G432" s="3"/>
     </row>
     <row r="433" customHeight="1" spans="1:7">
       <c r="A433" s="2">
         <f t="shared" si="6"/>
         <v>427</v>
       </c>
-      <c r="B433" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C433" s="6" t="s">
+      <c r="B433" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C433" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="D433" s="6" t="s">
+      <c r="D433" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="E433" s="6"/>
-      <c r="F433" s="6"/>
-      <c r="G433" s="6"/>
+      <c r="E433" s="3"/>
+      <c r="F433" s="3"/>
+      <c r="G433" s="3"/>
     </row>
     <row r="434" customHeight="1" spans="1:7">
       <c r="A434" s="2">
         <f t="shared" si="6"/>
         <v>428</v>
       </c>
-      <c r="B434" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C434" s="6" t="s">
+      <c r="B434" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C434" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="D434" s="6" t="s">
+      <c r="D434" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="E434" s="6"/>
-      <c r="F434" s="6"/>
-      <c r="G434" s="6"/>
+      <c r="E434" s="3"/>
+      <c r="F434" s="3"/>
+      <c r="G434" s="3"/>
     </row>
     <row r="435" customHeight="1" spans="1:7">
       <c r="A435" s="2">
         <f t="shared" si="6"/>
         <v>429</v>
       </c>
-      <c r="B435" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C435" s="6" t="s">
+      <c r="B435" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C435" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="D435" s="6" t="s">
+      <c r="D435" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="E435" s="6"/>
-      <c r="F435" s="6"/>
-      <c r="G435" s="6"/>
+      <c r="E435" s="3"/>
+      <c r="F435" s="3"/>
+      <c r="G435" s="3"/>
     </row>
     <row r="436" customHeight="1" spans="1:7">
       <c r="A436" s="2">
         <f t="shared" si="6"/>
         <v>430</v>
       </c>
-      <c r="B436" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C436" s="6" t="s">
+      <c r="B436" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C436" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D436" s="6" t="s">
+      <c r="D436" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="E436" s="6"/>
-      <c r="F436" s="6"/>
-      <c r="G436" s="6"/>
+      <c r="E436" s="3"/>
+      <c r="F436" s="3"/>
+      <c r="G436" s="3"/>
     </row>
     <row r="437" customHeight="1" spans="1:7">
       <c r="A437" s="2">
         <f t="shared" si="6"/>
         <v>431</v>
       </c>
-      <c r="B437" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C437" s="6" t="s">
+      <c r="B437" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C437" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D437" s="6" t="s">
+      <c r="D437" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="E437" s="6"/>
-      <c r="F437" s="6"/>
-      <c r="G437" s="6"/>
+      <c r="E437" s="3"/>
+      <c r="F437" s="3"/>
+      <c r="G437" s="3"/>
     </row>
     <row r="438" customHeight="1" spans="1:7">
       <c r="A438" s="2">
         <f t="shared" si="6"/>
         <v>432</v>
       </c>
-      <c r="B438" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C438" s="6" t="s">
+      <c r="B438" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C438" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D438" s="6" t="s">
+      <c r="D438" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="E438" s="6"/>
-      <c r="F438" s="6"/>
-      <c r="G438" s="6"/>
+      <c r="E438" s="3"/>
+      <c r="F438" s="3"/>
+      <c r="G438" s="3"/>
     </row>
     <row r="439" customHeight="1" spans="1:7">
       <c r="A439" s="2">
         <f t="shared" si="6"/>
         <v>433</v>
       </c>
-      <c r="B439" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C439" s="6" t="s">
+      <c r="B439" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C439" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D439" s="6" t="s">
+      <c r="D439" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="E439" s="6"/>
-      <c r="F439" s="6"/>
-      <c r="G439" s="6"/>
+      <c r="E439" s="3"/>
+      <c r="F439" s="3"/>
+      <c r="G439" s="3"/>
     </row>
     <row r="440" customHeight="1" spans="1:7">
       <c r="A440" s="2">
         <f t="shared" si="6"/>
         <v>434</v>
       </c>
-      <c r="B440" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C440" s="6" t="s">
+      <c r="B440" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C440" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="D440" s="6" t="s">
+      <c r="D440" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="E440" s="6"/>
-      <c r="F440" s="6"/>
-      <c r="G440" s="6"/>
+      <c r="E440" s="3"/>
+      <c r="F440" s="3"/>
+      <c r="G440" s="3"/>
     </row>
     <row r="441" customHeight="1" spans="1:7">
       <c r="A441" s="2">
         <f t="shared" si="6"/>
         <v>435</v>
       </c>
-      <c r="B441" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C441" s="6" t="s">
+      <c r="B441" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C441" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D441" s="6" t="s">
+      <c r="D441" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="E441" s="6"/>
-      <c r="F441" s="6"/>
-      <c r="G441" s="6"/>
+      <c r="E441" s="3"/>
+      <c r="F441" s="3"/>
+      <c r="G441" s="3"/>
     </row>
     <row r="442" customHeight="1" spans="1:7">
       <c r="A442" s="2">
         <f t="shared" si="6"/>
         <v>436</v>
       </c>
-      <c r="B442" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C442" s="6" t="s">
+      <c r="B442" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C442" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="D442" s="6" t="s">
+      <c r="D442" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="E442" s="6"/>
-      <c r="F442" s="6"/>
-      <c r="G442" s="6"/>
+      <c r="E442" s="3"/>
+      <c r="F442" s="3"/>
+      <c r="G442" s="3"/>
     </row>
     <row r="443" customHeight="1" spans="1:7">
       <c r="A443" s="2">
         <f t="shared" si="6"/>
         <v>437</v>
       </c>
-      <c r="B443" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C443" s="6" t="s">
+      <c r="B443" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C443" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D443" s="6" t="s">
+      <c r="D443" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="E443" s="6"/>
-      <c r="F443" s="6"/>
-      <c r="G443" s="6"/>
+      <c r="E443" s="3"/>
+      <c r="F443" s="3"/>
+      <c r="G443" s="3"/>
     </row>
     <row r="444" customHeight="1" spans="1:7">
       <c r="A444" s="2">
         <f t="shared" si="6"/>
         <v>438</v>
       </c>
-      <c r="B444" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C444" s="6" t="s">
+      <c r="B444" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C444" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D444" s="6" t="s">
+      <c r="D444" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="E444" s="6"/>
-      <c r="F444" s="6"/>
-      <c r="G444" s="6"/>
+      <c r="E444" s="3"/>
+      <c r="F444" s="3"/>
+      <c r="G444" s="3"/>
     </row>
     <row r="445" customHeight="1" spans="1:7">
       <c r="A445" s="2">
         <f t="shared" si="6"/>
         <v>439</v>
       </c>
-      <c r="B445" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C445" s="6" t="s">
+      <c r="B445" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C445" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="D445" s="6" t="s">
+      <c r="D445" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="E445" s="6"/>
-      <c r="F445" s="6"/>
-      <c r="G445" s="6"/>
+      <c r="E445" s="3"/>
+      <c r="F445" s="3"/>
+      <c r="G445" s="3"/>
     </row>
     <row r="446" customHeight="1" spans="1:7">
       <c r="A446" s="2">
         <f t="shared" si="6"/>
         <v>440</v>
       </c>
-      <c r="B446" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C446" s="6" t="s">
+      <c r="B446" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C446" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="D446" s="6" t="s">
+      <c r="D446" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="E446" s="6"/>
-      <c r="F446" s="6"/>
-      <c r="G446" s="6"/>
+      <c r="E446" s="3"/>
+      <c r="F446" s="3"/>
+      <c r="G446" s="3"/>
     </row>
     <row r="447" customHeight="1" spans="1:7">
       <c r="A447" s="2">
-        <f>A446+1</f>
+        <f t="shared" si="6"/>
         <v>441</v>
       </c>
-      <c r="B447" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C447" s="6" t="s">
+      <c r="B447" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C447" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="D447" s="6" t="s">
+      <c r="D447" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="E447" s="6"/>
-      <c r="F447" s="6"/>
-      <c r="G447" s="6"/>
+      <c r="E447" s="3"/>
+      <c r="F447" s="3"/>
+      <c r="G447" s="3"/>
     </row>
     <row r="448" customHeight="1" spans="1:7">
       <c r="A448" s="2">
-        <f>A447+1</f>
+        <f t="shared" si="6"/>
         <v>442</v>
       </c>
-      <c r="B448" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C448" s="6" t="s">
+      <c r="B448" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C448" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="D448" s="6" t="s">
+      <c r="D448" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="E448" s="6"/>
-      <c r="F448" s="6"/>
-      <c r="G448" s="6"/>
+      <c r="E448" s="3"/>
+      <c r="F448" s="3"/>
+      <c r="G448" s="3"/>
     </row>
     <row r="449" customHeight="1" spans="1:7">
       <c r="A449" s="2">
-        <f>A448+1</f>
+        <f t="shared" si="6"/>
         <v>443</v>
       </c>
-      <c r="B449" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C449" s="6" t="s">
+      <c r="B449" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C449" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="D449" s="6" t="s">
+      <c r="D449" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="E449" s="6"/>
-      <c r="F449" s="6"/>
-      <c r="G449" s="6"/>
+      <c r="E449" s="3"/>
+      <c r="F449" s="3"/>
+      <c r="G449" s="3"/>
     </row>
     <row r="450" customHeight="1" spans="1:7">
       <c r="A450" s="2">
-        <f>A449+1</f>
+        <f t="shared" si="6"/>
         <v>444</v>
       </c>
-      <c r="B450" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C450" s="6" t="s">
+      <c r="B450" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C450" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="D450" s="6" t="s">
+      <c r="D450" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="E450" s="6"/>
-      <c r="F450" s="6"/>
-      <c r="G450" s="6"/>
+      <c r="E450" s="3"/>
+      <c r="F450" s="3"/>
+      <c r="G450" s="3"/>
     </row>
     <row r="451" customHeight="1" spans="1:7">
       <c r="A451" s="2">
-        <f>A450+1</f>
+        <f t="shared" si="6"/>
         <v>445</v>
       </c>
-      <c r="B451" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C451" s="6" t="s">
+      <c r="B451" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C451" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="D451" s="6" t="s">
+      <c r="D451" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="E451" s="6"/>
-      <c r="F451" s="6"/>
-      <c r="G451" s="6"/>
+      <c r="E451" s="3"/>
+      <c r="F451" s="3"/>
+      <c r="G451" s="3"/>
     </row>
     <row r="452" customHeight="1" spans="1:7">
       <c r="A452" s="2">
-        <f>A451+1</f>
+        <f t="shared" si="6"/>
         <v>446</v>
       </c>
-      <c r="B452" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C452" s="6" t="s">
+      <c r="B452" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C452" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="D452" s="6" t="s">
+      <c r="D452" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="E452" s="6"/>
-      <c r="F452" s="6"/>
-      <c r="G452" s="6"/>
+      <c r="E452" s="3"/>
+      <c r="F452" s="3"/>
+      <c r="G452" s="3"/>
     </row>
     <row r="453" customHeight="1" spans="1:7">
       <c r="A453" s="2">
-        <f>A452+1</f>
+        <f t="shared" si="6"/>
         <v>447</v>
       </c>
-      <c r="B453" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C453" s="6" t="s">
+      <c r="B453" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C453" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="D453" s="6" t="s">
+      <c r="D453" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="E453" s="6"/>
-      <c r="F453" s="6"/>
-      <c r="G453" s="6"/>
+      <c r="E453" s="3"/>
+      <c r="F453" s="3"/>
+      <c r="G453" s="3"/>
     </row>
     <row r="454" customHeight="1" spans="1:7">
       <c r="A454" s="2">
-        <f>A453+1</f>
+        <f t="shared" si="6"/>
         <v>448</v>
       </c>
-      <c r="B454" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C454" s="6" t="s">
+      <c r="B454" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C454" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="D454" s="6" t="s">
+      <c r="D454" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="E454" s="6"/>
-      <c r="F454" s="6"/>
-      <c r="G454" s="6"/>
+      <c r="E454" s="3"/>
+      <c r="F454" s="3"/>
+      <c r="G454" s="3"/>
     </row>
     <row r="455" customHeight="1" spans="1:7">
       <c r="A455" s="2">
-        <f>A454+1</f>
+        <f t="shared" si="6"/>
         <v>449</v>
       </c>
-      <c r="B455" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C455" s="6" t="s">
+      <c r="B455" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C455" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="D455" s="6" t="s">
+      <c r="D455" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="E455" s="6"/>
-      <c r="F455" s="6"/>
-      <c r="G455" s="6"/>
+      <c r="E455" s="3"/>
+      <c r="F455" s="3"/>
+      <c r="G455" s="3"/>
     </row>
     <row r="456" customHeight="1" spans="1:7">
       <c r="A456" s="2">
         <f>A455+1</f>
         <v>450</v>
       </c>
-      <c r="B456" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C456" s="6" t="s">
+      <c r="B456" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C456" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="D456" s="6" t="s">
+      <c r="D456" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="E456" s="6"/>
-      <c r="F456" s="6"/>
-      <c r="G456" s="6"/>
+      <c r="E456" s="3"/>
+      <c r="F456" s="3"/>
+      <c r="G456" s="3"/>
     </row>
     <row r="457" customHeight="1" spans="1:7">
       <c r="A457" s="2">
         <f>A456+1</f>
         <v>451</v>
       </c>
-      <c r="B457" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C457" s="6" t="s">
+      <c r="B457" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C457" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="D457" s="6" t="s">
+      <c r="D457" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="E457" s="6"/>
-      <c r="F457" s="6"/>
-      <c r="G457" s="6"/>
+      <c r="E457" s="3"/>
+      <c r="F457" s="3"/>
+      <c r="G457" s="3"/>
     </row>
     <row r="458" customHeight="1" spans="1:7">
       <c r="A458" s="2">
         <f>A457+1</f>
         <v>452</v>
       </c>
-      <c r="B458" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C458" s="6" t="s">
+      <c r="B458" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C458" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="D458" s="6" t="s">
+      <c r="D458" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="E458" s="6"/>
-      <c r="F458" s="6"/>
-      <c r="G458" s="6"/>
+      <c r="E458" s="3"/>
+      <c r="F458" s="3"/>
+      <c r="G458" s="3"/>
     </row>
     <row r="459" customHeight="1" spans="1:7">
       <c r="A459" s="2">
         <f>A458+1</f>
         <v>453</v>
       </c>
-      <c r="B459" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C459" s="6" t="s">
+      <c r="B459" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C459" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="D459" s="6" t="s">
+      <c r="D459" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="E459" s="6"/>
-      <c r="F459" s="6"/>
-      <c r="G459" s="6"/>
+      <c r="E459" s="3"/>
+      <c r="F459" s="3"/>
+      <c r="G459" s="3"/>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A6:J62" etc:filterBottomFollowUsedRange="0">
-    <sortState ref="A6:J62">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A6:J459" etc:filterBottomFollowUsedRange="0">
+    <sortState ref="A6:J459">
       <sortCondition ref="B6"/>
     </sortState>
     <extLst/>
@@ -10046,4 +10024,201 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:I6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="5"/>
+  <cols>
+    <col min="1" max="1" width="17.7142857142857" customWidth="1"/>
+    <col min="2" max="2" width="27.5714285714286" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
+    <col min="4" max="4" width="11.1428571428571" customWidth="1"/>
+    <col min="5" max="5" width="16.4285714285714" customWidth="1"/>
+    <col min="6" max="6" width="76" customWidth="1"/>
+    <col min="7" max="7" width="15.7142857142857" customWidth="1"/>
+    <col min="8" max="8" width="16.8571428571429" customWidth="1"/>
+    <col min="9" max="9" width="17.2857142857143" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9">
+      <c r="A1" t="s">
+        <v>180</v>
+      </c>
+      <c r="B1" t="s">
+        <v>181</v>
+      </c>
+      <c r="C1" t="s">
+        <v>182</v>
+      </c>
+      <c r="D1" t="s">
+        <v>183</v>
+      </c>
+      <c r="E1" t="s">
+        <v>184</v>
+      </c>
+      <c r="F1" t="s">
+        <v>185</v>
+      </c>
+      <c r="G1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" t="s">
+        <v>187</v>
+      </c>
+      <c r="B2" t="s">
+        <v>188</v>
+      </c>
+      <c r="C2" t="s">
+        <v>189</v>
+      </c>
+      <c r="D2" t="s">
+        <v>190</v>
+      </c>
+      <c r="E2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G2">
+        <v>3</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" t="s">
+        <v>187</v>
+      </c>
+      <c r="B3" t="s">
+        <v>188</v>
+      </c>
+      <c r="C3" t="s">
+        <v>189</v>
+      </c>
+      <c r="D3" t="s">
+        <v>190</v>
+      </c>
+      <c r="E3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" t="s">
+        <v>72</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" t="s">
+        <v>187</v>
+      </c>
+      <c r="B4" t="s">
+        <v>188</v>
+      </c>
+      <c r="C4" t="s">
+        <v>189</v>
+      </c>
+      <c r="D4" t="s">
+        <v>190</v>
+      </c>
+      <c r="E4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" t="s">
+        <v>61</v>
+      </c>
+      <c r="G4">
+        <v>3</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" t="s">
+        <v>187</v>
+      </c>
+      <c r="B5" t="s">
+        <v>188</v>
+      </c>
+      <c r="C5" t="s">
+        <v>189</v>
+      </c>
+      <c r="D5" t="s">
+        <v>190</v>
+      </c>
+      <c r="E5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F5" t="s">
+        <v>57</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" t="s">
+        <v>187</v>
+      </c>
+      <c r="B6" t="s">
+        <v>188</v>
+      </c>
+      <c r="C6" t="s">
+        <v>189</v>
+      </c>
+      <c r="D6" t="s">
+        <v>190</v>
+      </c>
+      <c r="E6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F6" t="s">
+        <v>74</v>
+      </c>
+      <c r="G6">
+        <v>4</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>
--- a/MATERIAL 1.xlsx
+++ b/MATERIAL 1.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24000" windowHeight="9600" activeTab="1"/>
+    <workbookView windowWidth="24000" windowHeight="9600"/>
   </bookViews>
   <sheets>
     <sheet name="HEADER APLIKASI" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1409" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1465" uniqueCount="196">
   <si>
     <t>NAMA PEKERJAAN :</t>
   </si>
@@ -606,6 +606,21 @@
   </si>
   <si>
     <t>2026-08-13</t>
+  </si>
+  <si>
+    <t>paul panggi</t>
+  </si>
+  <si>
+    <t>pepelegi indah no 17</t>
+  </si>
+  <si>
+    <t>KONTRUKSI TM - 10</t>
+  </si>
+  <si>
+    <t>spklu menganti</t>
+  </si>
+  <si>
+    <t>menganti indah no 104</t>
   </si>
 </sst>
 </file>
@@ -10029,21 +10044,21 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="5"/>
+  <dimension ref="A1:J14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="17.7142857142857" customWidth="1"/>
-    <col min="2" max="2" width="27.5714285714286" customWidth="1"/>
-    <col min="3" max="3" width="16" customWidth="1"/>
-    <col min="4" max="4" width="11.1428571428571" customWidth="1"/>
-    <col min="5" max="5" width="16.4285714285714" customWidth="1"/>
-    <col min="6" max="6" width="76" customWidth="1"/>
-    <col min="7" max="7" width="15.7142857142857" customWidth="1"/>
-    <col min="8" max="8" width="16.8571428571429" customWidth="1"/>
-    <col min="9" max="9" width="17.2857142857143" customWidth="1"/>
+    <col min="1" max="1" width="17.7142857142857" style="1" customWidth="1"/>
+    <col min="2" max="2" width="27.5714285714286" style="1" customWidth="1"/>
+    <col min="3" max="3" width="16" style="1" customWidth="1"/>
+    <col min="4" max="4" width="11.1428571428571" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16.4285714285714" style="1" customWidth="1"/>
+    <col min="6" max="6" width="76" style="1" customWidth="1"/>
+    <col min="7" max="7" width="15.7142857142857" style="1" customWidth="1"/>
+    <col min="8" max="8" width="16.8571428571429" style="1" customWidth="1"/>
+    <col min="9" max="9" width="17.2857142857143" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:10">
       <c r="A1" t="s">
         <v>180</v>
       </c>
@@ -10072,7 +10087,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:10">
       <c r="A2" t="s">
         <v>187</v>
       </c>
@@ -10101,7 +10116,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:10">
       <c r="A3" t="s">
         <v>187</v>
       </c>
@@ -10130,7 +10145,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:10">
       <c r="A4" t="s">
         <v>187</v>
       </c>
@@ -10159,7 +10174,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" spans="1:10">
       <c r="A5" t="s">
         <v>187</v>
       </c>
@@ -10188,7 +10203,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:9">
+    <row r="6" spans="1:10">
       <c r="A6" t="s">
         <v>187</v>
       </c>
@@ -10215,6 +10230,262 @@
       </c>
       <c r="I6">
         <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" t="s">
+        <v>191</v>
+      </c>
+      <c r="B7" t="s">
+        <v>192</v>
+      </c>
+      <c r="C7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D7" t="s">
+        <v>190</v>
+      </c>
+      <c r="E7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F7" t="s">
+        <v>193</v>
+      </c>
+      <c r="G7" t="s">
+        <v>84</v>
+      </c>
+      <c r="H7">
+        <v>3</v>
+      </c>
+      <c r="I7">
+        <v>3</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="A8" t="s">
+        <v>191</v>
+      </c>
+      <c r="B8" t="s">
+        <v>192</v>
+      </c>
+      <c r="C8" t="s">
+        <v>189</v>
+      </c>
+      <c r="D8" t="s">
+        <v>190</v>
+      </c>
+      <c r="E8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F8" t="s">
+        <v>58</v>
+      </c>
+      <c r="G8" t="s">
+        <v>61</v>
+      </c>
+      <c r="H8">
+        <v>2</v>
+      </c>
+      <c r="I8">
+        <v>2</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9" t="s">
+        <v>191</v>
+      </c>
+      <c r="B9" t="s">
+        <v>192</v>
+      </c>
+      <c r="C9" t="s">
+        <v>189</v>
+      </c>
+      <c r="D9" t="s">
+        <v>190</v>
+      </c>
+      <c r="E9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F9" t="s">
+        <v>70</v>
+      </c>
+      <c r="G9" t="s">
+        <v>72</v>
+      </c>
+      <c r="H9">
+        <v>4</v>
+      </c>
+      <c r="I9">
+        <v>4</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="A10" t="s">
+        <v>191</v>
+      </c>
+      <c r="B10" t="s">
+        <v>192</v>
+      </c>
+      <c r="C10" t="s">
+        <v>189</v>
+      </c>
+      <c r="D10" t="s">
+        <v>190</v>
+      </c>
+      <c r="E10" t="s">
+        <v>11</v>
+      </c>
+      <c r="F10" t="s">
+        <v>13</v>
+      </c>
+      <c r="G10" t="s">
+        <v>15</v>
+      </c>
+      <c r="H10">
+        <v>2</v>
+      </c>
+      <c r="I10">
+        <v>2</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="A11" t="s">
+        <v>194</v>
+      </c>
+      <c r="B11" t="s">
+        <v>195</v>
+      </c>
+      <c r="C11" t="s">
+        <v>189</v>
+      </c>
+      <c r="D11" t="s">
+        <v>190</v>
+      </c>
+      <c r="E11" t="s">
+        <v>11</v>
+      </c>
+      <c r="F11" t="s">
+        <v>70</v>
+      </c>
+      <c r="G11" t="s">
+        <v>74</v>
+      </c>
+      <c r="H11">
+        <v>1</v>
+      </c>
+      <c r="I11">
+        <v>1</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="A12" t="s">
+        <v>194</v>
+      </c>
+      <c r="B12" t="s">
+        <v>195</v>
+      </c>
+      <c r="C12" t="s">
+        <v>189</v>
+      </c>
+      <c r="D12" t="s">
+        <v>190</v>
+      </c>
+      <c r="E12" t="s">
+        <v>11</v>
+      </c>
+      <c r="F12" t="s">
+        <v>58</v>
+      </c>
+      <c r="G12" t="s">
+        <v>61</v>
+      </c>
+      <c r="H12">
+        <v>1</v>
+      </c>
+      <c r="I12">
+        <v>1</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="A13" t="s">
+        <v>194</v>
+      </c>
+      <c r="B13" t="s">
+        <v>195</v>
+      </c>
+      <c r="C13" t="s">
+        <v>189</v>
+      </c>
+      <c r="D13" t="s">
+        <v>190</v>
+      </c>
+      <c r="E13" t="s">
+        <v>11</v>
+      </c>
+      <c r="F13" t="s">
+        <v>70</v>
+      </c>
+      <c r="G13" t="s">
+        <v>72</v>
+      </c>
+      <c r="H13">
+        <v>1</v>
+      </c>
+      <c r="I13">
+        <v>1</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="A14" t="s">
+        <v>194</v>
+      </c>
+      <c r="B14" t="s">
+        <v>195</v>
+      </c>
+      <c r="C14" t="s">
+        <v>189</v>
+      </c>
+      <c r="D14" t="s">
+        <v>190</v>
+      </c>
+      <c r="E14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F14" t="s">
+        <v>58</v>
+      </c>
+      <c r="G14" t="s">
+        <v>57</v>
+      </c>
+      <c r="H14">
+        <v>2</v>
+      </c>
+      <c r="I14">
+        <v>2</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
